--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Docker\weeklyreport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC9788B-B3AF-4737-ABB0-692230522D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4DD052-C237-427C-8473-95323DE205AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
+    <workbookView xWindow="-4020" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="6" r:id="rId1"/>
     <sheet name="テーブル構成" sheetId="9" r:id="rId2"/>
     <sheet name="画面構成" sheetId="10" r:id="rId3"/>
-    <sheet name="Docker構成" sheetId="7" r:id="rId4"/>
-    <sheet name="Docker" sheetId="11" r:id="rId5"/>
-    <sheet name="練習" sheetId="8" r:id="rId6"/>
-    <sheet name="パスの指定" sheetId="1" r:id="rId7"/>
-    <sheet name="ディスク使用について" sheetId="2" r:id="rId8"/>
-    <sheet name="capter5" sheetId="3" r:id="rId9"/>
-    <sheet name="chapter6" sheetId="4" r:id="rId10"/>
-    <sheet name="Imageの出力_取込" sheetId="5" r:id="rId11"/>
+    <sheet name="Docker" sheetId="11" r:id="rId4"/>
+    <sheet name="python" sheetId="12" r:id="rId5"/>
+    <sheet name="Docker構成" sheetId="7" r:id="rId6"/>
+    <sheet name="練習" sheetId="8" r:id="rId7"/>
+    <sheet name="パスの指定" sheetId="1" r:id="rId8"/>
+    <sheet name="ディスク使用について" sheetId="2" r:id="rId9"/>
+    <sheet name="capter5" sheetId="3" r:id="rId10"/>
+    <sheet name="chapter6" sheetId="4" r:id="rId11"/>
+    <sheet name="Imageの出力_取込" sheetId="5" r:id="rId12"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="315">
   <si>
     <t>Docker Image ディスク使用量とコンテンツサイズについて</t>
     <rPh sb="17" eb="20">
@@ -2213,12 +2214,52 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>エラーログ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ERR_LOG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実行</t>
+    <rPh sb="0" eb="2">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VcXsrvインストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://sourceforge.net/projects/vcxsrv/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インストーラ起動</t>
+    <rPh sb="6" eb="8">
+      <t>キドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インストール完了。デスクトップから起動</t>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2272,6 +2313,15 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2401,12 +2451,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2479,8 +2532,12 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2497,6 +2554,1476 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>258120</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133397</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC441701-70BE-980B-84A0-6AB219A7887C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3800475"/>
+          <a:ext cx="6773220" cy="333422"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>75343</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB7ED5AB-C77A-CC4D-F849-C82881E8C48D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="10975" r="23783"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="352425" y="409575"/>
+          <a:ext cx="9915525" cy="6104668"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>352424</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{456D84C9-F1A3-7595-28CB-1713BC7E7EEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="352424" y="4057650"/>
+          <a:ext cx="2638425" cy="885825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>95804</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>391</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25893D0D-C719-B555-77F4-6FEC7CDBB8C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="352425" y="7038975"/>
+          <a:ext cx="3972479" cy="2800741"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>143436</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>162311</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19469F6A-AFBB-C20F-8B80-5FDA13197B82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10039350"/>
+          <a:ext cx="4020111" cy="2762636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>143436</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>162311</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3D54FE1-31AD-E4BB-7C29-4BAC57973AFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13239750"/>
+          <a:ext cx="4020111" cy="2762636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>295415</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>133480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7EAEE57-B71B-507A-4345-46F688BADA9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="16640175"/>
+          <a:ext cx="1000265" cy="933580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>276903</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>95738</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E94AE0CD-7278-5C6D-6291-8E45A4EDAA3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="18040350"/>
+          <a:ext cx="4858428" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>276903</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>95738</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A60FDC-4BEA-772D-C170-DCABDD43F0BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="22240875"/>
+          <a:ext cx="4858428" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>276903</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>95738</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7C4EF31-CDBE-217E-1F6D-C51028506832}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="26241375"/>
+          <a:ext cx="4858428" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>276903</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>95738</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C3A54A2-96DC-4370-224E-EC9625446E9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="30441900"/>
+          <a:ext cx="4858428" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC42143-C3C3-4D85-8722-32073AC0303D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3495675" y="9486900"/>
+          <a:ext cx="828674" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74393334-7E95-4439-9E12-9E0442547C74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3505200" y="12639675"/>
+          <a:ext cx="819150" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{948C8B17-1ECA-496E-9381-48DDC73E9A5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3505200" y="15859125"/>
+          <a:ext cx="847725" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F8050BB-4075-47D8-9930-22B86EFD32EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="504824" y="19402425"/>
+          <a:ext cx="1076325" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>257174</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F74FB6FB-C14D-4D5A-B3B5-B537EE12CCA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3276600" y="21336000"/>
+          <a:ext cx="857249" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D43608EA-B86D-47E2-8E01-3B14F43C458F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="533400" y="23488650"/>
+          <a:ext cx="971550" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266699</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7FCF87C-E71B-4ECE-AE75-EACBDE1EF761}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3276599" y="25555575"/>
+          <a:ext cx="866775" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D5C495B-20BF-46A7-B9E3-A3D224A280DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="476250" y="28432125"/>
+          <a:ext cx="1409700" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD09FE5A-34D7-4CAE-9671-8A001AC13388}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3286124" y="29537025"/>
+          <a:ext cx="904875" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82439052-9302-43AB-986B-37D1FB3EC3C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="561975" y="32451675"/>
+          <a:ext cx="1181100" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="正方形/長方形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09CF3BAC-19AF-4BA5-AEEB-E1758079E529}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3276600" y="33756600"/>
+          <a:ext cx="866775" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6803688B-72AE-4DDA-A677-F50DCE5A318D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="514350" y="28003500"/>
+          <a:ext cx="904875" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="吹き出し: 折線 (枠付き、強調線付き) 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19019C57-E78A-CBDA-344B-441AF7C97321}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2352675" y="27451050"/>
+          <a:ext cx="1600200" cy="752475"/>
+        </a:xfrm>
+        <a:prstGeom prst="accentBorderCallout2">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 18750"/>
+            <a:gd name="adj2" fmla="val -8333"/>
+            <a:gd name="adj3" fmla="val 18750"/>
+            <a:gd name="adj4" fmla="val -16667"/>
+            <a:gd name="adj5" fmla="val 87183"/>
+            <a:gd name="adj6" fmla="val -93053"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1300">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>トラブル防止のため、チェックを外す</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="吹き出し: 折線 (枠付き、強調線付き) 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AABB4A19-7831-4EC9-B901-22A6488089E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3619500" y="31813500"/>
+          <a:ext cx="2447925" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="accentBorderCallout2">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 18750"/>
+            <a:gd name="adj2" fmla="val -8333"/>
+            <a:gd name="adj3" fmla="val 18750"/>
+            <a:gd name="adj4" fmla="val -16667"/>
+            <a:gd name="adj5" fmla="val 87183"/>
+            <a:gd name="adj6" fmla="val -93053"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1300">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>任意のフォルダに設定を保存。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1300">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1300">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>次回以降、上記設定で起動</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2721,7 +4248,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2858,7 +4385,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2907,7 +4434,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3044,7 +4571,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3093,7 +4620,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3363,7 +4890,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3545,9 +5072,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3585,7 +5112,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3691,7 +5218,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3833,7 +5360,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3842,9 +5369,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D024D6-0C31-4325-942C-9DF20C863483}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1">
@@ -4002,125 +5529,201 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951AFAFC-64BB-48A0-B0C5-F9BF0356E726}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00EB3AB-A229-45B6-BAF0-CBFC690801AC}">
+  <dimension ref="A1:A72"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1"/>
-    <row r="2" spans="1:3" s="7" customFormat="1">
+    <row r="1" spans="1:1" s="6" customFormat="1">
+      <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="7" customFormat="1">
       <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="7" customFormat="1">
-      <c r="A17" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" s="7" customFormat="1">
-      <c r="A95" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="1" t="s">
-        <v>64</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" s="7" customFormat="1">
+      <c r="A22" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" s="7" customFormat="1">
+      <c r="A37" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" s="7" customFormat="1">
+      <c r="A60" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4131,11 +5734,140 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951AFAFC-64BB-48A0-B0C5-F9BF0356E726}">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="8.75" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="6" customFormat="1"/>
+    <row r="2" spans="1:3" s="7" customFormat="1">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="7" customFormat="1">
+      <c r="A17" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" s="7" customFormat="1">
+      <c r="A95" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A15534C-900B-4E1C-9ED3-A15604A7DB2E}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1">
@@ -4187,18 +5919,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB8AA92-C104-4402-9D79-D3850C7E3800}">
-  <dimension ref="A1:I129"/>
-  <sheetFormatPr defaultColWidth="4.69921875" defaultRowHeight="15"/>
+  <dimension ref="A1:I136"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="4.69921875" style="1"/>
-    <col min="2" max="2" width="3.8984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.75" style="1"/>
+    <col min="2" max="2" width="3.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="4.69921875" style="1"/>
+    <col min="9" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="23" customFormat="1">
@@ -5649,12 +7381,69 @@
         <v>228</v>
       </c>
     </row>
-    <row r="129" spans="3:4">
+    <row r="129" spans="2:8">
       <c r="C129" s="1" t="s">
         <v>304</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>159</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8">
+      <c r="B131" s="1">
+        <v>11</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="D131" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="E131" s="21"/>
+      <c r="F131" s="21"/>
+      <c r="G131" s="21"/>
+      <c r="H131" s="21"/>
+    </row>
+    <row r="132" spans="2:8">
+      <c r="C132" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8">
+      <c r="C135" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8">
+      <c r="C136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5667,16 +7456,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71AA243-8FD7-4F02-9A26-7C24488241D4}">
   <dimension ref="B2:H36"/>
-  <sheetFormatPr defaultColWidth="4.69921875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="2" width="4.69921875" style="1"/>
-    <col min="3" max="3" width="17.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.3984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.69921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.8984375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="4.69921875" style="1"/>
+    <col min="1" max="2" width="4.75" style="1"/>
+    <col min="3" max="3" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -5716,7 +7505,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="30">
+    <row r="4" spans="2:8" ht="31.5">
       <c r="C4" s="1" t="s">
         <v>247</v>
       </c>
@@ -5982,7 +7771,7 @@
       </c>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="3:8" ht="30">
+    <row r="36" spans="3:8" ht="31.5">
       <c r="C36" s="1" t="s">
         <v>247</v>
       </c>
@@ -6003,11 +7792,181 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501F0FCE-E583-4CC3-AACB-28BDBA1C8EE7}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="4.75" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="6" customFormat="1">
+      <c r="A1" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="7" customFormat="1">
+      <c r="A18" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFBF6CF-7FC3-426B-AFBE-A22ED319995D}">
+  <dimension ref="A1:E83"/>
+  <sheetFormatPr defaultColWidth="4.625" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="4.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="18.75">
+      <c r="A1" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E1" r:id="rId1" xr:uid="{9C17269E-5DBD-4121-9C4A-CEF06319CE88}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954BCFCB-6BAA-41A6-B08B-38BC3239599E}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.499984740745262"/>
+  </sheetPr>
   <dimension ref="A1:AI63"/>
-  <sheetFormatPr defaultColWidth="4.69921875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="4.69921875" style="1"/>
+    <col min="1" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="6" customFormat="1">
@@ -6505,137 +8464,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501F0FCE-E583-4CC3-AACB-28BDBA1C8EE7}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="4.69921875" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="16384" width="4.69921875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1">
-      <c r="A1" s="18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="B14" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="B15" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264C402C-30BF-413A-B2A5-65201BF6F05B}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="6" customFormat="1">
@@ -6699,12 +8533,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5394D207-6464-436E-ADE4-2A4026304978}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
@@ -6713,12 +8547,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C229AB-5092-49C9-8D15-67A2BD891095}">
   <dimension ref="A1:A77"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1">
@@ -6726,36 +8560,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="22.2">
+    <row r="51" spans="1:1" ht="22.5">
       <c r="A51" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="18">
+    <row r="52" spans="1:1" ht="18.75">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" ht="18">
+    <row r="53" spans="1:1" ht="18.75">
       <c r="A53" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="18">
+    <row r="54" spans="1:1" ht="18.75">
       <c r="A54" s="3"/>
     </row>
-    <row r="55" spans="1:1" ht="18">
+    <row r="55" spans="1:1" ht="18.75">
       <c r="A55" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="18">
+    <row r="56" spans="1:1" ht="18.75">
       <c r="A56" s="3"/>
     </row>
-    <row r="57" spans="1:1" ht="18">
+    <row r="57" spans="1:1" ht="18.75">
       <c r="A57" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="18">
+    <row r="58" spans="1:1" ht="18.75">
       <c r="A58"/>
     </row>
     <row r="59" spans="1:1">
@@ -6763,31 +8597,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="18">
+    <row r="60" spans="1:1" ht="18.75">
       <c r="A60" s="3"/>
     </row>
-    <row r="61" spans="1:1" ht="18">
+    <row r="61" spans="1:1" ht="18.75">
       <c r="A61" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="18">
+    <row r="62" spans="1:1" ht="18.75">
       <c r="A62" s="3"/>
     </row>
-    <row r="63" spans="1:1" ht="18">
+    <row r="63" spans="1:1" ht="18.75">
       <c r="A63" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="18">
+    <row r="64" spans="1:1" ht="18.75">
       <c r="A64" s="3"/>
     </row>
-    <row r="65" spans="1:1" ht="18">
+    <row r="65" spans="1:1" ht="18.75">
       <c r="A65" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="18">
+    <row r="66" spans="1:1" ht="18.75">
       <c r="A66"/>
     </row>
     <row r="67" spans="1:1">
@@ -6795,31 +8629,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="18">
+    <row r="68" spans="1:1" ht="18.75">
       <c r="A68" s="3"/>
     </row>
-    <row r="69" spans="1:1" ht="18">
+    <row r="69" spans="1:1" ht="18.75">
       <c r="A69" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="18">
+    <row r="70" spans="1:1" ht="18.75">
       <c r="A70" s="3"/>
     </row>
-    <row r="71" spans="1:1" ht="18">
+    <row r="71" spans="1:1" ht="18.75">
       <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="18">
+    <row r="72" spans="1:1" ht="18.75">
       <c r="A72" s="3"/>
     </row>
-    <row r="73" spans="1:1" ht="18">
+    <row r="73" spans="1:1" ht="18.75">
       <c r="A73" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="18">
+    <row r="74" spans="1:1" ht="18.75">
       <c r="A74"/>
     </row>
     <row r="75" spans="1:1">
@@ -6827,216 +8661,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="18">
+    <row r="76" spans="1:1" ht="18.75">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1" ht="18">
+    <row r="77" spans="1:1" ht="18.75">
       <c r="A77"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00EB3AB-A229-45B6-BAF0-CBFC690801AC}">
-  <dimension ref="A1:A72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="16384" width="8.796875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="7" customFormat="1">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" s="7" customFormat="1">
-      <c r="A22" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" s="7" customFormat="1">
-      <c r="A37" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" s="7" customFormat="1">
-      <c r="A60" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="1" t="s">
-        <v>42</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4DD052-C237-427C-8473-95323DE205AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48883F6-BADF-41A9-8109-D284D1C70CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4020" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="6" r:id="rId1"/>

--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48883F6-BADF-41A9-8109-D284D1C70CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAC2290-1DFD-477A-8815-88C491123CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="6" r:id="rId1"/>
@@ -18,25 +18,35 @@
     <sheet name="画面構成" sheetId="10" r:id="rId3"/>
     <sheet name="Docker" sheetId="11" r:id="rId4"/>
     <sheet name="python" sheetId="12" r:id="rId5"/>
-    <sheet name="Docker構成" sheetId="7" r:id="rId6"/>
-    <sheet name="練習" sheetId="8" r:id="rId7"/>
-    <sheet name="パスの指定" sheetId="1" r:id="rId8"/>
-    <sheet name="ディスク使用について" sheetId="2" r:id="rId9"/>
-    <sheet name="capter5" sheetId="3" r:id="rId10"/>
-    <sheet name="chapter6" sheetId="4" r:id="rId11"/>
-    <sheet name="Imageの出力_取込" sheetId="5" r:id="rId12"/>
+    <sheet name="MARIADB" sheetId="13" r:id="rId6"/>
+    <sheet name="パスの指定" sheetId="1" r:id="rId7"/>
+    <sheet name="ディスク使用について" sheetId="2" r:id="rId8"/>
+    <sheet name="capter5" sheetId="3" r:id="rId9"/>
+    <sheet name="chapter6" sheetId="4" r:id="rId10"/>
+    <sheet name="Imageの出力_取込" sheetId="5" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="278">
   <si>
     <t>Docker Image ディスク使用量とコンテンツサイズについて</t>
     <rPh sb="17" eb="20">
@@ -714,270 +724,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Container1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【image】</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>mariaDB</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Typescript</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>webpage</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>network</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>cmd</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>netmariadb000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mariadb</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【Container2】</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【volume:bindmount】</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>file pass</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D:\Docker\weeklyreport\web</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D:\Docker\weeklyreport\mariadb</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-v D:\Docker\weeklyreport\web:</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker create --name mariadb</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker create --name webpage</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-p 3000:8080</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>--net =netmariadb000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker start --name mariadb -i</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker image pull mariadb</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker image pull</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-e MYSQL_ROOT_PASSWORD=mariadbroot</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-e MYSQL_DATABASE=weeklyreport</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-e MYSQL_USER=user01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-e MYSQL_PASSWORD=user01pass</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-dit</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-v D:\Docker\weeklyreport\mariadb:/var/lib/mysql</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-p 3000:3306</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker network create netmariadb000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>mariadb ログイン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>① コンテナ起動後、コンテナ内のubuntuをbashで実行</t>
-    <rPh sb="6" eb="9">
-      <t>キドウゴ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>② ログイン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>mariadb -u ユーザ名 -p</t>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>パスワード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>③ mariaDBコマンド実行が可能になる</t>
-    <rPh sb="13" eb="15">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>④ 外部から接続する場合</t>
-    <rPh sb="2" eb="4">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>--net netmariadb000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker run --name my-web -dit --net  netmariadb000 -p 8080:80 -v D:\www:/var/www/html php:8.2-apache</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>apache　PHPを利用してDB接続を行う</t>
-    <rPh sb="11" eb="13">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>① PHP apacheのイメージを取得</t>
-    <rPh sb="18" eb="20">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>② DB接続の拡張機能（ドライバー）を取得</t>
-    <rPh sb="4" eb="6">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>カクチョウキノウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker exec でコンテナ内に入り、docker-php-ext-install pdo_mysql でドライバーをインストール</t>
-    <rPh sb="17" eb="18">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>③ phpでdb接続を確認</t>
-    <rPh sb="8" eb="10">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>db接続のポイント</t>
-    <rPh sb="2" eb="4">
-      <t>セツゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hostはコンテナ名を指定する。</t>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>dbコンテナとapacheコンテナを同じnetで作成する。</t>
-    <rPh sb="18" eb="19">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>サクセイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2033,10 +1784,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>docker exec -it dbコンテナ名 bash</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>作成</t>
     <rPh sb="0" eb="2">
       <t>サクセイ</t>
@@ -2252,6 +1999,46 @@
     <rPh sb="17" eb="19">
       <t>キドウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DATETIME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PROC_NAME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ERR_CODE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ERR_MESSAGE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ERR_PARAM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>INT(11)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP()</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AUTO_INCREMENT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2324,7 +2111,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2345,12 +2132,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2362,92 +2143,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -2459,7 +2160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2484,52 +2185,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1">
@@ -4027,368 +3692,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>263529</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>131484</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72ABFC51-7EC3-7926-F24F-567675DCC336}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5810250" y="5953125"/>
-          <a:ext cx="4587879" cy="281979"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>206930</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>15560</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C33B864-2752-C31D-EC02-06AB1685086C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5791200" y="7239000"/>
-          <a:ext cx="8526065" cy="2295845"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>19709</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>114502</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6120C943-632D-0FA4-8149-7E96616AF7D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5791200" y="10096500"/>
-          <a:ext cx="4725059" cy="1448002"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>267987</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>53694</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C3C4B3-3C92-2841-E7DC-ABFF06655CC6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5730240" y="12001500"/>
-          <a:ext cx="9221487" cy="2534004"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>160742</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>88094</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FF3C702-B84F-7D80-3BB6-1E7719C85778}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5730240" y="15049500"/>
-          <a:ext cx="5172797" cy="3324689"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1117</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>65058</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB17855-C141-4DDB-8249-5302DF7A2ED9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1228725"/>
-          <a:ext cx="8002117" cy="2076738"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>1905</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>416279</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>103521</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA98C907-C190-4068-BCBC-565B0A1A41A4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5145405"/>
-          <a:ext cx="7083779" cy="4673616"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>191271</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>72744</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEBE43F2-7DA6-4643-9313-02B550F08003}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9925050"/>
-          <a:ext cx="5525271" cy="2530194"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -4434,7 +3737,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4571,7 +3874,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4620,7 +3923,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4890,7 +4193,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -5389,7 +4692,7 @@
         <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5397,7 +4700,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5405,7 +4708,7 @@
         <v>76</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -5413,7 +4716,7 @@
         <v>77</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -5433,93 +4736,93 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -5529,211 +4832,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00EB3AB-A229-45B6-BAF0-CBFC690801AC}">
-  <dimension ref="A1:A72"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="7" customFormat="1">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" s="7" customFormat="1">
-      <c r="A22" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" s="7" customFormat="1">
-      <c r="A37" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" s="7" customFormat="1">
-      <c r="A60" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951AFAFC-64BB-48A0-B0C5-F9BF0356E726}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
@@ -5862,7 +4960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A15534C-900B-4E1C-9ED3-A15604A7DB2E}">
   <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
@@ -5919,7 +5017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB8AA92-C104-4402-9D79-D3850C7E3800}">
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="4.75" style="1"/>
@@ -5933,1517 +5031,1561 @@
     <col min="9" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="23" customFormat="1">
-      <c r="A1" s="23" t="s">
-        <v>305</v>
+    <row r="1" spans="1:9" s="11" customFormat="1">
+      <c r="A1" s="11" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="I5" s="1" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="C6" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
       <c r="I6" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="C7" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="C8" s="1" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="C10" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="C11" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="C12" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="C13" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
+      <c r="C15" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
       <c r="I15" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="C16" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="C17" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="C18" s="1" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="C19" s="1" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="C20" s="1" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="C21" s="1" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="C22" s="1" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="C23" s="1" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="2:8">
       <c r="C24" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="C25" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="C26" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="C27" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
+      <c r="C29" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" spans="2:8">
       <c r="C30" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="C31" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="C32" s="1" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="C33" s="1" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="C34" s="1" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="C35" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="C36" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="C37" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="C38" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="1">
         <v>4</v>
       </c>
-      <c r="C41" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="C41" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
     </row>
     <row r="42" spans="2:8">
       <c r="C42" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="C43" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="C44" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="C45" s="1" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="C46" s="1" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="C47" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="C48" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="C49" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="C50" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="1">
         <v>5</v>
       </c>
-      <c r="C52" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
+      <c r="C52" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
     </row>
     <row r="53" spans="2:8">
       <c r="C53" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="C54" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="C55" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="C56" s="1" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="C58" s="1" t="s">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="C59" s="1" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="C60" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="C61" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="C62" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="C63" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="2:8">
       <c r="B65" s="1">
         <v>6</v>
       </c>
-      <c r="C65" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
+      <c r="C65" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
     </row>
     <row r="66" spans="2:8">
       <c r="C66" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="C67" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="C68" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="C69" s="1" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="C70" s="1" t="s">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="C71" s="1" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="C72" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="C73" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="2:8">
       <c r="C74" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="75" spans="2:8">
       <c r="C75" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="2:8">
       <c r="B77" s="1">
         <v>7</v>
       </c>
-      <c r="C77" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
+      <c r="C77" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
     </row>
     <row r="78" spans="2:8">
       <c r="C78" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="2:8">
       <c r="C79" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="2:8">
       <c r="C80" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="C81" s="1" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" spans="2:8">
       <c r="C82" s="1" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="2:8">
       <c r="C83" s="1" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="2:8">
       <c r="C84" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="2:8">
       <c r="C85" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="C86" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="87" spans="2:8">
       <c r="C87" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="2:8">
       <c r="B89" s="1">
         <v>8</v>
       </c>
-      <c r="C89" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="E89" s="21"/>
-      <c r="F89" s="21"/>
-      <c r="G89" s="21"/>
-      <c r="H89" s="21"/>
+      <c r="C89" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
     </row>
     <row r="90" spans="2:8">
       <c r="C90" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="2:8">
       <c r="C91" s="1" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="2:8">
       <c r="C92" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="2:8">
       <c r="C93" s="1" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>238</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="2:8">
       <c r="C94" s="1" t="s">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="2:8">
       <c r="C95" s="1" t="s">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="2:8">
       <c r="C96" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" spans="2:8">
       <c r="C97" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="1">
         <v>9</v>
       </c>
-      <c r="C100" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="D100" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="E100" s="21"/>
-      <c r="F100" s="21"/>
-      <c r="G100" s="21"/>
-      <c r="H100" s="21"/>
+      <c r="C100" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
     </row>
     <row r="101" spans="2:8">
       <c r="C101" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="C102" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="103" spans="2:8">
       <c r="C103" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="104" spans="2:8">
       <c r="C104" s="1" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
     </row>
     <row r="105" spans="2:8">
       <c r="C105" s="1" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="C106" s="1" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="2:8">
       <c r="C107" s="1" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="2:8">
       <c r="C108" s="1" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="2:8">
       <c r="C109" s="1" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="2:8">
       <c r="C110" s="1" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="111" spans="2:8">
       <c r="C111" s="1" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="2:8">
       <c r="C112" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113" spans="2:8">
       <c r="C113" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="114" spans="2:8">
       <c r="C114" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="2:8">
       <c r="C115" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="2:8">
       <c r="B117" s="1">
         <v>10</v>
       </c>
-      <c r="C117" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="D117" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E117" s="21"/>
-      <c r="F117" s="21"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21"/>
+      <c r="C117" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="9"/>
     </row>
     <row r="118" spans="2:8">
       <c r="C118" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H118" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="2:8">
       <c r="C119" s="1" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
     </row>
     <row r="120" spans="2:8">
       <c r="C120" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H120" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="121" spans="2:8">
       <c r="C121" s="1" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="122" spans="2:8">
       <c r="C122" s="1" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
     </row>
     <row r="123" spans="2:8">
       <c r="C123" s="1" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
     </row>
     <row r="124" spans="2:8">
       <c r="C124" s="1" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
     </row>
     <row r="125" spans="2:8">
       <c r="C125" s="1" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
     </row>
     <row r="126" spans="2:8">
       <c r="C126" s="1" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="127" spans="2:8">
       <c r="C127" s="1" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="128" spans="2:8">
       <c r="C128" s="1" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="2:8">
       <c r="C129" s="1" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="2:8">
       <c r="B131" s="1">
         <v>11</v>
       </c>
-      <c r="C131" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="D131" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="E131" s="21"/>
-      <c r="F131" s="21"/>
-      <c r="G131" s="21"/>
-      <c r="H131" s="21"/>
+      <c r="C131" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9"/>
     </row>
     <row r="132" spans="2:8">
       <c r="C132" s="7" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>167</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8">
+      <c r="C133" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8">
+      <c r="C134" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="2:8">
       <c r="C135" s="1" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="136" spans="2:8">
       <c r="C136" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8">
+      <c r="C137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8">
+      <c r="C138" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -7472,317 +6614,317 @@
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="C2" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3" spans="2:8">
       <c r="C3" s="7" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="31.5">
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>254</v>
+        <v>202</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="C5" s="1" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>252</v>
+        <v>206</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="D6" s="1" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="C7" s="1" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="D8" s="1" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="C9" s="1" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="D10" s="1" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="C11" s="1" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="D12" s="1" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="1">
         <v>2</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="C19" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="2:8">
       <c r="C20" s="7" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="C22" s="1" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="D23" s="1" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="2:8">
-      <c r="C27" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="C27" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" spans="2:8">
       <c r="C28" s="7" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="H28" s="7"/>
     </row>
     <row r="29" spans="2:8">
       <c r="C29" s="1" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="2:8">
       <c r="C30" s="1" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="C31" s="1" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="3:8">
-      <c r="C34" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
+      <c r="C34" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" spans="3:8">
       <c r="C35" s="7" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="H35" s="7"/>
     </row>
     <row r="36" spans="3:8" ht="31.5">
       <c r="C36" s="1" t="s">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>254</v>
+        <v>202</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -7800,119 +6942,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="8" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="7" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -7932,20 +7074,20 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" ht="18.75">
       <c r="A1" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>312</v>
+        <v>264</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="1" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="1" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -7959,581 +7101,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954BCFCB-6BAA-41A6-B08B-38BC3239599E}">
-  <sheetPr>
-    <tabColor theme="0" tint="-0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:AI63"/>
-  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="4.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:35" s="6" customFormat="1">
-      <c r="A1" s="18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:35" s="7" customFormat="1">
-      <c r="A2" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="8"/>
-      <c r="AI2" s="9"/>
-    </row>
-    <row r="3" spans="1:35">
-      <c r="A3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI3" s="11"/>
-    </row>
-    <row r="4" spans="1:35">
-      <c r="A4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI4" s="11"/>
-    </row>
-    <row r="5" spans="1:35">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI5" s="11"/>
-    </row>
-    <row r="6" spans="1:35">
-      <c r="A6" s="10"/>
-      <c r="B6" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI6" s="11"/>
-    </row>
-    <row r="7" spans="1:35">
-      <c r="A7" s="10"/>
-      <c r="B7" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="10"/>
-      <c r="T7" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="AI7" s="11"/>
-    </row>
-    <row r="8" spans="1:35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="10"/>
-      <c r="T8" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI8" s="11"/>
-    </row>
-    <row r="9" spans="1:35">
-      <c r="A9" s="10"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI9" s="11"/>
-    </row>
-    <row r="10" spans="1:35">
-      <c r="A10" s="10"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI10" s="11"/>
-    </row>
-    <row r="11" spans="1:35">
-      <c r="P11" s="11"/>
-      <c r="R11" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="AI11" s="11"/>
-    </row>
-    <row r="12" spans="1:35">
-      <c r="P12" s="11"/>
-      <c r="R12" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI12" s="11"/>
-    </row>
-    <row r="13" spans="1:35">
-      <c r="A13" s="10"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI13" s="11"/>
-    </row>
-    <row r="14" spans="1:35">
-      <c r="A14" s="10"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="10"/>
-      <c r="AI14" s="11"/>
-    </row>
-    <row r="15" spans="1:35">
-      <c r="A15" s="10"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="10"/>
-      <c r="AI15" s="11"/>
-    </row>
-    <row r="16" spans="1:35">
-      <c r="A16" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AI16" s="11"/>
-    </row>
-    <row r="17" spans="1:35">
-      <c r="A17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AI17" s="11"/>
-    </row>
-    <row r="18" spans="1:35">
-      <c r="A18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="R18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AI18" s="11"/>
-    </row>
-    <row r="19" spans="1:35">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
-      <c r="AI19" s="11"/>
-    </row>
-    <row r="20" spans="1:35">
-      <c r="A20" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI20" s="11"/>
-    </row>
-    <row r="21" spans="1:35">
-      <c r="A21" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI21" s="11"/>
-    </row>
-    <row r="22" spans="1:35">
-      <c r="A22" s="10"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="10"/>
-      <c r="AI22" s="11"/>
-    </row>
-    <row r="23" spans="1:35">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="13"/>
-      <c r="AB23" s="13"/>
-      <c r="AC23" s="13"/>
-      <c r="AD23" s="13"/>
-      <c r="AE23" s="13"/>
-      <c r="AF23" s="13"/>
-      <c r="AG23" s="13"/>
-      <c r="AH23" s="13"/>
-      <c r="AI23" s="14"/>
-    </row>
-    <row r="24" spans="1:35">
-      <c r="A24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="8"/>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="8"/>
-      <c r="AF24" s="8"/>
-      <c r="AG24" s="8"/>
-      <c r="AH24" s="8"/>
-      <c r="AI24" s="9"/>
-    </row>
-    <row r="25" spans="1:35">
-      <c r="A25" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI25" s="11"/>
-    </row>
-    <row r="26" spans="1:35">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="13"/>
-      <c r="AG26" s="13"/>
-      <c r="AH26" s="13"/>
-      <c r="AI26" s="14"/>
-    </row>
-    <row r="29" spans="1:35">
-      <c r="Q29" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:35">
-      <c r="Q30" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35">
-      <c r="R31" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="35" spans="17:18">
-      <c r="Q35" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="17:18">
-      <c r="R36" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="17:18">
-      <c r="R37" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="52" spans="17:17">
-      <c r="Q52" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="17:17">
-      <c r="Q63" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-  </sheetData>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0CD117-9164-4B42-8B44-5B255580D7A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264C402C-30BF-413A-B2A5-65201BF6F05B}">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1">
-      <c r="A1" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5394D207-6464-436E-ADE4-2A4026304978}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
@@ -8547,7 +7124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C229AB-5092-49C9-8D15-67A2BD891095}">
   <dimension ref="A1:A77"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
@@ -8672,4 +7249,209 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00EB3AB-A229-45B6-BAF0-CBFC690801AC}">
+  <dimension ref="A1:A72"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="8.75" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="6" customFormat="1">
+      <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="7" customFormat="1">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" s="7" customFormat="1">
+      <c r="A22" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" s="7" customFormat="1">
+      <c r="A37" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" s="7" customFormat="1">
+      <c r="A60" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAC2290-1DFD-477A-8815-88C491123CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987D3929-5B4C-4B3A-B1E5-97CC6D8C1CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="6" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="6" r:id="rId1"/>
@@ -19,11 +19,7 @@
     <sheet name="Docker" sheetId="11" r:id="rId4"/>
     <sheet name="python" sheetId="12" r:id="rId5"/>
     <sheet name="MARIADB" sheetId="13" r:id="rId6"/>
-    <sheet name="パスの指定" sheetId="1" r:id="rId7"/>
-    <sheet name="ディスク使用について" sheetId="2" r:id="rId8"/>
-    <sheet name="capter5" sheetId="3" r:id="rId9"/>
-    <sheet name="chapter6" sheetId="4" r:id="rId10"/>
-    <sheet name="Imageの出力_取込" sheetId="5" r:id="rId11"/>
+    <sheet name="ログインプロセス" sheetId="14" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,565 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="278">
-  <si>
-    <t>Docker Image ディスク使用量とコンテンツサイズについて</t>
-    <rPh sb="17" eb="20">
-      <t>シヨウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>DISK USAGEを抑えるためのポイント</t>
-  </si>
-  <si>
-    <t>もしディスク容量が圧迫されている場合は、以下のコマンドが役立ちます。</t>
-  </si>
-  <si>
-    <r>
-      <t>1. 使っていないデータの掃除</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <t>Bash</t>
-  </si>
-  <si>
-    <t>docker image prune</t>
-  </si>
-  <si>
-    <t>タグのない古いイメージ（dangling images）を削除します。</t>
-  </si>
-  <si>
-    <r>
-      <t>2. システム全体のクリーンアップ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <t>docker system prune</t>
-  </si>
-  <si>
-    <t>停止中のコンテナーや、使用されていないネットワーク、イメージを一括削除します。</t>
-  </si>
-  <si>
-    <r>
-      <t>3. より詳細な分析</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: 画像のリストは </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>docker system df -v</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 等で確認されているかと思いますが、以下のコマンドで各レイヤーごとのサイズを追跡できます。</t>
-    </r>
-  </si>
-  <si>
-    <t>docker history [イメージID]</t>
-  </si>
-  <si>
-    <t>コマンド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>##CHAPTER-5</t>
-  </si>
-  <si>
-    <t>#SECTION-2</t>
-  </si>
-  <si>
-    <t>#ネットワーク作成</t>
-  </si>
-  <si>
-    <t>docker network create wordpress000net1</t>
-  </si>
-  <si>
-    <t>#mysqlのイメージ/コンテナ作成</t>
-  </si>
-  <si>
-    <t>docker run --name mysql000ex11 -dit --net=wordpress000net1 -e MYSQL_ROOT_PASSWORD=myrootpass -e MYSQL_DATABASE=wordpress000db -e MYSQL_USER=wordpress000kun -e MYSQL_PASSWORD=wkunpass mysql:5.7 --character-set-server=utf8mb4 --collation-server=utf8mb4_unicode_ci</t>
-  </si>
-  <si>
-    <t>#wordpressのイメージ/コンテナ作成</t>
-  </si>
-  <si>
-    <t>docker run --name wordpress000ex12 -dit --net=wordpress000net1 -p 8085:80 -e WORDPRESS_DB_HOST=mysql000ex11 -e WORDPRESS_DB_NAME=wordpress000db -e WORDPRESS_DB_USER=wordpress000kun -e WORDPRESS_DB_PASSWORD=wkunpass wordpress</t>
-  </si>
-  <si>
-    <t>#ブラウザ確認</t>
-  </si>
-  <si>
-    <t>http://localhost:8085/</t>
-  </si>
-  <si>
-    <t>実行しているコンテナのログ（実行状況）を確認</t>
-    <rPh sb="0" eb="2">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>ジッコウジョウキョウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker logs コンテナ名</t>
-    <rPh sb="16" eb="17">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>##SECTION-4</t>
-  </si>
-  <si>
-    <t>docker network create redmine000net2</t>
-  </si>
-  <si>
-    <t>#mysqlコンテナの作成・起動</t>
-  </si>
-  <si>
-    <t>docker run --name mysql000ex13 -dit --net=redmine000net2 -e MYSQL_ROOT_PASSWORD=myrootpass -e MYSQL_DATABASE=redmine000db -e MYSQL_USER=redmine000kun -e MYSQL_PASSWORD=rkunpass mysql:5.7</t>
-  </si>
-  <si>
-    <t>## --character-set-server=utf8mb4 --collation-server=utf8mb4_unicode_ci --default-authentication-plugin=mysql_native_password</t>
-  </si>
-  <si>
-    <t>#Readmeコンテナの作成・起動</t>
-  </si>
-  <si>
-    <t>docker run -dit --name redmine000ex14  --network redmine000net2 -p 8086:3000 -e REDMINE_DB_MYSQL=mysql000ex13 -e REDMINE_DB_DATABASE=redmine000db -e REDMINE_DB_USERNAME=root -e REDMINE_DB_PASSWORD=myrootpass redmine</t>
-  </si>
-  <si>
-    <t>http://localhost:8086/</t>
-  </si>
-  <si>
-    <t>CHAPTER 5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>補足</t>
-    <rPh sb="0" eb="2">
-      <t>ホソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　REDMINEは初期実行時、新規で複数テーブルを自動作成する処理がある。</t>
-    <rPh sb="9" eb="14">
-      <t>ショキジッコウジ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　処理に数分かかるため、docker logs でINFO -- : Listening on http://0.0.0.0:3000　の表記が出るまで待機しなくてはならない。</t>
-    <rPh sb="1" eb="3">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>スウフン</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>デ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>タイキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　それまでの間はブラウザでアクセスしてもエラー扱いになる。決してsqlのログインエラーではない。そのため、rootでログインしなくても大丈夫である想定。</t>
-    <rPh sb="6" eb="7">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>アツカ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ケッ</t>
-    </rPh>
-    <rPh sb="67" eb="70">
-      <t>ダイジョウブ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ソウテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker network create redmine000net3</t>
-  </si>
-  <si>
-    <t>#MariaDB コンテナ作成・実行</t>
-  </si>
-  <si>
-    <t>docker run --name mariadb000ex15 -dit --net=redmine000net3 -e MYSQL_ROOT_PASSWORD=mariarootpass -e MYSQL_DATABASE=redmine000db -e MYSQL_USER=redmine000kun -e MYSQL_PASSWORD=rkunpass mariadb --character-set-server=utf8mb4 --collation-server=utf8mb4_unicode_ci --default-authentication-plugin=mysql_native_password</t>
-  </si>
-  <si>
-    <t>docker run -dit --name redmine000ex16  --network redmine000net3 -p 8087:3000 -e REDMINE_DB_MYSQL=mariadb000ex15 -e REDMINE_DB_DATABASE=redmine000db -e REDMINE_DB_USERNAME=redmine000kun -e REDMINE_DB_PASSWORD=rkunpass redmine</t>
-  </si>
-  <si>
-    <t>http://localhost:8087/</t>
-  </si>
-  <si>
-    <t>MariaDB コマンド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#Apatchコンテナ作成・起動</t>
-    <rPh sb="11" eb="13">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#ブラウザ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>http://localhost:8089/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#コピー元のパス</t>
-    <rPh sb="4" eb="5">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"D:\www\index.html"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker run --name apache000ex19 -d -p 8089:80 httpd</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>cd D:/www</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>※コピー元のディレクトリに事前移動すると、ファイルの指定が相対パスで済む</t>
-    <rPh sb="4" eb="5">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ソウタイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker cp index.html apache000ex19:/usr/local/apache2/htdocs/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker cp D:/www/index.html apacheoooex19:/usr/local/apache2/htdocs/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#ローカルの相対パスを使う方法</t>
-    <rPh sb="6" eb="8">
-      <t>ソウタイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エラーの対応</t>
-    <rPh sb="4" eb="6">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◆Docker側のパスを間違えた時のエラー</t>
-    <rPh sb="7" eb="8">
-      <t>ガワ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>トキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◆対応方法</t>
-    <rPh sb="1" eb="3">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Docker desktop からコンテナ名を押下、Filesを選択するとフォルダ構成を確認できる。</t>
-    <rPh sb="21" eb="22">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確認した構成に合わせてコピー元（先）を指定する</t>
-    <rPh sb="0" eb="2">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◆ローカルの参照パス表記を間違えた場合</t>
-    <rPh sb="6" eb="8">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◆コンテナ名を間違えた場合</t>
-    <rPh sb="5" eb="6">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OSのディレクトリにバインドマウント</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#マウント</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◆マウントエラーを起こした場合</t>
-    <rPh sb="9" eb="10">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker run --name apa000ex20 -d -p 8090:80 -v D:\www:/usr/local/apache2/htdocs httpd</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Imageの出力</t>
-    <rPh sb="6" eb="8">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出力したいファイルパスへ移動後、saveコマンドを実行</t>
-    <rPh sb="0" eb="2">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>イドウゴ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker save -o データファイル名（拡張子に.tar を指定する）　Image名</t>
-    <rPh sb="22" eb="23">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="24" eb="27">
-      <t>カクチョウシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：httpd イメージを出力</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出力したイメージの取込</t>
-    <rPh sb="0" eb="2">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>トリコミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>docker load -i ファイル名</t>
-    <rPh sb="19" eb="20">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例：Savedata.tarファイルの取込</t>
-    <rPh sb="0" eb="1">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>トリコミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>取り込むtarファイルのあるパスへ移動後、loadコマンドを実行</t>
-    <rPh sb="0" eb="1">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>イドウゴ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="212">
   <si>
     <t>作業週報アプリ</t>
     <rPh sb="0" eb="4">
@@ -2039,6 +1477,41 @@
   </si>
   <si>
     <t>AUTO_INCREMENT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>docker compose up -d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PR_LOGIN_CHECK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインプロセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード再設定</t>
+    <rPh sb="5" eb="8">
+      <t>サイセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PR_PASS_RESET</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Y</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2046,7 +1519,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2071,30 +1544,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13.5"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Meiryo UI"/>
@@ -2111,7 +1560,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2142,6 +1591,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2156,27 +1611,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2185,7 +1628,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2197,7 +1640,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2224,14 +1676,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>258120</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>105720</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>133397</xdr:rowOff>
+      <xdr:rowOff>19096</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2246,16 +1698,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="39657" t="2856" b="1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3800475"/>
-          <a:ext cx="6773220" cy="333422"/>
+          <a:off x="0" y="3695699"/>
+          <a:ext cx="4087170" cy="323897"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3690,685 +3143,4294 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="フローチャート: 処理 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F220D22-BC54-7134-8653-9F4D15B69DF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="708933" y="727982"/>
+          <a:ext cx="1570264" cy="959303"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ログイン処理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワード</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>175532</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>14968</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>413656</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>240847</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="フローチャート: データ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D82B15E5-A04D-D23A-7BAD-3846DF4A7FC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2216603" y="1239611"/>
+          <a:ext cx="1598839" cy="715736"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>User_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Password</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>17690</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>272142</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="フローチャート: 判断 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3808204-4085-252F-BD32-39C76AF33E6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2058761" y="2354036"/>
+          <a:ext cx="2295524" cy="1224643"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>User_id</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>未登録</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>231322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>530679</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>136073</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="フローチャート: 処理 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30DEF454-A525-683D-7640-A3DADB39CF7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2422072" y="3905251"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>が正しくありません</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>227920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>454477</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>14968</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="コネクタ: カギ線 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E24EB49-B910-03B0-1958-74C3D5E2EDB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2279197" y="1207634"/>
+          <a:ext cx="896709" cy="276905"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>134711</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>240846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485095</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="コネクタ: カギ線 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34F6657D-CF04-499D-8CF6-7D562647A357}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="4" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2831987" y="1979499"/>
+          <a:ext cx="398689" cy="350384"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485094</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>115661</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>231322</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="コネクタ: カギ線 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D1324A-C5A0-4235-8067-FC45368C45B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="3198699" y="3586503"/>
+          <a:ext cx="326572" cy="310924"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>74839</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>329292</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>125186</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="フローチャート: 判断 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CF4DFC0-1756-43A5-AB0A-D61B50DF8016}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4837339" y="2394857"/>
+          <a:ext cx="2295524" cy="1159329"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Password</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>：正</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>有効フラグ：１</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>272142</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542244</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="コネクタ: カギ線 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FEFC0A5-4C2A-4D8C-9B1D-8E67E143464E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="17" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4354285" y="2394857"/>
+          <a:ext cx="1630816" cy="571501"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 14810"/>
+            <a:gd name="adj2" fmla="val 147143"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542244</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>125185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>50348</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>43543</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="コネクタ: カギ線 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F533AF8E-97A9-4A43-827B-9C5D86E91FC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="17" idx="2"/>
+          <a:endCxn id="25" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="5875224" y="3664062"/>
+          <a:ext cx="408215" cy="188461"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>315687</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>43544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>465366</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>193223</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="フローチャート: 処理 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37972674-D495-405D-9ED2-5596E26CA7EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5078187" y="3962401"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ログインに成功しました</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>129267</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>383720</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>138793</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="フローチャート: 判断 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2A93821-0408-45D8-BF82-521D9B61A485}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7613196" y="2653393"/>
+          <a:ext cx="2295524" cy="1159329"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Password</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>：〇</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>有効フラグ：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>329292</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>374555</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>57424</xdr:rowOff>
+      <xdr:colOff>596672</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>35380</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="コネクタ: カギ線 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78988A25-4E1B-F347-3F5C-B390B4118DF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{149DC178-3B8B-48BE-A1AD-E31FF3CE1DE4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="32" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7132863" y="2653393"/>
+          <a:ext cx="1628095" cy="566058"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 14751"/>
+            <a:gd name="adj2" fmla="val 142788"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>118382</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>206828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>372834</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>141514</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="フローチャート: 判断 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D8B4965-FCE3-4969-87B0-AC133C166EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8421275" cy="1962424"/>
+          <a:off x="10323739" y="2656114"/>
+          <a:ext cx="2295524" cy="1159329"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartDecision">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Password</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>：誤</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>有効フラグ：１</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>234044</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>383723</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="フローチャート: 処理 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916D5DA1-0F63-4C74-9E36-DA9C262E4583}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7717973" y="4275365"/>
+          <a:ext cx="2190750" cy="884464"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザは無効です。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>383720</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>206828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>585787</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>48987</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="コネクタ: カギ線 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5A78E93-24B1-4FA1-9551-317485726406}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="32" idx="3"/>
+          <a:endCxn id="37" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9908720" y="2656114"/>
+          <a:ext cx="1562781" cy="576944"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 13278"/>
+            <a:gd name="adj2" fmla="val 140094"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>596673</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>138792</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>174502</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>86083</xdr:rowOff>
+      <xdr:colOff>649063</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>111578</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="コネクタ: カギ線 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA7EAB94-DFBE-7512-AD32-A46A32F8F17F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{977A0BC7-0498-4AE2-B2F4-18755F5D51F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="32" idx="2"/>
+          <a:endCxn id="38" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="8555832" y="4017848"/>
+          <a:ext cx="462643" cy="52390"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>386444</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>100693</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>536122</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="フローチャート: 処理 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BB466B0-B6B6-4C75-A67A-5C82663779CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1828800"/>
-          <a:ext cx="8221222" cy="2562583"/>
+          <a:off x="10591801" y="4264479"/>
+          <a:ext cx="2190750" cy="884464"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワードがただしくありません。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>198120</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>585786</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>141514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>121104</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>100693</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="コネクタ: カギ線 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E57D2B8-3971-42CE-B2CF-5077302C071F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="37" idx="2"/>
+          <a:endCxn id="46" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="11354820" y="3932123"/>
+          <a:ext cx="449036" cy="215675"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>372834</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>51707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>570141</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="コネクタ: カギ線 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC51326D-F1DD-4CF5-8C34-DB5D0B0F7434}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="37" idx="3"/>
+          <a:endCxn id="52" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12619263" y="3480707"/>
+          <a:ext cx="1558021" cy="1042308"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>155123</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>304802</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="フローチャート: 処理 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6FABF18-7316-415F-AD54-EC46E5D6BFDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13081909" y="4523015"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ログインに失敗しました。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>447674</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14969</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>340178</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>240849</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="フローチャート: データ 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFDA3D26-2A16-4837-95A8-165CC45284CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1128031" y="6872969"/>
+          <a:ext cx="1933576" cy="715737"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：質問</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>53749</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>121106</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14969</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="コネクタ: カギ線 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13DE930D-DDF8-4139-90E4-82A31B80CB4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="46" idx="2"/>
+          <a:endCxn id="55" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="6151450" y="1337242"/>
+          <a:ext cx="1479097" cy="9592357"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>503465</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>639536</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="フローチャート: 処理 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B696EB-5AD9-4357-B783-52607137F0DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1183822" y="7960179"/>
+          <a:ext cx="2177143" cy="993321"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>再設定依頼</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>解答</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>176893</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="フローチャート: データ 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940BBBF7-3BAA-4E47-AD44-ED8A7E065231}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2857500" y="8694964"/>
+          <a:ext cx="3442607" cy="1877786"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>User_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>new_Password</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>null</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>update_user</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>user_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>reset_fg</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>true</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>question:null</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>answer</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>question__update_fg:false</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>408216</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>167367</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>204108</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>136070</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="フローチャート: 判断 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C85E9C65-7BB1-4E8B-878C-B2CB02AF47B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9933216" y="13883367"/>
+          <a:ext cx="2517321" cy="1193346"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>リセット：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>540747</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>240848</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>231323</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="コネクタ: カギ線 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5BB6EA3-B77C-41F4-ADBB-40319477C64B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="55" idx="3"/>
+          <a:endCxn id="62" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="1901191" y="7588975"/>
+          <a:ext cx="371473" cy="370933"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>639536</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>129269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>496661</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="72" name="コネクタ: カギ線 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE77D17-BB3B-47ED-896B-FE6E6E0E2ADF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="62" idx="3"/>
+          <a:endCxn id="64" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3360965" y="8456840"/>
+          <a:ext cx="1217839" cy="238124"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>104778</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>166008</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="79" name="コネクタ: カギ線 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77940D3-231A-48AF-A5A2-94C4CFF10742}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="64" idx="3"/>
+          <a:endCxn id="88" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3535818" y="11223853"/>
+          <a:ext cx="1349829" cy="47623"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>585108</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>13606</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="83" name="フローチャート: 処理 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B487559-FB51-472A-91D3-0D5C8DDABB9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10110108" y="17893392"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>同じパスワードです</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>319769</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>223157</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>325213</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>13606</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="84" name="コネクタ: カギ線 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AEECB5A-312B-4198-9F98-6B148396B5B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="169" idx="2"/>
+          <a:endCxn id="83" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="10823123" y="17505588"/>
+          <a:ext cx="770164" cy="5444"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>206830</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>166008</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2723</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>125186</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="88" name="フローチャート: 判断 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91428BA0-0F70-443A-9D1A-20DE680F28D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2928259" y="11922579"/>
+          <a:ext cx="2517321" cy="1183821"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>未登録ユーザ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>246290</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>89807</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>306163</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>167366</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="89" name="コネクタ: カギ線 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{315EFCBA-5733-4C8D-A73A-0E61ADE41C2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="103" idx="2"/>
+          <a:endCxn id="65" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="10755768" y="13447257"/>
+          <a:ext cx="812345" cy="59873"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>29935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2722</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>179614</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="93" name="フローチャート: 処理 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21AFD3D9-2896-49E7-8084-CAA89A691D2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3254829" y="13745935"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>が正しくありません</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>104778</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>125185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>268062</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>29934</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="94" name="コネクタ: カギ線 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{181CFF40-0D39-4492-BE78-C917A0435CC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="88" idx="2"/>
+          <a:endCxn id="93" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="3948795" y="13344525"/>
+          <a:ext cx="639535" cy="163284"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>590551</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>168729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>386443</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>127907</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="97" name="フローチャート: 判断 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71D509BB-46DD-4FC7-8D65-A3242F181A67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6713765" y="11925300"/>
+          <a:ext cx="2517321" cy="1183821"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>リセット：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>質問更新：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2723</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>168729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>488497</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>23133</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="98" name="コネクタ: カギ線 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5668D11B-65CC-41AB-9D9A-D45B435A84EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="88" idx="3"/>
+          <a:endCxn id="97" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5445580" y="11925300"/>
+          <a:ext cx="2526846" cy="589190"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 25094"/>
+            <a:gd name="adj2" fmla="val 139261"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>481694</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>209551</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>317397</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>133502</xdr:rowOff>
+      <xdr:colOff>503465</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="102" name="フローチャート: 処理 101">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE3D338D-99B1-01B0-DF96-C09EC16B042C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E637D4D3-41D8-4CCB-8A5F-5EC54F2A7643}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="426720"/>
-          <a:ext cx="8364117" cy="1086002"/>
+          <a:off x="7285265" y="13680622"/>
+          <a:ext cx="1382486" cy="429986"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>質問の更新</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>348343</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>130630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>317397</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>115034</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>144235</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>89808</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="103" name="フローチャート: 判断 102">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B05BB137-4FAE-DB9F-850D-D80391503233}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A77009A-6D17-4304-968F-FC73FFBEC289}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="4000500"/>
-          <a:ext cx="8364117" cy="5258534"/>
+          <a:off x="9873343" y="11887201"/>
+          <a:ext cx="2517321" cy="1183821"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartDecision">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>質問更新：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>488498</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>127906</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>117344</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>124082</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>492580</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="104" name="コネクタ: カギ線 103">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D4C0C1-AB60-3EAB-C028-12FCBA0A22DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{922D82BE-CA7C-4BD0-A6CF-CDBD91FB2E0D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="97" idx="2"/>
+          <a:endCxn id="102" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="7688717" y="13392830"/>
+          <a:ext cx="571501" cy="4082"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>386443</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>130630</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>246290</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>25854</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="107" name="コネクタ: カギ線 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8011A8A5-2E3B-459A-9A9C-A2993AEC200B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="97" idx="3"/>
+          <a:endCxn id="103" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="9231086" y="11887201"/>
+          <a:ext cx="1900918" cy="630010"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 16893"/>
+            <a:gd name="adj2" fmla="val 136285"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>176892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>204106</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="111" name="フローチャート: 処理 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{064DB8FC-2F90-4C03-AECF-1DD00EA111C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="4572000"/>
-          <a:ext cx="8164064" cy="1838582"/>
+          <a:off x="6885214" y="14382749"/>
+          <a:ext cx="2163535" cy="983796"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：セキュリティ質問の更新が完了しました</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>483054</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>94575</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>9606</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>492580</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>176891</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="112" name="コネクタ: カギ線 111">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA9BA65-21FA-44DD-97C7-12332BFEB29E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F100CAE-4073-49E6-9BF9-86B98699DEF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="102" idx="2"/>
+          <a:endCxn id="111" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="7835675" y="14241915"/>
+          <a:ext cx="272141" cy="9526"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>375558</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>225879</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>397330</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166008</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="115" name="フローチャート: 処理 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31C23DB-CF7A-4FBE-A12B-4BF7A68BA224}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3810000"/>
-          <a:ext cx="8811855" cy="581106"/>
+          <a:off x="15343415" y="15901308"/>
+          <a:ext cx="1382486" cy="429986"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワードのリセット</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>144235</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>232683</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>655320</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>34834</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>5443</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>48987</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="116" name="コネクタ: カギ線 115">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{585C3A3D-C1CC-46E6-A9ED-C962093D208A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82C1C6E4-7193-4993-AE8F-A6FC94A44D56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect t="38737" r="37522"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="103" idx="3"/>
+          <a:endCxn id="150" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5791200"/>
-          <a:ext cx="8079377" cy="2277291"/>
+          <a:off x="12390664" y="12479112"/>
+          <a:ext cx="3943350" cy="551089"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>70756</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>220439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>193220</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>224521</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="119" name="フローチャート: 処理 118">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032B978D-997E-45BA-9944-EC044EE1D4F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17079685" y="15895868"/>
+          <a:ext cx="2163535" cy="983796"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワードの変更が完了しました</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>新しいパスワード：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>PASSWORD</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>386443</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>220439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>472166</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166008</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="120" name="コネクタ: カギ線 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBE8D735-9105-4585-8038-D1F05D79E9B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="115" idx="2"/>
+          <a:endCxn id="119" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="16880342" y="15050183"/>
+          <a:ext cx="435426" cy="2126795"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector5">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -52500"/>
+            <a:gd name="adj2" fmla="val 40819"/>
+            <a:gd name="adj3" fmla="val 152500"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>674914</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>48987</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>16328</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="150" name="フローチャート: 処理 149">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2941BE2D-847C-46D1-A455-FB97F5820ACD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15642771" y="13030201"/>
+          <a:ext cx="1382486" cy="617763"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>不正なパラメータの組み合わせです</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>195940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>359229</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>100691</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="153" name="フローチャート: 処理 152">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA03429-6EC4-434E-A5F9-41AEEEBBBE02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14497050" y="17830797"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワードの更新が完了しました</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>新しいパスワード：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>USERID</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>166008</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>179613</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>642258</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>138791</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="158" name="フローチャート: 判断 157">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A88E7947-A4F0-4F1D-877B-DD403C4BB6BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13092794" y="13895613"/>
+          <a:ext cx="2517321" cy="1183821"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>リセット：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>204108</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>179613</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>63955</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>29254</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="159" name="コネクタ: カギ線 158">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09D44A9D-0D12-4597-B367-9DD23B48BBD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="65" idx="3"/>
+          <a:endCxn id="158" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12450537" y="13895613"/>
+          <a:ext cx="1900918" cy="584427"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 16893"/>
+            <a:gd name="adj2" fmla="val 141211"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>63954</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>138791</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>386443</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>225879</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="164" name="コネクタ: カギ線 163">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B044B6B-50F3-4AEA-9D68-8926BD9F2613}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="158" idx="2"/>
+          <a:endCxn id="115" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="14782119" y="14648769"/>
+          <a:ext cx="821874" cy="1683203"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>427266</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>216719</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>102943</xdr:rowOff>
+      <xdr:colOff>223158</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>223157</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="169" name="フローチャート: 判断 168">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06AAD9CD-6ED2-0E0C-A0BF-4E7A8EC7BBE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F573872-09D5-4C30-975C-0947B84AB749}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="8229600"/>
-          <a:ext cx="12365176" cy="6373114"/>
+          <a:off x="9952266" y="15939407"/>
+          <a:ext cx="2517321" cy="1183821"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="flowChartDecision">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>既存パスと同じ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>185057</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>306163</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>136070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>223334</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>149755</xdr:rowOff>
+      <xdr:colOff>325213</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="170" name="コネクタ: カギ線 169">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC30042-08D7-13F2-C623-3E8B6157A09D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{481E64C1-6BC4-473D-BEFE-645963B09FD6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="65" idx="2"/>
+          <a:endCxn id="169" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="10770055" y="15498535"/>
+          <a:ext cx="862694" cy="19050"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>223158</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>121104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>345621</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>239485</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="177" name="コネクタ: カギ線 176">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3815B8AD-BEFE-47B8-A200-8AC8D81F7403}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="169" idx="3"/>
+          <a:endCxn id="182" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="15272657"/>
-          <a:ext cx="11021963" cy="552527"/>
+          <a:off x="12469587" y="16531318"/>
+          <a:ext cx="802820" cy="1343024"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>334735</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>239485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>356507</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>179614</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="182" name="フローチャート: 処理 181">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC972AE-A9A1-4F5D-B4D0-40FCA09EA3A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12581164" y="17874342"/>
+          <a:ext cx="1382486" cy="429986"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワードの更新</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>345621</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>195940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>658636</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>31383</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>624568</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>179614</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="186" name="コネクタ: カギ線 185">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F468024E-2C83-4ED8-B3C8-3FC0CF821B17}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED009091-47E7-482B-912E-373D6E6E8301}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="182" idx="2"/>
+          <a:endCxn id="153" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="16851086"/>
-          <a:ext cx="10107436" cy="619211"/>
+        <a:xfrm rot="5400000" flipH="1" flipV="1">
+          <a:off x="14195650" y="16907554"/>
+          <a:ext cx="473531" cy="2320018"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+        <a:prstGeom prst="bentConnector5">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -48276"/>
+            <a:gd name="adj2" fmla="val 41290"/>
+            <a:gd name="adj3" fmla="val 148276"/>
+          </a:avLst>
         </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>642258</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>350087</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>88540</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>5443</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>36738</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="254" name="コネクタ: カギ線 253">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DCB022C-F528-429A-8A2D-8C68EFDB5C35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E44AF79-81ED-4CFA-A284-F7972319437A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="158" idx="3"/>
+          <a:endCxn id="150" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="19986171"/>
-          <a:ext cx="12498544" cy="676369"/>
+        <a:xfrm flipV="1">
+          <a:off x="15610115" y="13647964"/>
+          <a:ext cx="723899" cy="839560"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="bentConnector2">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>205174</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>28760</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D174229F-7ED7-D0F0-99AC-0F1164EC8C09}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1181100"/>
-          <a:ext cx="9593014" cy="1324160"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>494681</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>266</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2099FE4A-DA4F-8FB9-65D5-34B6144871F5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="2667000"/>
-          <a:ext cx="9211961" cy="1905266"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>284633</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>152501</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44DEFD08-285E-B3B1-F239-5EAE51987D44}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5715000"/>
-          <a:ext cx="5649113" cy="724001"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>622708</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>29137</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FDD82FC-6495-BAD8-E25F-044BA4A5705A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6667500"/>
-          <a:ext cx="12022228" cy="4029637"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4672,157 +7734,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D024D6-0C31-4325-942C-9DF20C863483}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="7" customFormat="1">
-      <c r="A2" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -4831,194 +7893,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951AFAFC-64BB-48A0-B0C5-F9BF0356E726}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1"/>
-    <row r="2" spans="1:3" s="7" customFormat="1">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="7" customFormat="1">
-      <c r="A17" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" s="7" customFormat="1">
-      <c r="A95" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A15534C-900B-4E1C-9ED3-A15604A7DB2E}">
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" s="6" customFormat="1">
-      <c r="A26" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB8AA92-C104-4402-9D79-D3850C7E3800}">
   <dimension ref="A1:I138"/>
-  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.75" style="1"/>
     <col min="2" max="2" width="3.875" style="1" customWidth="1"/>
@@ -5031,1561 +7909,1561 @@
     <col min="9" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1">
-      <c r="A1" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="I5" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C10" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="C7" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="C8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="C9" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="C10" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="C11" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="C12" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="C13" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="C15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="C16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C17" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C18" s="1" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C19" s="1" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C20" s="1" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C21" s="1" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C22" s="1" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C23" s="1" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C24" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C25" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C26" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C27" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="1">
         <v>3</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="C30" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
+      <c r="C29" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C32" s="1" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C33" s="1" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C34" s="1" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C35" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C36" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C37" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C38" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B41" s="1">
         <v>4</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="C42" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G42" s="7" t="s">
+      <c r="C41" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C43" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C44" s="1" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C45" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C46" s="1" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C47" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C48" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C49" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C50" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B52" s="1">
         <v>5</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="2:8">
-      <c r="C53" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
+      <c r="C52" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C54" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C55" s="1" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C56" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C57" s="1" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C58" s="1" t="s">
-        <v>220</v>
+        <v>146</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C59" s="1" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C60" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C61" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C62" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C63" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B65" s="1">
         <v>6</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="C66" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
+      <c r="C65" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C66" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C67" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C68" s="1" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C69" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C70" s="1" t="s">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C71" s="1" t="s">
-        <v>218</v>
+        <v>144</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C72" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C73" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C74" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C75" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B77" s="1">
         <v>7</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-    </row>
-    <row r="78" spans="2:8">
-      <c r="C78" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8">
+      <c r="C77" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C78" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C79" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C80" s="1" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C81" s="1" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C82" s="1" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C83" s="1" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C84" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C85" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C86" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C87" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B89" s="1">
         <v>8</v>
       </c>
-      <c r="C89" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
-    </row>
-    <row r="90" spans="2:8">
-      <c r="C90" s="7" t="s">
+      <c r="C89" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C90" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C91" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D91" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H91" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E90" s="7" t="s">
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C92" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C93" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H93" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F90" s="7" t="s">
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C94" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C95" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G90" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8">
-      <c r="C91" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8">
-      <c r="C92" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8">
-      <c r="C93" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="C94" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8">
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C96" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8">
-      <c r="C96" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8">
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C97" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B100" s="1">
         <v>9</v>
       </c>
-      <c r="C100" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-    </row>
-    <row r="101" spans="2:8">
-      <c r="C101" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="102" spans="2:8">
+      <c r="C100" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C102" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C103" s="1" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="104" spans="2:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C104" s="1" t="s">
-        <v>235</v>
+        <v>161</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="105" spans="2:8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C105" s="1" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C106" s="1" t="s">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C107" s="1" t="s">
-        <v>237</v>
+        <v>163</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C108" s="1" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C109" s="1" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C110" s="1" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="111" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C111" s="1" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C112" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="113" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C113" s="1" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C114" s="1" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C115" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="117" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B117" s="1">
         <v>10</v>
       </c>
-      <c r="C117" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
-    </row>
-    <row r="118" spans="2:8">
-      <c r="C118" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="119" spans="2:8">
+      <c r="C117" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C118" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C119" s="1" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C120" s="1" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C121" s="1" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C122" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C123" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C124" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C125" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C126" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C127" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C128" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8">
-      <c r="C122" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="123" spans="2:8">
-      <c r="C123" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="124" spans="2:8">
-      <c r="C124" s="1" t="s">
+      <c r="D128" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C129" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="125" spans="2:8">
-      <c r="C125" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="126" spans="2:8">
-      <c r="C126" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="127" spans="2:8">
-      <c r="C127" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="128" spans="2:8">
-      <c r="C128" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8">
-      <c r="C129" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="D129" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="131" spans="2:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B131" s="1">
         <v>11</v>
       </c>
-      <c r="C131" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="D131" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
-    </row>
-    <row r="132" spans="2:8">
-      <c r="C132" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E132" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="133" spans="2:8">
+      <c r="C131" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C132" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C133" s="1" t="s">
-        <v>275</v>
+        <v>201</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="134" spans="2:8">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C134" s="1" t="s">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>274</v>
+        <v>200</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="135" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C135" s="1" t="s">
-        <v>270</v>
+        <v>196</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C136" s="1" t="s">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C137" s="1" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="138" spans="2:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C138" s="1" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>276</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6598,7 +9476,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71AA243-8FD7-4F02-9A26-7C24488241D4}">
   <dimension ref="B2:H36"/>
-  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="4.75" style="1"/>
     <col min="3" max="3" width="17.375" style="1" bestFit="1" customWidth="1"/>
@@ -6610,321 +9488,321 @@
     <col min="9" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="C3" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="31.5">
+      <c r="C2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="31.5" x14ac:dyDescent="0.4">
       <c r="C4" s="1" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
+        <v>128</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C5" s="1" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="D6" s="1" t="s">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C7" s="1" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="D8" s="1" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C9" s="1" t="s">
-        <v>222</v>
+        <v>148</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="D10" s="1" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C11" s="1" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="D12" s="1" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="1">
         <v>2</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="C20" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
+      <c r="C19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C21" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C22" s="1" t="s">
-        <v>240</v>
+        <v>166</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>239</v>
+        <v>165</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="D23" s="1" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="C27" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="C28" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="2:8">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="C28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C29" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="1" t="s">
-        <v>241</v>
+        <v>167</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="1" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8">
-      <c r="C34" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="3:8">
-      <c r="C35" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="3:8" ht="31.5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C34" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="3:8" ht="31.5" x14ac:dyDescent="0.4">
       <c r="C36" s="1" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>208</v>
+        <v>128</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -6935,126 +9813,131 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501F0FCE-E583-4CC3-AACB-28BDBA1C8EE7}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultColWidth="4.75" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="4.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1">
-      <c r="A1" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" s="7" customFormat="1">
-      <c r="A18" s="7" t="s">
-        <v>263</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -7067,27 +9950,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFBF6CF-7FC3-426B-AFBE-A22ED319995D}">
   <dimension ref="A1:E83"/>
-  <sheetFormatPr defaultColWidth="4.625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="4.625" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="4.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" ht="18.75">
-      <c r="A1" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B83" s="1" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -7103,7 +9986,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0CD117-9164-4B42-8B44-5B255580D7A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7111,342 +9994,83 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5394D207-6464-436E-ADE4-2A4026304978}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C229AB-5092-49C9-8D15-67A2BD891095}">
-  <dimension ref="A1:A77"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C563F4-B99E-41EF-AEA8-184ECBADBB4E}">
+  <dimension ref="A1:T55"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="22.5">
-      <c r="A51" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="18.75">
-      <c r="A52"/>
-    </row>
-    <row r="53" spans="1:1" ht="18.75">
-      <c r="A53" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="18.75">
-      <c r="A54" s="3"/>
-    </row>
-    <row r="55" spans="1:1" ht="18.75">
-      <c r="A55" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="18.75">
-      <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:1" ht="18.75">
-      <c r="A57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="18.75">
-      <c r="A58"/>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="18.75">
-      <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:1" ht="18.75">
-      <c r="A61" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="18.75">
-      <c r="A62" s="3"/>
-    </row>
-    <row r="63" spans="1:1" ht="18.75">
-      <c r="A63" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="18.75">
-      <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1" ht="18.75">
-      <c r="A65" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="18.75">
-      <c r="A66"/>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="18.75">
-      <c r="A68" s="3"/>
-    </row>
-    <row r="69" spans="1:1" ht="18.75">
-      <c r="A69" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="18.75">
-      <c r="A70" s="3"/>
-    </row>
-    <row r="71" spans="1:1" ht="18.75">
-      <c r="A71" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="18.75">
-      <c r="A72" s="3"/>
-    </row>
-    <row r="73" spans="1:1" ht="18.75">
-      <c r="A73" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" ht="18.75">
-      <c r="A74"/>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="18.75">
-      <c r="A76"/>
-    </row>
-    <row r="77" spans="1:1" ht="18.75">
-      <c r="A77"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00EB3AB-A229-45B6-BAF0-CBFC690801AC}">
-  <dimension ref="A1:A72"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75"/>
-  <cols>
-    <col min="1" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1">
-      <c r="A1" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="7" customFormat="1">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" s="7" customFormat="1">
-      <c r="A22" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" s="7" customFormat="1">
-      <c r="A37" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" s="7" customFormat="1">
-      <c r="A60" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="1" t="s">
-        <v>42</v>
+    <row r="1" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B11" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="G13" t="s">
+        <v>210</v>
+      </c>
+      <c r="K13" t="s">
+        <v>210</v>
+      </c>
+      <c r="O13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="T14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="D17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I17" t="s">
+        <v>211</v>
+      </c>
+      <c r="M17" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C46" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" s="10"/>
+    </row>
+    <row r="50" spans="6:14" x14ac:dyDescent="0.4">
+      <c r="N50" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="6:14" x14ac:dyDescent="0.4">
+      <c r="I51" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="6:14" x14ac:dyDescent="0.4">
+      <c r="F55" t="s">
+        <v>211</v>
+      </c>
+      <c r="K55" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987D3929-5B4C-4B3A-B1E5-97CC6D8C1CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75577B4C-8D04-4091-92E2-431E10EF233B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="6" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="7" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="python" sheetId="12" r:id="rId5"/>
     <sheet name="MARIADB" sheetId="13" r:id="rId6"/>
     <sheet name="ログインプロセス" sheetId="14" r:id="rId7"/>
+    <sheet name="ユーザー管理プロセス" sheetId="15" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="215">
   <si>
     <t>作業週報アプリ</t>
     <rPh sb="0" eb="4">
@@ -1512,6 +1513,24 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザ管理プロセス</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー作成</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PR_USER_CREATE</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1598,12 +1617,92 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1615,7 +1714,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1646,10 +1745,40 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7436,6 +7565,304 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>189940</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="フローチャート: 処理 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E21C30FC-C940-4290-9CD6-61C7F9FDD144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="280147" y="672353"/>
+          <a:ext cx="1590675" cy="1109382"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>登録処理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワード未設定の場合、パスワード＝ユーザー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>で作成</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>127346</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>124225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>65712</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19531</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="フローチャート: データ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0C89B94-829D-486F-B1A3-5CA67A6F21DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1808228" y="1401696"/>
+          <a:ext cx="1619249" cy="702129"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>User_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>189940</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>151279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>258453</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>124225</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="コネクタ: カギ線 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E2B54E5-E3B9-453A-B809-F4FA7C91FB00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1870822" y="1227044"/>
+          <a:ext cx="908955" cy="174652"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>216793</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6882</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>37619</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="コネクタ: カギ線 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA421F4-B282-4E8A-87C5-A9EBDE59E363}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2321557" y="2240236"/>
+          <a:ext cx="623207" cy="350384"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
@@ -8375,9 +8802,6 @@
       <c r="E43" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H43" s="1" t="s">
         <v>99</v>
       </c>
@@ -8504,9 +8928,6 @@
       <c r="E54" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H54" s="1" t="s">
         <v>99</v>
       </c>
@@ -8655,9 +9076,6 @@
       <c r="E67" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H67" s="1" t="s">
         <v>99</v>
       </c>
@@ -8795,9 +9213,6 @@
       <c r="E79" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H79" s="1" t="s">
         <v>99</v>
       </c>
@@ -8941,9 +9356,6 @@
       <c r="E91" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H91" s="1" t="s">
         <v>117</v>
       </c>
@@ -8970,9 +9382,6 @@
         <v>39</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F93" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H93" s="1" t="s">
@@ -9062,9 +9471,6 @@
       <c r="E102" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G102" s="1" t="s">
         <v>45</v>
       </c>
@@ -9146,9 +9552,6 @@
       </c>
       <c r="D110" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.4">
@@ -9240,9 +9643,6 @@
         <v>39</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F119" s="1" t="s">
         <v>45</v>
       </c>
       <c r="G119" s="1" t="s">
@@ -9995,83 +10395,1408 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C563F4-B99E-41EF-AEA8-184ECBADBB4E}">
-  <dimension ref="A1:T55"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="11" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="B11" s="10" t="s">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B11" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="10"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="G13" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="14"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="17"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="K13" t="s">
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="O13" t="s">
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="T14" t="s">
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="17"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="D17" t="s">
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="17"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="17"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="17"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="I17" t="s">
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="M17" t="s">
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="17"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="17"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="17"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="17"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B21" s="15"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="17"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="17"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B23" s="15"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="17"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="20"/>
+    </row>
+    <row r="27" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C46" s="10" t="s">
+    <row r="46" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C46" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D46" s="10"/>
-    </row>
-    <row r="50" spans="6:14" x14ac:dyDescent="0.4">
-      <c r="N50" t="s">
+      <c r="D46" s="12"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+      <c r="Q46" s="13"/>
+      <c r="R46" s="13"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="13"/>
+      <c r="U46" s="13"/>
+      <c r="V46" s="13"/>
+      <c r="W46" s="13"/>
+      <c r="X46" s="13"/>
+      <c r="Y46" s="13"/>
+      <c r="Z46" s="13"/>
+      <c r="AA46" s="13"/>
+      <c r="AB46" s="13"/>
+      <c r="AC46" s="14"/>
+    </row>
+    <row r="47" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C47" s="15"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="17"/>
+    </row>
+    <row r="48" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C48" s="15"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="17"/>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C49" s="15"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="16"/>
+      <c r="AB49" s="16"/>
+      <c r="AC49" s="17"/>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C50" s="15"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="51" spans="6:14" x14ac:dyDescent="0.4">
-      <c r="I51" t="s">
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="55" spans="6:14" x14ac:dyDescent="0.4">
-      <c r="F55" t="s">
+      <c r="T50" s="16"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
+      <c r="Z50" s="16"/>
+      <c r="AA50" s="16"/>
+      <c r="AB50" s="16"/>
+      <c r="AC50" s="17"/>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C51" s="15"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
+      <c r="AB51" s="16"/>
+      <c r="AC51" s="17"/>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C52" s="15"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="16"/>
+      <c r="W52" s="16"/>
+      <c r="X52" s="16"/>
+      <c r="Y52" s="16"/>
+      <c r="Z52" s="16"/>
+      <c r="AA52" s="16"/>
+      <c r="AB52" s="16"/>
+      <c r="AC52" s="17"/>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C53" s="15"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="16"/>
+      <c r="R53" s="16"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="17"/>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C54" s="15"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="16"/>
+      <c r="R54" s="16"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="16"/>
+      <c r="U54" s="16"/>
+      <c r="V54" s="16"/>
+      <c r="W54" s="16"/>
+      <c r="X54" s="16"/>
+      <c r="Y54" s="16"/>
+      <c r="Z54" s="16"/>
+      <c r="AA54" s="16"/>
+      <c r="AB54" s="16"/>
+      <c r="AC54" s="17"/>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C55" s="15"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="K55" t="s">
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16" t="s">
         <v>211</v>
       </c>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q55" s="16"/>
+      <c r="R55" s="16"/>
+      <c r="S55" s="16"/>
+      <c r="T55" s="16"/>
+      <c r="U55" s="16"/>
+      <c r="V55" s="16"/>
+      <c r="W55" s="16"/>
+      <c r="X55" s="16"/>
+      <c r="Y55" s="16"/>
+      <c r="Z55" s="16"/>
+      <c r="AA55" s="16"/>
+      <c r="AB55" s="16"/>
+      <c r="AC55" s="17"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C56" s="15"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
+      <c r="R56" s="16"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="16"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="16"/>
+      <c r="X56" s="16"/>
+      <c r="Y56" s="16"/>
+      <c r="Z56" s="16"/>
+      <c r="AA56" s="16"/>
+      <c r="AB56" s="16"/>
+      <c r="AC56" s="17"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C57" s="15"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="16"/>
+      <c r="R57" s="16"/>
+      <c r="S57" s="16"/>
+      <c r="T57" s="16"/>
+      <c r="U57" s="16"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="16"/>
+      <c r="X57" s="16"/>
+      <c r="Y57" s="16"/>
+      <c r="Z57" s="16"/>
+      <c r="AA57" s="16"/>
+      <c r="AB57" s="16"/>
+      <c r="AC57" s="17"/>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C58" s="15"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="16"/>
+      <c r="R58" s="16"/>
+      <c r="S58" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="T58" s="16"/>
+      <c r="U58" s="16"/>
+      <c r="V58" s="16"/>
+      <c r="W58" s="16"/>
+      <c r="X58" s="16"/>
+      <c r="Y58" s="16"/>
+      <c r="Z58" s="16"/>
+      <c r="AA58" s="16"/>
+      <c r="AB58" s="16"/>
+      <c r="AC58" s="17"/>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C59" s="15"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="16"/>
+      <c r="Q59" s="16"/>
+      <c r="R59" s="16"/>
+      <c r="S59" s="16"/>
+      <c r="T59" s="16"/>
+      <c r="U59" s="16"/>
+      <c r="V59" s="16"/>
+      <c r="W59" s="16"/>
+      <c r="X59" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y59" s="16"/>
+      <c r="Z59" s="16"/>
+      <c r="AA59" s="16"/>
+      <c r="AB59" s="16"/>
+      <c r="AC59" s="17"/>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C60" s="15"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="16"/>
+      <c r="V60" s="16"/>
+      <c r="W60" s="16"/>
+      <c r="X60" s="16"/>
+      <c r="Y60" s="16"/>
+      <c r="Z60" s="16"/>
+      <c r="AA60" s="16"/>
+      <c r="AB60" s="16"/>
+      <c r="AC60" s="17"/>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C61" s="15"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16"/>
+      <c r="S61" s="16"/>
+      <c r="T61" s="16"/>
+      <c r="U61" s="16"/>
+      <c r="V61" s="16"/>
+      <c r="W61" s="16"/>
+      <c r="X61" s="16"/>
+      <c r="Y61" s="16"/>
+      <c r="Z61" s="16"/>
+      <c r="AA61" s="16"/>
+      <c r="AB61" s="16"/>
+      <c r="AC61" s="17"/>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C62" s="15"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="16"/>
+      <c r="V62" s="16"/>
+      <c r="W62" s="16"/>
+      <c r="X62" s="16"/>
+      <c r="Y62" s="16"/>
+      <c r="Z62" s="16"/>
+      <c r="AA62" s="16"/>
+      <c r="AB62" s="16"/>
+      <c r="AC62" s="17"/>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C63" s="15"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q63" s="16"/>
+      <c r="R63" s="16"/>
+      <c r="S63" s="16"/>
+      <c r="T63" s="16"/>
+      <c r="U63" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="V63" s="16"/>
+      <c r="W63" s="16"/>
+      <c r="X63" s="16"/>
+      <c r="Y63" s="16"/>
+      <c r="Z63" s="16"/>
+      <c r="AA63" s="16"/>
+      <c r="AB63" s="16"/>
+      <c r="AC63" s="17"/>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C64" s="15"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16"/>
+      <c r="P64" s="16"/>
+      <c r="Q64" s="16"/>
+      <c r="R64" s="16"/>
+      <c r="S64" s="16"/>
+      <c r="T64" s="16"/>
+      <c r="U64" s="16"/>
+      <c r="V64" s="16"/>
+      <c r="W64" s="16"/>
+      <c r="X64" s="16"/>
+      <c r="Y64" s="16"/>
+      <c r="Z64" s="16"/>
+      <c r="AA64" s="16"/>
+      <c r="AB64" s="16"/>
+      <c r="AC64" s="17"/>
+    </row>
+    <row r="65" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C65" s="15"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16"/>
+      <c r="K65" s="16"/>
+      <c r="L65" s="16"/>
+      <c r="M65" s="16"/>
+      <c r="N65" s="16"/>
+      <c r="O65" s="16"/>
+      <c r="P65" s="16"/>
+      <c r="Q65" s="16"/>
+      <c r="R65" s="16"/>
+      <c r="S65" s="16"/>
+      <c r="T65" s="16"/>
+      <c r="U65" s="16"/>
+      <c r="V65" s="16"/>
+      <c r="W65" s="16"/>
+      <c r="X65" s="16"/>
+      <c r="Y65" s="16"/>
+      <c r="Z65" s="16"/>
+      <c r="AA65" s="16"/>
+      <c r="AB65" s="16"/>
+      <c r="AC65" s="17"/>
+    </row>
+    <row r="66" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C66" s="15"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="16"/>
+      <c r="M66" s="16"/>
+      <c r="N66" s="16"/>
+      <c r="O66" s="16"/>
+      <c r="P66" s="16"/>
+      <c r="Q66" s="16"/>
+      <c r="R66" s="16"/>
+      <c r="S66" s="16"/>
+      <c r="T66" s="16"/>
+      <c r="U66" s="16"/>
+      <c r="V66" s="16"/>
+      <c r="W66" s="16"/>
+      <c r="X66" s="16"/>
+      <c r="Y66" s="16"/>
+      <c r="Z66" s="16"/>
+      <c r="AA66" s="16"/>
+      <c r="AB66" s="16"/>
+      <c r="AC66" s="17"/>
+    </row>
+    <row r="67" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C67" s="15"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="16"/>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="16"/>
+      <c r="R67" s="16"/>
+      <c r="S67" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="T67" s="16"/>
+      <c r="U67" s="16"/>
+      <c r="V67" s="16"/>
+      <c r="W67" s="16"/>
+      <c r="X67" s="16"/>
+      <c r="Y67" s="16"/>
+      <c r="Z67" s="16"/>
+      <c r="AA67" s="16"/>
+      <c r="AB67" s="16"/>
+      <c r="AC67" s="17"/>
+    </row>
+    <row r="68" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C68" s="15"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+      <c r="K68" s="16"/>
+      <c r="L68" s="16"/>
+      <c r="M68" s="16"/>
+      <c r="N68" s="16"/>
+      <c r="O68" s="16"/>
+      <c r="P68" s="16"/>
+      <c r="Q68" s="16"/>
+      <c r="R68" s="16"/>
+      <c r="S68" s="16"/>
+      <c r="T68" s="16"/>
+      <c r="U68" s="16"/>
+      <c r="V68" s="16"/>
+      <c r="W68" s="16"/>
+      <c r="X68" s="16"/>
+      <c r="Y68" s="16"/>
+      <c r="Z68" s="16"/>
+      <c r="AA68" s="16"/>
+      <c r="AB68" s="16"/>
+      <c r="AC68" s="17"/>
+    </row>
+    <row r="69" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C69" s="15"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16"/>
+      <c r="V69" s="16"/>
+      <c r="W69" s="16"/>
+      <c r="X69" s="16"/>
+      <c r="Y69" s="16"/>
+      <c r="Z69" s="16"/>
+      <c r="AA69" s="16"/>
+      <c r="AB69" s="16"/>
+      <c r="AC69" s="17"/>
+    </row>
+    <row r="70" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C70" s="15"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+      <c r="N70" s="16"/>
+      <c r="O70" s="16"/>
+      <c r="P70" s="16"/>
+      <c r="Q70" s="16"/>
+      <c r="R70" s="16"/>
+      <c r="S70" s="16"/>
+      <c r="T70" s="16"/>
+      <c r="U70" s="16"/>
+      <c r="V70" s="16"/>
+      <c r="W70" s="16"/>
+      <c r="X70" s="16"/>
+      <c r="Y70" s="16"/>
+      <c r="Z70" s="16"/>
+      <c r="AA70" s="16"/>
+      <c r="AB70" s="16"/>
+      <c r="AC70" s="17"/>
+    </row>
+    <row r="71" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C71" s="15"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+      <c r="O71" s="16"/>
+      <c r="P71" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16"/>
+      <c r="S71" s="16"/>
+      <c r="T71" s="16"/>
+      <c r="U71" s="16"/>
+      <c r="V71" s="16"/>
+      <c r="W71" s="16"/>
+      <c r="X71" s="16"/>
+      <c r="Y71" s="16"/>
+      <c r="Z71" s="16"/>
+      <c r="AA71" s="16"/>
+      <c r="AB71" s="16"/>
+      <c r="AC71" s="17"/>
+    </row>
+    <row r="72" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C72" s="15"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+      <c r="N72" s="16"/>
+      <c r="O72" s="16"/>
+      <c r="P72" s="16"/>
+      <c r="Q72" s="16"/>
+      <c r="R72" s="16"/>
+      <c r="S72" s="16"/>
+      <c r="T72" s="16"/>
+      <c r="U72" s="16"/>
+      <c r="V72" s="16"/>
+      <c r="W72" s="16"/>
+      <c r="X72" s="16"/>
+      <c r="Y72" s="16"/>
+      <c r="Z72" s="16"/>
+      <c r="AA72" s="16"/>
+      <c r="AB72" s="16"/>
+      <c r="AC72" s="17"/>
+    </row>
+    <row r="73" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C73" s="15"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+      <c r="N73" s="16"/>
+      <c r="O73" s="16"/>
+      <c r="P73" s="16"/>
+      <c r="Q73" s="16"/>
+      <c r="R73" s="16"/>
+      <c r="S73" s="16"/>
+      <c r="T73" s="16"/>
+      <c r="U73" s="16"/>
+      <c r="V73" s="16"/>
+      <c r="W73" s="16"/>
+      <c r="X73" s="16"/>
+      <c r="Y73" s="16"/>
+      <c r="Z73" s="16"/>
+      <c r="AA73" s="16"/>
+      <c r="AB73" s="16"/>
+      <c r="AC73" s="17"/>
+    </row>
+    <row r="74" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C74" s="15"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+      <c r="N74" s="16"/>
+      <c r="O74" s="16"/>
+      <c r="P74" s="16"/>
+      <c r="Q74" s="16"/>
+      <c r="R74" s="16"/>
+      <c r="S74" s="16"/>
+      <c r="T74" s="16"/>
+      <c r="U74" s="16"/>
+      <c r="V74" s="16"/>
+      <c r="W74" s="16"/>
+      <c r="X74" s="16"/>
+      <c r="Y74" s="16"/>
+      <c r="Z74" s="16"/>
+      <c r="AA74" s="16"/>
+      <c r="AB74" s="16"/>
+      <c r="AC74" s="17"/>
+    </row>
+    <row r="75" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C75" s="15"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
+      <c r="N75" s="16"/>
+      <c r="O75" s="16"/>
+      <c r="P75" s="16"/>
+      <c r="Q75" s="16"/>
+      <c r="R75" s="16"/>
+      <c r="S75" s="16"/>
+      <c r="T75" s="16"/>
+      <c r="U75" s="16"/>
+      <c r="V75" s="16"/>
+      <c r="W75" s="16"/>
+      <c r="X75" s="16"/>
+      <c r="Y75" s="16"/>
+      <c r="Z75" s="16"/>
+      <c r="AA75" s="16"/>
+      <c r="AB75" s="16"/>
+      <c r="AC75" s="17"/>
+    </row>
+    <row r="76" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C76" s="15"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
+      <c r="N76" s="16"/>
+      <c r="O76" s="16"/>
+      <c r="P76" s="16"/>
+      <c r="Q76" s="16"/>
+      <c r="R76" s="16"/>
+      <c r="S76" s="16"/>
+      <c r="T76" s="16"/>
+      <c r="U76" s="16"/>
+      <c r="V76" s="16"/>
+      <c r="W76" s="16"/>
+      <c r="X76" s="16"/>
+      <c r="Y76" s="16"/>
+      <c r="Z76" s="16"/>
+      <c r="AA76" s="16"/>
+      <c r="AB76" s="16"/>
+      <c r="AC76" s="17"/>
+    </row>
+    <row r="77" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C77" s="15"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
+      <c r="M77" s="16"/>
+      <c r="N77" s="16"/>
+      <c r="O77" s="16"/>
+      <c r="P77" s="16"/>
+      <c r="Q77" s="16"/>
+      <c r="R77" s="16"/>
+      <c r="S77" s="16"/>
+      <c r="T77" s="16"/>
+      <c r="U77" s="16"/>
+      <c r="V77" s="16"/>
+      <c r="W77" s="16"/>
+      <c r="X77" s="16"/>
+      <c r="Y77" s="16"/>
+      <c r="Z77" s="16"/>
+      <c r="AA77" s="16"/>
+      <c r="AB77" s="16"/>
+      <c r="AC77" s="17"/>
+    </row>
+    <row r="78" spans="3:29" x14ac:dyDescent="0.4">
+      <c r="C78" s="18"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="19"/>
+      <c r="K78" s="19"/>
+      <c r="L78" s="19"/>
+      <c r="M78" s="19"/>
+      <c r="N78" s="19"/>
+      <c r="O78" s="19"/>
+      <c r="P78" s="19"/>
+      <c r="Q78" s="19"/>
+      <c r="R78" s="19"/>
+      <c r="S78" s="19"/>
+      <c r="T78" s="19"/>
+      <c r="U78" s="19"/>
+      <c r="V78" s="19"/>
+      <c r="W78" s="19"/>
+      <c r="X78" s="19"/>
+      <c r="Y78" s="19"/>
+      <c r="Z78" s="19"/>
+      <c r="AA78" s="19"/>
+      <c r="AB78" s="19"/>
+      <c r="AC78" s="20"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4134A2B4-72BC-4B59-9994-741C3D55585D}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="3.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D15" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75577B4C-8D04-4091-92E2-431E10EF233B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D461B16A-2FB5-4D29-A533-808187A5F671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="7" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="220">
   <si>
     <t>作業週報アプリ</t>
     <rPh sb="0" eb="4">
@@ -1531,6 +1531,32 @@
   </si>
   <si>
     <t>PR_USER_CREATE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PR_USER_DELETE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署管理プロセス</t>
+    <rPh sb="0" eb="4">
+      <t>ブショカンリ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1714,7 +1740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1763,9 +1789,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1778,7 +1801,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7678,16 +7728,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>127346</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>124225</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>37699</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>101814</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>65712</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>19531</xdr:rowOff>
+      <xdr:colOff>134470</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7702,8 +7752,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1808228" y="1401696"/>
-          <a:ext cx="1619249" cy="702129"/>
+          <a:off x="1998728" y="1580990"/>
+          <a:ext cx="1497507" cy="749834"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartInputOutput">
           <a:avLst/>
@@ -7738,6 +7788,86 @@
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>User_ln</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>User_fn</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>usermn</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>leader_fg</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>enable_fg</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>deparment_cd</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>add_user</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>passwrd</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
@@ -7755,10 +7885,10 @@
       <xdr:rowOff>151279</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>258453</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>124225</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95761</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>101814</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7777,7 +7907,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1870822" y="1227044"/>
-          <a:ext cx="908955" cy="174652"/>
+          <a:ext cx="1026410" cy="353946"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector2">
           <a:avLst/>
@@ -7805,16 +7935,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>216793</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>19530</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76406</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>6882</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>37619</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>240925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7827,17 +7957,3284 @@
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="101" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1">
-          <a:off x="2321557" y="2240236"/>
-          <a:ext cx="623207" cy="350384"/>
+          <a:off x="2170123" y="2758431"/>
+          <a:ext cx="1019734" cy="164519"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
             <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>44824</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="フローチャート: 判断 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84960553-F06F-46D7-B497-20D05AB67BA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1725706" y="3339353"/>
+          <a:ext cx="2084294" cy="672353"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>未登録ユーザ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>246529</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>112058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>253212</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="コネクタ: カギ線 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23A29E89-0863-40F5-9ED5-3610DD0730B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="2"/>
+          <a:endCxn id="19" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2631121" y="4148437"/>
+          <a:ext cx="280147" cy="6683"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>158484</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>57230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="フローチャート: 処理 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{994007E4-F5EE-4133-A132-52A70054941A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4370294" y="5109882"/>
+          <a:ext cx="2231572" cy="864054"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>はすでに存在しています。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114219</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="フローチャート: 処理 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBD414FF-DBE9-4FFF-826C-6F621475235B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2073088" y="4291853"/>
+          <a:ext cx="1402896" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>新規登録処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>6723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="コネクタ: カギ線 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E46BE8-7345-44B4-9C4A-7581BA1CAD78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="49" idx="2"/>
+          <a:endCxn id="18" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="5181440" y="4805242"/>
+          <a:ext cx="598394" cy="10886"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>264459</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>129988</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>254854</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>187218</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="フローチャート: 処理 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD0CC21F-134F-4F61-A7B3-233958D41716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1665194" y="5038164"/>
+          <a:ext cx="2231572" cy="864054"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>登録が完了しました</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>253213</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1759</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>259657</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>129987</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="コネクタ: カギ線 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B35A980D-EAA2-4021-B903-F352F971C6B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="19" idx="2"/>
+          <a:endCxn id="26" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2612792" y="4869975"/>
+          <a:ext cx="329933" cy="6444"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>257736</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>167529</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="フローチャート: 処理 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CF5C191-AAFC-40C2-95E6-D7F34AAF8442}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7821707" y="6499412"/>
+          <a:ext cx="1590675" cy="728382"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果表示</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>259656</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>187217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>257736</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>140073</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="36" name="コネクタ: カギ線 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E8E11E9-E0BD-4C62-BD87-FE1E7C50CF94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="26" idx="2"/>
+          <a:endCxn id="35" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="4820651" y="3862546"/>
+          <a:ext cx="961385" cy="5040727"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>57229</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>257736</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>140073</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="コネクタ: カギ線 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{245FC7B5-447E-49B3-A8AD-8972FC861486}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="2"/>
+          <a:endCxn id="35" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="6209060" y="5250955"/>
+          <a:ext cx="889667" cy="2335627"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>89646</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>100293</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="フローチャート: 処理 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E468E2FF-4122-4B22-96B5-34A2ECCEB70D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="470647" y="7619999"/>
+          <a:ext cx="1590675" cy="728383"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除処理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>127346</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>135432</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>100853</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="フローチャート: データ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2878B181-972A-4BD0-8A9D-98EFC41343E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2088375" y="8472608"/>
+          <a:ext cx="1374243" cy="424862"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>User_id</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>100293</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>50426</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>111450</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>135432</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="コネクタ: カギ線 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{425397D9-1F2E-4D45-AEE4-14A78F6ACDB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="43" idx="3"/>
+          <a:endCxn id="44" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2061322" y="7984191"/>
+          <a:ext cx="851599" cy="488417"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>230841</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>141194</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>73959</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>6723</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="フローチャート: 判断 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A643AA55-BDA5-4009-8471-A12C63C69E07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4433047" y="3839135"/>
+          <a:ext cx="2084294" cy="672353"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザあり</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>230841</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>73959</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="コネクタ: カギ線 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72A2457D-22A6-4589-ADA3-A30A72DE8FF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="3"/>
+          <a:endCxn id="49" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3810000" y="3675530"/>
+          <a:ext cx="623047" cy="499782"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>230840</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>186017</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>221236</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>41542</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="フローチャート: 処理 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6190AA5C-251B-4594-B94C-B4765041EDD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7514664" y="4489076"/>
+          <a:ext cx="2231572" cy="864054"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>はすでに存在しています。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>73959</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>73959</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>230840</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>12927</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="57" name="コネクタ: カギ線 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88D9505E-3715-4B00-984A-13E92D1B94C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="49" idx="3"/>
+          <a:endCxn id="56" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6517341" y="4175312"/>
+          <a:ext cx="997323" cy="745791"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>212633</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>41543</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>226038</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="コネクタ: カギ線 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8FD222C-0E9E-4D04-8193-57FE749E331D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="56" idx="2"/>
+          <a:endCxn id="35" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8050607" y="5919569"/>
+          <a:ext cx="1146282" cy="13405"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>112060</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>235324</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>11207</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="フローチャート: 判断 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74AB3852-01FC-462E-8D13-263838D69FBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1792942" y="9693089"/>
+          <a:ext cx="2084294" cy="672353"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>未登録ユーザ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>254174</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>156881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>33619</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="67" name="コネクタ: カギ線 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69839651-D05E-4315-9B17-0B79295AA531}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="44" idx="4"/>
+          <a:endCxn id="66" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2407484" y="9265483"/>
+          <a:ext cx="795619" cy="59592"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>235324</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>78442</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>257735</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="71" name="コネクタ: カギ線 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB565CC9-E35E-4FE5-98AA-51D5465B9650}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="66" idx="3"/>
+          <a:endCxn id="76" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3877236" y="10029266"/>
+          <a:ext cx="1423146" cy="246528"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>118463</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>11207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>33619</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="コネクタ: カギ線 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{914E2072-E056-4B9C-B301-11A0089130CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="66" idx="2"/>
+          <a:endCxn id="77" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2524527" y="10480702"/>
+          <a:ext cx="425823" cy="195303"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>11205</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>224118</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>136231</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="76" name="フローチャート: 処理 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7322CF53-8DF1-4399-A921-F814577AB265}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4493558" y="10275794"/>
+          <a:ext cx="1613648" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>パスワード</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザー削除</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123265</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>113660</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>90848</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="フローチャート: 処理 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06CF3F56-D795-4F44-B0F9-42CE02CC9404}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1524000" y="10791265"/>
+          <a:ext cx="2231572" cy="864054"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>が正しくありません</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>40342</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>197224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>30738</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>52749</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="82" name="フローチャート: 処理 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDBB4780-5CC9-49DA-8C9A-1F073BE7347B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4242548" y="10954871"/>
+          <a:ext cx="2231572" cy="864054"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>が正しくありません</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>257736</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>136230</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>35541</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>197223</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="83" name="コネクタ: カギ線 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A68DD40A-6083-42EE-A908-AD3684363A4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="76" idx="2"/>
+          <a:endCxn id="82" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="5198009" y="10794545"/>
+          <a:ext cx="262699" cy="57952"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>67234</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>100852</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>257174</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="87" name="フローチャート: 処理 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ACAA46E-F71D-4B9F-A4CD-A115362A1C2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7911352" y="11665323"/>
+          <a:ext cx="1590675" cy="728382"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>処理結果表示</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>35541</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>52748</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>67235</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>61631</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="88" name="コネクタ: カギ線 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE369E1A-A07F-435F-9E61-8B90EE304764}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="82" idx="2"/>
+          <a:endCxn id="87" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="6529549" y="10647710"/>
+          <a:ext cx="210589" cy="2553018"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>118463</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>90847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>67235</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>61631</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="91" name="コネクタ: カギ線 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A0F3E67-E296-43BF-B769-EA7EDD65DCA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="77" idx="2"/>
+          <a:endCxn id="87" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="5088472" y="9206633"/>
+          <a:ext cx="374195" cy="5271566"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>189940</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123266</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="98" name="フローチャート: 処理 97">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{507A45FA-85EE-4933-8AF8-9E455886A5CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="280147" y="13178118"/>
+          <a:ext cx="1590675" cy="728383"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>登録・削除処理</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>216993</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>45785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>145676</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>100852</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="99" name="フローチャート: データ 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A3B6824-CD8A-4229-AC67-91D61E2CCB3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1897875" y="14030726"/>
+          <a:ext cx="1609566" cy="660185"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartInputOutput">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>User_id</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>224117</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>257735</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>67234</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="101" name="フローチャート: 判断 100">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E0339BB-1DC7-4A08-8F3C-41CB9B9EE712}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1344705" y="3350558"/>
+          <a:ext cx="2835089" cy="818029"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>新規登録フラグ：１</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114219</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>102613</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="102" name="フローチャート: 処理 101">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F49E262C-1C4D-4357-8356-06D05AB83E76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2073088" y="4997823"/>
+          <a:ext cx="1402896" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>新規登録</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>240926</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>67234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>253212</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="105" name="コネクタ: カギ線 104">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B49AB5A-527F-4A26-9BC7-F24E5F4695B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="101" idx="2"/>
+          <a:endCxn id="102" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="2353775" y="4577062"/>
+          <a:ext cx="829236" cy="12286"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>246530</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>102613</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>253213</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="108" name="コネクタ: カギ線 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C20B39B4-D833-405B-9456-0FA71E88A528}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="102" idx="2"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="2295825" y="5886230"/>
+          <a:ext cx="950741" cy="6683"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>257735</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>61632</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>62754</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>58031</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="113" name="コネクタ: カギ線 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E760AB72-5BBE-4449-B8BB-AFA9342776E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="101" idx="3"/>
+          <a:endCxn id="120" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4179794" y="3759573"/>
+          <a:ext cx="7088842" cy="198105"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>78441</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>100854</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="116" name="フローチャート: 判断 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{605B5684-CC07-40A1-96ED-6096D78134EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10690411" y="4796119"/>
+          <a:ext cx="2835089" cy="818029"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザーあり</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>62754</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>51548</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>64914</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>64514</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="120" name="フローチャート: 処理 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{604B7A91-2FB3-48FB-B832-ABB0CD33697E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11268636" y="3749489"/>
+          <a:ext cx="1402896" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>更新</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>203908</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>64514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>61632</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="123" name="コネクタ: カギ線 122">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9FE24E8-6906-4DC5-B686-304B6587FF9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="120" idx="2"/>
+          <a:endCxn id="116" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="11723894" y="4412057"/>
+          <a:ext cx="630252" cy="137872"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>61631</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>100854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>201664</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>22410</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="129" name="コネクタ: カギ線 128">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CB7A020-9D2F-41F5-910B-3C9F1B6001A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="116" idx="2"/>
+          <a:endCxn id="133" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="11813782" y="5908321"/>
+          <a:ext cx="728380" cy="140033"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>60512</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>22410</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>62672</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>35377</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="133" name="フローチャート: 処理 132">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4D2F7E2-0059-4B11-8F3F-91746EE3379F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11546541" y="6342528"/>
+          <a:ext cx="1402896" cy="416378"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>更新処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>212912</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>163605</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>203307</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19128</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="134" name="フローチャート: 処理 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F0EFABB-8F15-459F-B016-CCAA682E20F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11138647" y="7088840"/>
+          <a:ext cx="2231572" cy="864053"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>更新が完了しました</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>10085</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>94129</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>168087</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="135" name="コネクタ: カギ線 134">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BF345C0-A2B2-40DD-84D8-4A5FEB78BFEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="21203211" y="5017433"/>
+          <a:ext cx="840440" cy="84044"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>201665</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>35377</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>208109</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>163605</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="137" name="コネクタ: カギ線 136">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD103D1E-1605-4B44-80A2-5D6560F0C82F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="133" idx="2"/>
+          <a:endCxn id="134" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="12086244" y="6920651"/>
+          <a:ext cx="329934" cy="6444"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>50426</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>200905</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="140" name="フローチャート: 処理 139">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C368A03-E5BD-4302-A82B-55E4E2B8AA78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13828058" y="5838264"/>
+          <a:ext cx="2190750" cy="884465"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>メッセージ：</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ユーザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>が正しくありません</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>78441</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95252</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>75639</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="141" name="コネクタ: カギ線 140">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC5878B3-98AB-4DBA-ADA1-741F22A9B8F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="116" idx="3"/>
+          <a:endCxn id="140" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13525500" y="5205134"/>
+          <a:ext cx="1397933" cy="633130"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>167529</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19129</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>208109</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>140074</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="145" name="コネクタ: カギ線 144">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7163DA1-342E-4435-AB92-76B87503175F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="134" idx="2"/>
+          <a:endCxn id="35" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="9865259" y="7500017"/>
+          <a:ext cx="1936298" cy="2842051"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>167529</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>200906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>75639</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>140074</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="148" name="コネクタ: カギ線 147">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54F10ABC-6E07-40C4-9F97-F2D42150C9E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="140" idx="2"/>
+          <a:endCxn id="35" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="10584677" y="5550435"/>
+          <a:ext cx="3166462" cy="5511051"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
         </a:prstGeom>
         <a:ln>
           <a:tailEnd type="triangle"/>
@@ -10437,344 +13834,100 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="17"/>
+      <c r="X12" s="16"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16" t="s">
+      <c r="G13" t="s">
         <v>210</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16" t="s">
+      <c r="K13" t="s">
         <v>210</v>
       </c>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16" t="s">
+      <c r="O13" t="s">
         <v>210</v>
       </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="17"/>
+      <c r="X13" s="16"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16" t="s">
+      <c r="T14" t="s">
         <v>210</v>
       </c>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="17"/>
+      <c r="X14" s="16"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="17"/>
+      <c r="X15" s="16"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="17"/>
+      <c r="X16" s="16"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16" t="s">
+      <c r="D17" t="s">
         <v>211</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16" t="s">
+      <c r="I17" t="s">
         <v>211</v>
       </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16" t="s">
+      <c r="M17" t="s">
         <v>211</v>
       </c>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16" t="s">
+      <c r="Q17" t="s">
         <v>211</v>
       </c>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="17"/>
+      <c r="X17" s="16"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="17"/>
+      <c r="X18" s="16"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="17"/>
+      <c r="X19" s="16"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="17"/>
+      <c r="X20" s="16"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="17"/>
+      <c r="X21" s="16"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="17"/>
+      <c r="X22" s="16"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.4">
       <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="17"/>
+      <c r="X23" s="16"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="20"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="19"/>
     </row>
     <row r="27" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
@@ -10814,955 +13967,192 @@
     </row>
     <row r="47" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C47" s="15"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-      <c r="Z47" s="16"/>
-      <c r="AA47" s="16"/>
-      <c r="AB47" s="16"/>
-      <c r="AC47" s="17"/>
+      <c r="AC47" s="16"/>
     </row>
     <row r="48" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C48" s="15"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-      <c r="Z48" s="16"/>
-      <c r="AA48" s="16"/>
-      <c r="AB48" s="16"/>
-      <c r="AC48" s="17"/>
+      <c r="AC48" s="16"/>
     </row>
     <row r="49" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C49" s="15"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
-      <c r="Z49" s="16"/>
-      <c r="AA49" s="16"/>
-      <c r="AB49" s="16"/>
-      <c r="AC49" s="17"/>
+      <c r="AC49" s="16"/>
     </row>
     <row r="50" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C50" s="15"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16" t="s">
+      <c r="N50" t="s">
         <v>210</v>
       </c>
-      <c r="O50" s="16"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
-      <c r="S50" s="16" t="s">
+      <c r="S50" t="s">
         <v>210</v>
       </c>
-      <c r="T50" s="16"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="16"/>
-      <c r="X50" s="16"/>
-      <c r="Y50" s="16"/>
-      <c r="Z50" s="16"/>
-      <c r="AA50" s="16"/>
-      <c r="AB50" s="16"/>
-      <c r="AC50" s="17"/>
+      <c r="AC50" s="16"/>
     </row>
     <row r="51" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C51" s="15"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16" t="s">
+      <c r="I51" t="s">
         <v>210</v>
       </c>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-      <c r="Z51" s="16"/>
-      <c r="AA51" s="16"/>
-      <c r="AB51" s="16"/>
-      <c r="AC51" s="17"/>
+      <c r="AC51" s="16"/>
     </row>
     <row r="52" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C52" s="15"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-      <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="16"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
-      <c r="Z52" s="16"/>
-      <c r="AA52" s="16"/>
-      <c r="AB52" s="16"/>
-      <c r="AC52" s="17"/>
+      <c r="AC52" s="16"/>
     </row>
     <row r="53" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C53" s="15"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
-      <c r="O53" s="16"/>
-      <c r="P53" s="16"/>
-      <c r="Q53" s="16"/>
-      <c r="R53" s="16"/>
-      <c r="S53" s="16"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="16"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="16"/>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
-      <c r="Z53" s="16"/>
-      <c r="AA53" s="16"/>
-      <c r="AB53" s="16"/>
-      <c r="AC53" s="17"/>
+      <c r="AC53" s="16"/>
     </row>
     <row r="54" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C54" s="15"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="16"/>
-      <c r="R54" s="16"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="16"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="16"/>
-      <c r="X54" s="16"/>
-      <c r="Y54" s="16"/>
-      <c r="Z54" s="16"/>
-      <c r="AA54" s="16"/>
-      <c r="AB54" s="16"/>
-      <c r="AC54" s="17"/>
+      <c r="AC54" s="16"/>
     </row>
     <row r="55" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C55" s="15"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16" t="s">
+      <c r="F55" t="s">
         <v>211</v>
       </c>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16" t="s">
+      <c r="L55" t="s">
         <v>211</v>
       </c>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
-      <c r="O55" s="16"/>
-      <c r="P55" s="16" t="s">
+      <c r="P55" t="s">
         <v>211</v>
       </c>
-      <c r="Q55" s="16"/>
-      <c r="R55" s="16"/>
-      <c r="S55" s="16"/>
-      <c r="T55" s="16"/>
-      <c r="U55" s="16"/>
-      <c r="V55" s="16"/>
-      <c r="W55" s="16"/>
-      <c r="X55" s="16"/>
-      <c r="Y55" s="16"/>
-      <c r="Z55" s="16"/>
-      <c r="AA55" s="16"/>
-      <c r="AB55" s="16"/>
-      <c r="AC55" s="17"/>
+      <c r="AC55" s="16"/>
     </row>
     <row r="56" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C56" s="15"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
-      <c r="Z56" s="16"/>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="16"/>
-      <c r="AC56" s="17"/>
+      <c r="AC56" s="16"/>
     </row>
     <row r="57" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C57" s="15"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
-      <c r="Z57" s="16"/>
-      <c r="AA57" s="16"/>
-      <c r="AB57" s="16"/>
-      <c r="AC57" s="17"/>
+      <c r="AC57" s="16"/>
     </row>
     <row r="58" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C58" s="15"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="16"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16" t="s">
+      <c r="S58" t="s">
         <v>210</v>
       </c>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
-      <c r="Z58" s="16"/>
-      <c r="AA58" s="16"/>
-      <c r="AB58" s="16"/>
-      <c r="AC58" s="17"/>
+      <c r="AC58" s="16"/>
     </row>
     <row r="59" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C59" s="15"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="16"/>
-      <c r="R59" s="16"/>
-      <c r="S59" s="16"/>
-      <c r="T59" s="16"/>
-      <c r="U59" s="16"/>
-      <c r="V59" s="16"/>
-      <c r="W59" s="16"/>
-      <c r="X59" s="16" t="s">
+      <c r="X59" t="s">
         <v>210</v>
       </c>
-      <c r="Y59" s="16"/>
-      <c r="Z59" s="16"/>
-      <c r="AA59" s="16"/>
-      <c r="AB59" s="16"/>
-      <c r="AC59" s="17"/>
+      <c r="AC59" s="16"/>
     </row>
     <row r="60" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C60" s="15"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="16"/>
-      <c r="R60" s="16"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="16"/>
-      <c r="U60" s="16"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="16"/>
-      <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
-      <c r="Z60" s="16"/>
-      <c r="AA60" s="16"/>
-      <c r="AB60" s="16"/>
-      <c r="AC60" s="17"/>
+      <c r="AC60" s="16"/>
     </row>
     <row r="61" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C61" s="15"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="16"/>
-      <c r="I61" s="16"/>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="16"/>
-      <c r="O61" s="16"/>
-      <c r="P61" s="16"/>
-      <c r="Q61" s="16"/>
-      <c r="R61" s="16"/>
-      <c r="S61" s="16"/>
-      <c r="T61" s="16"/>
-      <c r="U61" s="16"/>
-      <c r="V61" s="16"/>
-      <c r="W61" s="16"/>
-      <c r="X61" s="16"/>
-      <c r="Y61" s="16"/>
-      <c r="Z61" s="16"/>
-      <c r="AA61" s="16"/>
-      <c r="AB61" s="16"/>
-      <c r="AC61" s="17"/>
+      <c r="AC61" s="16"/>
     </row>
     <row r="62" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C62" s="15"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16"/>
-      <c r="I62" s="16"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="16"/>
-      <c r="O62" s="16"/>
-      <c r="P62" s="16"/>
-      <c r="Q62" s="16"/>
-      <c r="R62" s="16"/>
-      <c r="S62" s="16"/>
-      <c r="T62" s="16"/>
-      <c r="U62" s="16"/>
-      <c r="V62" s="16"/>
-      <c r="W62" s="16"/>
-      <c r="X62" s="16"/>
-      <c r="Y62" s="16"/>
-      <c r="Z62" s="16"/>
-      <c r="AA62" s="16"/>
-      <c r="AB62" s="16"/>
-      <c r="AC62" s="17"/>
+      <c r="AC62" s="16"/>
     </row>
     <row r="63" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C63" s="15"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="16"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="16"/>
-      <c r="O63" s="16"/>
-      <c r="P63" s="16" t="s">
+      <c r="P63" t="s">
         <v>211</v>
       </c>
-      <c r="Q63" s="16"/>
-      <c r="R63" s="16"/>
-      <c r="S63" s="16"/>
-      <c r="T63" s="16"/>
-      <c r="U63" s="16" t="s">
+      <c r="U63" t="s">
         <v>211</v>
       </c>
-      <c r="V63" s="16"/>
-      <c r="W63" s="16"/>
-      <c r="X63" s="16"/>
-      <c r="Y63" s="16"/>
-      <c r="Z63" s="16"/>
-      <c r="AA63" s="16"/>
-      <c r="AB63" s="16"/>
-      <c r="AC63" s="17"/>
+      <c r="AC63" s="16"/>
     </row>
     <row r="64" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C64" s="15"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-      <c r="P64" s="16"/>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
-      <c r="S64" s="16"/>
-      <c r="T64" s="16"/>
-      <c r="U64" s="16"/>
-      <c r="V64" s="16"/>
-      <c r="W64" s="16"/>
-      <c r="X64" s="16"/>
-      <c r="Y64" s="16"/>
-      <c r="Z64" s="16"/>
-      <c r="AA64" s="16"/>
-      <c r="AB64" s="16"/>
-      <c r="AC64" s="17"/>
+      <c r="AC64" s="16"/>
     </row>
     <row r="65" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C65" s="15"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="16"/>
-      <c r="O65" s="16"/>
-      <c r="P65" s="16"/>
-      <c r="Q65" s="16"/>
-      <c r="R65" s="16"/>
-      <c r="S65" s="16"/>
-      <c r="T65" s="16"/>
-      <c r="U65" s="16"/>
-      <c r="V65" s="16"/>
-      <c r="W65" s="16"/>
-      <c r="X65" s="16"/>
-      <c r="Y65" s="16"/>
-      <c r="Z65" s="16"/>
-      <c r="AA65" s="16"/>
-      <c r="AB65" s="16"/>
-      <c r="AC65" s="17"/>
+      <c r="AC65" s="16"/>
     </row>
     <row r="66" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C66" s="15"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
-      <c r="H66" s="16"/>
-      <c r="I66" s="16"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="16"/>
-      <c r="O66" s="16"/>
-      <c r="P66" s="16"/>
-      <c r="Q66" s="16"/>
-      <c r="R66" s="16"/>
-      <c r="S66" s="16"/>
-      <c r="T66" s="16"/>
-      <c r="U66" s="16"/>
-      <c r="V66" s="16"/>
-      <c r="W66" s="16"/>
-      <c r="X66" s="16"/>
-      <c r="Y66" s="16"/>
-      <c r="Z66" s="16"/>
-      <c r="AA66" s="16"/>
-      <c r="AB66" s="16"/>
-      <c r="AC66" s="17"/>
+      <c r="AC66" s="16"/>
     </row>
     <row r="67" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C67" s="15"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-      <c r="I67" s="16"/>
-      <c r="J67" s="16"/>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="16"/>
-      <c r="O67" s="16"/>
-      <c r="P67" s="16"/>
-      <c r="Q67" s="16"/>
-      <c r="R67" s="16"/>
-      <c r="S67" s="16" t="s">
+      <c r="S67" t="s">
         <v>210</v>
       </c>
-      <c r="T67" s="16"/>
-      <c r="U67" s="16"/>
-      <c r="V67" s="16"/>
-      <c r="W67" s="16"/>
-      <c r="X67" s="16"/>
-      <c r="Y67" s="16"/>
-      <c r="Z67" s="16"/>
-      <c r="AA67" s="16"/>
-      <c r="AB67" s="16"/>
-      <c r="AC67" s="17"/>
+      <c r="AC67" s="16"/>
     </row>
     <row r="68" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C68" s="15"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="16"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="16"/>
-      <c r="O68" s="16"/>
-      <c r="P68" s="16"/>
-      <c r="Q68" s="16"/>
-      <c r="R68" s="16"/>
-      <c r="S68" s="16"/>
-      <c r="T68" s="16"/>
-      <c r="U68" s="16"/>
-      <c r="V68" s="16"/>
-      <c r="W68" s="16"/>
-      <c r="X68" s="16"/>
-      <c r="Y68" s="16"/>
-      <c r="Z68" s="16"/>
-      <c r="AA68" s="16"/>
-      <c r="AB68" s="16"/>
-      <c r="AC68" s="17"/>
+      <c r="AC68" s="16"/>
     </row>
     <row r="69" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C69" s="15"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="16"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="16"/>
-      <c r="U69" s="16"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="16"/>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
-      <c r="Z69" s="16"/>
-      <c r="AA69" s="16"/>
-      <c r="AB69" s="16"/>
-      <c r="AC69" s="17"/>
+      <c r="AC69" s="16"/>
     </row>
     <row r="70" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C70" s="15"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="16"/>
-      <c r="O70" s="16"/>
-      <c r="P70" s="16"/>
-      <c r="Q70" s="16"/>
-      <c r="R70" s="16"/>
-      <c r="S70" s="16"/>
-      <c r="T70" s="16"/>
-      <c r="U70" s="16"/>
-      <c r="V70" s="16"/>
-      <c r="W70" s="16"/>
-      <c r="X70" s="16"/>
-      <c r="Y70" s="16"/>
-      <c r="Z70" s="16"/>
-      <c r="AA70" s="16"/>
-      <c r="AB70" s="16"/>
-      <c r="AC70" s="17"/>
+      <c r="AC70" s="16"/>
     </row>
     <row r="71" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C71" s="15"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="16"/>
-      <c r="O71" s="16"/>
-      <c r="P71" s="16" t="s">
+      <c r="P71" t="s">
         <v>211</v>
       </c>
-      <c r="Q71" s="16"/>
-      <c r="R71" s="16"/>
-      <c r="S71" s="16"/>
-      <c r="T71" s="16"/>
-      <c r="U71" s="16"/>
-      <c r="V71" s="16"/>
-      <c r="W71" s="16"/>
-      <c r="X71" s="16"/>
-      <c r="Y71" s="16"/>
-      <c r="Z71" s="16"/>
-      <c r="AA71" s="16"/>
-      <c r="AB71" s="16"/>
-      <c r="AC71" s="17"/>
+      <c r="AC71" s="16"/>
     </row>
     <row r="72" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C72" s="15"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="16"/>
-      <c r="O72" s="16"/>
-      <c r="P72" s="16"/>
-      <c r="Q72" s="16"/>
-      <c r="R72" s="16"/>
-      <c r="S72" s="16"/>
-      <c r="T72" s="16"/>
-      <c r="U72" s="16"/>
-      <c r="V72" s="16"/>
-      <c r="W72" s="16"/>
-      <c r="X72" s="16"/>
-      <c r="Y72" s="16"/>
-      <c r="Z72" s="16"/>
-      <c r="AA72" s="16"/>
-      <c r="AB72" s="16"/>
-      <c r="AC72" s="17"/>
+      <c r="AC72" s="16"/>
     </row>
     <row r="73" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C73" s="15"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="16"/>
-      <c r="O73" s="16"/>
-      <c r="P73" s="16"/>
-      <c r="Q73" s="16"/>
-      <c r="R73" s="16"/>
-      <c r="S73" s="16"/>
-      <c r="T73" s="16"/>
-      <c r="U73" s="16"/>
-      <c r="V73" s="16"/>
-      <c r="W73" s="16"/>
-      <c r="X73" s="16"/>
-      <c r="Y73" s="16"/>
-      <c r="Z73" s="16"/>
-      <c r="AA73" s="16"/>
-      <c r="AB73" s="16"/>
-      <c r="AC73" s="17"/>
+      <c r="AC73" s="16"/>
     </row>
     <row r="74" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C74" s="15"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="16"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="16"/>
-      <c r="O74" s="16"/>
-      <c r="P74" s="16"/>
-      <c r="Q74" s="16"/>
-      <c r="R74" s="16"/>
-      <c r="S74" s="16"/>
-      <c r="T74" s="16"/>
-      <c r="U74" s="16"/>
-      <c r="V74" s="16"/>
-      <c r="W74" s="16"/>
-      <c r="X74" s="16"/>
-      <c r="Y74" s="16"/>
-      <c r="Z74" s="16"/>
-      <c r="AA74" s="16"/>
-      <c r="AB74" s="16"/>
-      <c r="AC74" s="17"/>
+      <c r="AC74" s="16"/>
     </row>
     <row r="75" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C75" s="15"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="16"/>
-      <c r="O75" s="16"/>
-      <c r="P75" s="16"/>
-      <c r="Q75" s="16"/>
-      <c r="R75" s="16"/>
-      <c r="S75" s="16"/>
-      <c r="T75" s="16"/>
-      <c r="U75" s="16"/>
-      <c r="V75" s="16"/>
-      <c r="W75" s="16"/>
-      <c r="X75" s="16"/>
-      <c r="Y75" s="16"/>
-      <c r="Z75" s="16"/>
-      <c r="AA75" s="16"/>
-      <c r="AB75" s="16"/>
-      <c r="AC75" s="17"/>
+      <c r="AC75" s="16"/>
     </row>
     <row r="76" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C76" s="15"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="16"/>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="16"/>
-      <c r="O76" s="16"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="16"/>
-      <c r="R76" s="16"/>
-      <c r="S76" s="16"/>
-      <c r="T76" s="16"/>
-      <c r="U76" s="16"/>
-      <c r="V76" s="16"/>
-      <c r="W76" s="16"/>
-      <c r="X76" s="16"/>
-      <c r="Y76" s="16"/>
-      <c r="Z76" s="16"/>
-      <c r="AA76" s="16"/>
-      <c r="AB76" s="16"/>
-      <c r="AC76" s="17"/>
+      <c r="AC76" s="16"/>
     </row>
     <row r="77" spans="3:29" x14ac:dyDescent="0.4">
       <c r="C77" s="15"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="16"/>
-      <c r="O77" s="16"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="16"/>
-      <c r="R77" s="16"/>
-      <c r="S77" s="16"/>
-      <c r="T77" s="16"/>
-      <c r="U77" s="16"/>
-      <c r="V77" s="16"/>
-      <c r="W77" s="16"/>
-      <c r="X77" s="16"/>
-      <c r="Y77" s="16"/>
-      <c r="Z77" s="16"/>
-      <c r="AA77" s="16"/>
-      <c r="AB77" s="16"/>
-      <c r="AC77" s="17"/>
+      <c r="AC77" s="16"/>
     </row>
     <row r="78" spans="3:29" x14ac:dyDescent="0.4">
-      <c r="C78" s="18"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19"/>
-      <c r="O78" s="19"/>
-      <c r="P78" s="19"/>
-      <c r="Q78" s="19"/>
-      <c r="R78" s="19"/>
-      <c r="S78" s="19"/>
-      <c r="T78" s="19"/>
-      <c r="U78" s="19"/>
-      <c r="V78" s="19"/>
-      <c r="W78" s="19"/>
-      <c r="X78" s="19"/>
-      <c r="Y78" s="19"/>
-      <c r="Z78" s="19"/>
-      <c r="AA78" s="19"/>
-      <c r="AB78" s="19"/>
-      <c r="AC78" s="20"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+      <c r="M78" s="18"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
+      <c r="P78" s="18"/>
+      <c r="Q78" s="18"/>
+      <c r="R78" s="18"/>
+      <c r="S78" s="18"/>
+      <c r="T78" s="18"/>
+      <c r="U78" s="18"/>
+      <c r="V78" s="18"/>
+      <c r="W78" s="18"/>
+      <c r="X78" s="18"/>
+      <c r="Y78" s="18"/>
+      <c r="Z78" s="18"/>
+      <c r="AA78" s="18"/>
+      <c r="AB78" s="18"/>
+      <c r="AC78" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -11773,30 +14163,2257 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4134A2B4-72BC-4B59-9994-741C3D55585D}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:BF79"/>
   <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="3.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:58" s="9" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:58" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="D15" s="21" t="s">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="D15" s="20" t="s">
         <v>214</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="22"/>
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="22"/>
+      <c r="AH15" s="22"/>
+      <c r="AI15" s="22"/>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="22"/>
+      <c r="AL15" s="22"/>
+      <c r="AM15" s="22"/>
+      <c r="AN15" s="22"/>
+      <c r="AO15" s="22"/>
+      <c r="AP15" s="22"/>
+      <c r="AQ15" s="22"/>
+      <c r="AR15" s="22"/>
+      <c r="AS15" s="22"/>
+      <c r="AT15" s="22"/>
+      <c r="AU15" s="22"/>
+      <c r="AV15" s="22"/>
+      <c r="AW15" s="22"/>
+      <c r="AX15" s="22"/>
+      <c r="AY15" s="22"/>
+      <c r="AZ15" s="22"/>
+      <c r="BA15" s="22"/>
+      <c r="BB15" s="22"/>
+      <c r="BC15" s="22"/>
+      <c r="BD15" s="22"/>
+      <c r="BE15" s="22"/>
+      <c r="BF15" s="23"/>
+    </row>
+    <row r="16" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="25"/>
+      <c r="AI16" s="25"/>
+      <c r="AJ16" s="25"/>
+      <c r="AK16" s="25"/>
+      <c r="AL16" s="25"/>
+      <c r="AM16" s="25"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="25"/>
+      <c r="AQ16" s="25"/>
+      <c r="AR16" s="25"/>
+      <c r="AS16" s="25"/>
+      <c r="AT16" s="25"/>
+      <c r="AU16" s="25"/>
+      <c r="AV16" s="25"/>
+      <c r="AW16" s="25"/>
+      <c r="AX16" s="25"/>
+      <c r="AY16" s="25"/>
+      <c r="AZ16" s="25"/>
+      <c r="BA16" s="25"/>
+      <c r="BB16" s="25"/>
+      <c r="BC16" s="25"/>
+      <c r="BD16" s="25"/>
+      <c r="BE16" s="25"/>
+      <c r="BF16" s="26"/>
+    </row>
+    <row r="17" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AL17" s="25"/>
+      <c r="AM17" s="25"/>
+      <c r="AN17" s="25"/>
+      <c r="AO17" s="25"/>
+      <c r="AP17" s="25"/>
+      <c r="AQ17" s="25"/>
+      <c r="AR17" s="25"/>
+      <c r="AS17" s="25"/>
+      <c r="AT17" s="25"/>
+      <c r="AU17" s="25"/>
+      <c r="AV17" s="25"/>
+      <c r="AW17" s="25"/>
+      <c r="AX17" s="25"/>
+      <c r="AY17" s="25"/>
+      <c r="AZ17" s="25"/>
+      <c r="BA17" s="25"/>
+      <c r="BB17" s="25"/>
+      <c r="BC17" s="25"/>
+      <c r="BD17" s="25"/>
+      <c r="BE17" s="25"/>
+      <c r="BF17" s="26"/>
+    </row>
+    <row r="18" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D18" s="24"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="25"/>
+      <c r="AI18" s="25"/>
+      <c r="AJ18" s="25"/>
+      <c r="AK18" s="25"/>
+      <c r="AL18" s="25"/>
+      <c r="AM18" s="25"/>
+      <c r="AN18" s="25"/>
+      <c r="AO18" s="25"/>
+      <c r="AP18" s="25"/>
+      <c r="AQ18" s="25"/>
+      <c r="AR18" s="25"/>
+      <c r="AS18" s="25"/>
+      <c r="AT18" s="25"/>
+      <c r="AU18" s="25"/>
+      <c r="AV18" s="25"/>
+      <c r="AW18" s="25"/>
+      <c r="AX18" s="25"/>
+      <c r="AY18" s="25"/>
+      <c r="AZ18" s="25"/>
+      <c r="BA18" s="25"/>
+      <c r="BB18" s="25"/>
+      <c r="BC18" s="25"/>
+      <c r="BD18" s="25"/>
+      <c r="BE18" s="25"/>
+      <c r="BF18" s="26"/>
+    </row>
+    <row r="19" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="25"/>
+      <c r="AI19" s="25"/>
+      <c r="AJ19" s="25"/>
+      <c r="AK19" s="25"/>
+      <c r="AL19" s="25"/>
+      <c r="AM19" s="25"/>
+      <c r="AN19" s="25"/>
+      <c r="AO19" s="25"/>
+      <c r="AP19" s="25"/>
+      <c r="AQ19" s="25"/>
+      <c r="AR19" s="25"/>
+      <c r="AS19" s="25"/>
+      <c r="AT19" s="25"/>
+      <c r="AU19" s="25"/>
+      <c r="AV19" s="25"/>
+      <c r="AW19" s="25"/>
+      <c r="AX19" s="25"/>
+      <c r="AY19" s="25"/>
+      <c r="AZ19" s="25"/>
+      <c r="BA19" s="25"/>
+      <c r="BB19" s="25"/>
+      <c r="BC19" s="25"/>
+      <c r="BD19" s="25"/>
+      <c r="BE19" s="25"/>
+      <c r="BF19" s="26"/>
+    </row>
+    <row r="20" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="25"/>
+      <c r="AJ20" s="25"/>
+      <c r="AK20" s="25"/>
+      <c r="AL20" s="25"/>
+      <c r="AM20" s="25"/>
+      <c r="AN20" s="25"/>
+      <c r="AO20" s="25"/>
+      <c r="AP20" s="25"/>
+      <c r="AQ20" s="25"/>
+      <c r="AR20" s="25"/>
+      <c r="AS20" s="25"/>
+      <c r="AT20" s="25"/>
+      <c r="AU20" s="25"/>
+      <c r="AV20" s="25"/>
+      <c r="AW20" s="25"/>
+      <c r="AX20" s="25"/>
+      <c r="AY20" s="25"/>
+      <c r="AZ20" s="25"/>
+      <c r="BA20" s="25"/>
+      <c r="BB20" s="25"/>
+      <c r="BC20" s="25"/>
+      <c r="BD20" s="25"/>
+      <c r="BE20" s="25"/>
+      <c r="BF20" s="26"/>
+    </row>
+    <row r="21" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D21" s="24"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="25"/>
+      <c r="AJ21" s="25"/>
+      <c r="AK21" s="25"/>
+      <c r="AL21" s="25"/>
+      <c r="AM21" s="25"/>
+      <c r="AN21" s="25"/>
+      <c r="AO21" s="25"/>
+      <c r="AP21" s="25"/>
+      <c r="AQ21" s="25"/>
+      <c r="AR21" s="25"/>
+      <c r="AS21" s="25"/>
+      <c r="AT21" s="25"/>
+      <c r="AU21" s="25"/>
+      <c r="AV21" s="25"/>
+      <c r="AW21" s="25"/>
+      <c r="AX21" s="25"/>
+      <c r="AY21" s="25"/>
+      <c r="AZ21" s="25"/>
+      <c r="BA21" s="25"/>
+      <c r="BB21" s="25"/>
+      <c r="BC21" s="25"/>
+      <c r="BD21" s="25"/>
+      <c r="BE21" s="25"/>
+      <c r="BF21" s="26"/>
+    </row>
+    <row r="22" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="25"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="25"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="25"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="25"/>
+      <c r="AQ22" s="25"/>
+      <c r="AR22" s="25"/>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="25"/>
+      <c r="AU22" s="25"/>
+      <c r="AV22" s="25"/>
+      <c r="AW22" s="25"/>
+      <c r="AX22" s="25"/>
+      <c r="AY22" s="25"/>
+      <c r="AZ22" s="25"/>
+      <c r="BA22" s="25"/>
+      <c r="BB22" s="25"/>
+      <c r="BC22" s="25"/>
+      <c r="BD22" s="25"/>
+      <c r="BE22" s="25"/>
+      <c r="BF22" s="26"/>
+    </row>
+    <row r="23" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D23" s="24"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="25"/>
+      <c r="AL23" s="25"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+      <c r="AR23" s="25"/>
+      <c r="AS23" s="25"/>
+      <c r="AT23" s="25"/>
+      <c r="AU23" s="25"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="25"/>
+      <c r="AX23" s="25"/>
+      <c r="AY23" s="25"/>
+      <c r="AZ23" s="25"/>
+      <c r="BA23" s="25"/>
+      <c r="BB23" s="25"/>
+      <c r="BC23" s="25"/>
+      <c r="BD23" s="25"/>
+      <c r="BE23" s="25"/>
+      <c r="BF23" s="26"/>
+    </row>
+    <row r="24" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="25"/>
+      <c r="AJ24" s="25"/>
+      <c r="AK24" s="25"/>
+      <c r="AL24" s="25"/>
+      <c r="AM24" s="25"/>
+      <c r="AN24" s="25"/>
+      <c r="AO24" s="25"/>
+      <c r="AP24" s="25"/>
+      <c r="AQ24" s="25"/>
+      <c r="AR24" s="25"/>
+      <c r="AS24" s="25"/>
+      <c r="AT24" s="25"/>
+      <c r="AU24" s="25"/>
+      <c r="AV24" s="25"/>
+      <c r="AW24" s="25"/>
+      <c r="AX24" s="25"/>
+      <c r="AY24" s="25"/>
+      <c r="AZ24" s="25"/>
+      <c r="BA24" s="25"/>
+      <c r="BB24" s="25"/>
+      <c r="BC24" s="25"/>
+      <c r="BD24" s="25"/>
+      <c r="BE24" s="25"/>
+      <c r="BF24" s="26"/>
+    </row>
+    <row r="25" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
+      <c r="AI25" s="25"/>
+      <c r="AJ25" s="25"/>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="25"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="25"/>
+      <c r="AO25" s="25"/>
+      <c r="AP25" s="25"/>
+      <c r="AQ25" s="25"/>
+      <c r="AR25" s="25"/>
+      <c r="AS25" s="25"/>
+      <c r="AT25" s="25"/>
+      <c r="AU25" s="25"/>
+      <c r="AV25" s="25"/>
+      <c r="AW25" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="AX25" s="25"/>
+      <c r="AY25" s="25"/>
+      <c r="AZ25" s="25"/>
+      <c r="BA25" s="25"/>
+      <c r="BB25" s="25"/>
+      <c r="BC25" s="25"/>
+      <c r="BD25" s="25"/>
+      <c r="BE25" s="25"/>
+      <c r="BF25" s="26"/>
+    </row>
+    <row r="26" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25"/>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="25"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="25"/>
+      <c r="AO26" s="25"/>
+      <c r="AP26" s="25"/>
+      <c r="AQ26" s="25"/>
+      <c r="AR26" s="25"/>
+      <c r="AS26" s="25"/>
+      <c r="AT26" s="25"/>
+      <c r="AU26" s="25"/>
+      <c r="AV26" s="25"/>
+      <c r="AW26" s="25"/>
+      <c r="AX26" s="25"/>
+      <c r="AY26" s="25"/>
+      <c r="AZ26" s="25"/>
+      <c r="BA26" s="25"/>
+      <c r="BB26" s="25"/>
+      <c r="BC26" s="25"/>
+      <c r="BD26" s="25"/>
+      <c r="BE26" s="25"/>
+      <c r="BF26" s="26"/>
+    </row>
+    <row r="27" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D27" s="24"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="25"/>
+      <c r="AK27" s="25"/>
+      <c r="AL27" s="25"/>
+      <c r="AM27" s="25"/>
+      <c r="AN27" s="25"/>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="25"/>
+      <c r="AQ27" s="25"/>
+      <c r="AR27" s="25"/>
+      <c r="AS27" s="25"/>
+      <c r="AT27" s="25"/>
+      <c r="AU27" s="25"/>
+      <c r="AV27" s="25"/>
+      <c r="AW27" s="25"/>
+      <c r="AX27" s="25"/>
+      <c r="AY27" s="25"/>
+      <c r="AZ27" s="25"/>
+      <c r="BA27" s="25"/>
+      <c r="BB27" s="25"/>
+      <c r="BC27" s="25"/>
+      <c r="BD27" s="25"/>
+      <c r="BE27" s="25"/>
+      <c r="BF27" s="26"/>
+    </row>
+    <row r="28" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D28" s="24"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="25"/>
+      <c r="AI28" s="25"/>
+      <c r="AJ28" s="25"/>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="25"/>
+      <c r="AM28" s="25"/>
+      <c r="AN28" s="25"/>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="25"/>
+      <c r="AQ28" s="25"/>
+      <c r="AR28" s="25"/>
+      <c r="AS28" s="25"/>
+      <c r="AT28" s="25"/>
+      <c r="AU28" s="25"/>
+      <c r="AV28" s="25"/>
+      <c r="AW28" s="25"/>
+      <c r="AX28" s="25"/>
+      <c r="AY28" s="25"/>
+      <c r="AZ28" s="25"/>
+      <c r="BA28" s="25"/>
+      <c r="BB28" s="25"/>
+      <c r="BC28" s="25"/>
+      <c r="BD28" s="25"/>
+      <c r="BE28" s="25"/>
+      <c r="BF28" s="26"/>
+    </row>
+    <row r="29" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="25"/>
+      <c r="AI29" s="25"/>
+      <c r="AJ29" s="25"/>
+      <c r="AK29" s="25"/>
+      <c r="AL29" s="25"/>
+      <c r="AM29" s="25"/>
+      <c r="AN29" s="25"/>
+      <c r="AO29" s="25"/>
+      <c r="AP29" s="25"/>
+      <c r="AQ29" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR29" s="25"/>
+      <c r="AS29" s="25"/>
+      <c r="AT29" s="25"/>
+      <c r="AU29" s="25"/>
+      <c r="AV29" s="25"/>
+      <c r="AW29" s="25"/>
+      <c r="AX29" s="25"/>
+      <c r="AY29" s="25"/>
+      <c r="AZ29" s="25"/>
+      <c r="BA29" s="25"/>
+      <c r="BB29" s="25"/>
+      <c r="BC29" s="25"/>
+      <c r="BD29" s="25"/>
+      <c r="BE29" s="25"/>
+      <c r="BF29" s="26"/>
+    </row>
+    <row r="30" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D30" s="24"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+      <c r="AH30" s="25"/>
+      <c r="AI30" s="25"/>
+      <c r="AJ30" s="25"/>
+      <c r="AK30" s="25"/>
+      <c r="AL30" s="25"/>
+      <c r="AM30" s="25"/>
+      <c r="AN30" s="25"/>
+      <c r="AO30" s="25"/>
+      <c r="AP30" s="25"/>
+      <c r="AQ30" s="25"/>
+      <c r="AR30" s="25"/>
+      <c r="AS30" s="25"/>
+      <c r="AT30" s="25"/>
+      <c r="AU30" s="25"/>
+      <c r="AV30" s="25"/>
+      <c r="AW30" s="25"/>
+      <c r="AX30" s="25"/>
+      <c r="AY30" s="25"/>
+      <c r="AZ30" s="25"/>
+      <c r="BA30" s="25"/>
+      <c r="BB30" s="25"/>
+      <c r="BC30" s="25"/>
+      <c r="BD30" s="25"/>
+      <c r="BE30" s="25"/>
+      <c r="BF30" s="26"/>
+    </row>
+    <row r="31" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25"/>
+      <c r="AH31" s="25"/>
+      <c r="AI31" s="25"/>
+      <c r="AJ31" s="25"/>
+      <c r="AK31" s="25"/>
+      <c r="AL31" s="25"/>
+      <c r="AM31" s="25"/>
+      <c r="AN31" s="25"/>
+      <c r="AO31" s="25"/>
+      <c r="AP31" s="25"/>
+      <c r="AQ31" s="25"/>
+      <c r="AR31" s="25"/>
+      <c r="AS31" s="25"/>
+      <c r="AT31" s="25"/>
+      <c r="AU31" s="25"/>
+      <c r="AV31" s="25"/>
+      <c r="AW31" s="25"/>
+      <c r="AX31" s="25"/>
+      <c r="AY31" s="25"/>
+      <c r="AZ31" s="25"/>
+      <c r="BA31" s="25"/>
+      <c r="BB31" s="25"/>
+      <c r="BC31" s="25"/>
+      <c r="BD31" s="25"/>
+      <c r="BE31" s="25"/>
+      <c r="BF31" s="26"/>
+    </row>
+    <row r="32" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+      <c r="W32" s="25"/>
+      <c r="X32" s="25"/>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="25"/>
+      <c r="AA32" s="25"/>
+      <c r="AB32" s="25"/>
+      <c r="AC32" s="25"/>
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="25"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="25"/>
+      <c r="AH32" s="25"/>
+      <c r="AI32" s="25"/>
+      <c r="AJ32" s="25"/>
+      <c r="AK32" s="25"/>
+      <c r="AL32" s="25"/>
+      <c r="AM32" s="25"/>
+      <c r="AN32" s="25"/>
+      <c r="AO32" s="25"/>
+      <c r="AP32" s="25"/>
+      <c r="AQ32" s="25"/>
+      <c r="AR32" s="25"/>
+      <c r="AS32" s="25"/>
+      <c r="AT32" s="25"/>
+      <c r="AU32" s="25"/>
+      <c r="AV32" s="25"/>
+      <c r="AW32" s="25"/>
+      <c r="AX32" s="25"/>
+      <c r="AY32" s="25"/>
+      <c r="AZ32" s="25"/>
+      <c r="BA32" s="25"/>
+      <c r="BB32" s="25"/>
+      <c r="BC32" s="25"/>
+      <c r="BD32" s="25"/>
+      <c r="BE32" s="25"/>
+      <c r="BF32" s="26"/>
+    </row>
+    <row r="33" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="25"/>
+      <c r="AA33" s="25"/>
+      <c r="AB33" s="25"/>
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+      <c r="AH33" s="25"/>
+      <c r="AI33" s="25"/>
+      <c r="AJ33" s="25"/>
+      <c r="AK33" s="25"/>
+      <c r="AL33" s="25"/>
+      <c r="AM33" s="25"/>
+      <c r="AN33" s="25"/>
+      <c r="AO33" s="25"/>
+      <c r="AP33" s="25"/>
+      <c r="AQ33" s="25"/>
+      <c r="AR33" s="25"/>
+      <c r="AS33" s="25"/>
+      <c r="AT33" s="25"/>
+      <c r="AU33" s="25"/>
+      <c r="AV33" s="25"/>
+      <c r="AW33" s="25"/>
+      <c r="AX33" s="25"/>
+      <c r="AY33" s="25"/>
+      <c r="AZ33" s="25"/>
+      <c r="BA33" s="25"/>
+      <c r="BB33" s="25"/>
+      <c r="BC33" s="25"/>
+      <c r="BD33" s="25"/>
+      <c r="BE33" s="25"/>
+      <c r="BF33" s="26"/>
+    </row>
+    <row r="34" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D34" s="24"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="25"/>
+      <c r="AI34" s="25"/>
+      <c r="AJ34" s="25"/>
+      <c r="AK34" s="25"/>
+      <c r="AL34" s="25"/>
+      <c r="AM34" s="25"/>
+      <c r="AN34" s="25"/>
+      <c r="AO34" s="25"/>
+      <c r="AP34" s="25"/>
+      <c r="AQ34" s="25"/>
+      <c r="AR34" s="25"/>
+      <c r="AS34" s="25"/>
+      <c r="AT34" s="25"/>
+      <c r="AU34" s="25"/>
+      <c r="AV34" s="25"/>
+      <c r="AW34" s="25"/>
+      <c r="AX34" s="25"/>
+      <c r="AY34" s="25"/>
+      <c r="AZ34" s="25"/>
+      <c r="BA34" s="25"/>
+      <c r="BB34" s="25"/>
+      <c r="BC34" s="25"/>
+      <c r="BD34" s="25"/>
+      <c r="BE34" s="25"/>
+      <c r="BF34" s="26"/>
+    </row>
+    <row r="35" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D35" s="24"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="25"/>
+      <c r="AA35" s="25"/>
+      <c r="AB35" s="25"/>
+      <c r="AC35" s="25"/>
+      <c r="AD35" s="25"/>
+      <c r="AE35" s="25"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="25"/>
+      <c r="AH35" s="25"/>
+      <c r="AI35" s="25"/>
+      <c r="AJ35" s="25"/>
+      <c r="AK35" s="25"/>
+      <c r="AL35" s="25"/>
+      <c r="AM35" s="25"/>
+      <c r="AN35" s="25"/>
+      <c r="AO35" s="25"/>
+      <c r="AP35" s="25"/>
+      <c r="AQ35" s="25"/>
+      <c r="AR35" s="25"/>
+      <c r="AS35" s="25"/>
+      <c r="AT35" s="25"/>
+      <c r="AU35" s="25"/>
+      <c r="AV35" s="25"/>
+      <c r="AW35" s="25"/>
+      <c r="AX35" s="25"/>
+      <c r="AY35" s="25"/>
+      <c r="AZ35" s="25"/>
+      <c r="BA35" s="25"/>
+      <c r="BB35" s="25"/>
+      <c r="BC35" s="25"/>
+      <c r="BD35" s="25"/>
+      <c r="BE35" s="25"/>
+      <c r="BF35" s="26"/>
+    </row>
+    <row r="36" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D36" s="24"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+      <c r="W36" s="25"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="25"/>
+      <c r="Z36" s="25"/>
+      <c r="AA36" s="25"/>
+      <c r="AB36" s="25"/>
+      <c r="AC36" s="25"/>
+      <c r="AD36" s="25"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="25"/>
+      <c r="AJ36" s="25"/>
+      <c r="AK36" s="25"/>
+      <c r="AL36" s="25"/>
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="25"/>
+      <c r="AO36" s="25"/>
+      <c r="AP36" s="25"/>
+      <c r="AQ36" s="25"/>
+      <c r="AR36" s="25"/>
+      <c r="AS36" s="25"/>
+      <c r="AT36" s="25"/>
+      <c r="AU36" s="25"/>
+      <c r="AV36" s="25"/>
+      <c r="AW36" s="25"/>
+      <c r="AX36" s="25"/>
+      <c r="AY36" s="25"/>
+      <c r="AZ36" s="25"/>
+      <c r="BA36" s="25"/>
+      <c r="BB36" s="25"/>
+      <c r="BC36" s="25"/>
+      <c r="BD36" s="25"/>
+      <c r="BE36" s="25"/>
+      <c r="BF36" s="26"/>
+    </row>
+    <row r="37" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D37" s="24"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
+      <c r="Z37" s="25"/>
+      <c r="AA37" s="25"/>
+      <c r="AB37" s="25"/>
+      <c r="AC37" s="25"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="25"/>
+      <c r="AH37" s="25"/>
+      <c r="AI37" s="25"/>
+      <c r="AJ37" s="25"/>
+      <c r="AK37" s="25"/>
+      <c r="AL37" s="25"/>
+      <c r="AM37" s="25"/>
+      <c r="AN37" s="25"/>
+      <c r="AO37" s="25"/>
+      <c r="AP37" s="25"/>
+      <c r="AQ37" s="25"/>
+      <c r="AR37" s="25"/>
+      <c r="AS37" s="25"/>
+      <c r="AT37" s="25"/>
+      <c r="AU37" s="25"/>
+      <c r="AV37" s="25"/>
+      <c r="AW37" s="25"/>
+      <c r="AX37" s="25"/>
+      <c r="AY37" s="25"/>
+      <c r="AZ37" s="25"/>
+      <c r="BA37" s="25"/>
+      <c r="BB37" s="25"/>
+      <c r="BC37" s="25"/>
+      <c r="BD37" s="25"/>
+      <c r="BE37" s="25"/>
+      <c r="BF37" s="26"/>
+    </row>
+    <row r="38" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D38" s="24"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
+      <c r="Z38" s="25"/>
+      <c r="AA38" s="25"/>
+      <c r="AB38" s="25"/>
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+      <c r="AH38" s="25"/>
+      <c r="AI38" s="25"/>
+      <c r="AJ38" s="25"/>
+      <c r="AK38" s="25"/>
+      <c r="AL38" s="25"/>
+      <c r="AM38" s="25"/>
+      <c r="AN38" s="25"/>
+      <c r="AO38" s="25"/>
+      <c r="AP38" s="25"/>
+      <c r="AQ38" s="25"/>
+      <c r="AR38" s="25"/>
+      <c r="AS38" s="25"/>
+      <c r="AT38" s="25"/>
+      <c r="AU38" s="25"/>
+      <c r="AV38" s="25"/>
+      <c r="AW38" s="25"/>
+      <c r="AX38" s="25"/>
+      <c r="AY38" s="25"/>
+      <c r="AZ38" s="25"/>
+      <c r="BA38" s="25"/>
+      <c r="BB38" s="25"/>
+      <c r="BC38" s="25"/>
+      <c r="BD38" s="25"/>
+      <c r="BE38" s="25"/>
+      <c r="BF38" s="26"/>
+    </row>
+    <row r="39" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D39" s="24"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+      <c r="Z39" s="25"/>
+      <c r="AA39" s="25"/>
+      <c r="AB39" s="25"/>
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+      <c r="AH39" s="25"/>
+      <c r="AI39" s="25"/>
+      <c r="AJ39" s="25"/>
+      <c r="AK39" s="25"/>
+      <c r="AL39" s="25"/>
+      <c r="AM39" s="25"/>
+      <c r="AN39" s="25"/>
+      <c r="AO39" s="25"/>
+      <c r="AP39" s="25"/>
+      <c r="AQ39" s="25"/>
+      <c r="AR39" s="25"/>
+      <c r="AS39" s="25"/>
+      <c r="AT39" s="25"/>
+      <c r="AU39" s="25"/>
+      <c r="AV39" s="25"/>
+      <c r="AW39" s="25"/>
+      <c r="AX39" s="25"/>
+      <c r="AY39" s="25"/>
+      <c r="AZ39" s="25"/>
+      <c r="BA39" s="25"/>
+      <c r="BB39" s="25"/>
+      <c r="BC39" s="25"/>
+      <c r="BD39" s="25"/>
+      <c r="BE39" s="25"/>
+      <c r="BF39" s="26"/>
+    </row>
+    <row r="40" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D40" s="24"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="25"/>
+      <c r="P40" s="25"/>
+      <c r="Q40" s="25"/>
+      <c r="R40" s="25"/>
+      <c r="S40" s="25"/>
+      <c r="T40" s="25"/>
+      <c r="U40" s="25"/>
+      <c r="V40" s="25"/>
+      <c r="W40" s="25"/>
+      <c r="X40" s="25"/>
+      <c r="Y40" s="25"/>
+      <c r="Z40" s="25"/>
+      <c r="AA40" s="25"/>
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="25"/>
+      <c r="AH40" s="25"/>
+      <c r="AI40" s="25"/>
+      <c r="AJ40" s="25"/>
+      <c r="AK40" s="25"/>
+      <c r="AL40" s="25"/>
+      <c r="AM40" s="25"/>
+      <c r="AN40" s="25"/>
+      <c r="AO40" s="25"/>
+      <c r="AP40" s="25"/>
+      <c r="AQ40" s="25"/>
+      <c r="AR40" s="25"/>
+      <c r="AS40" s="25"/>
+      <c r="AT40" s="25"/>
+      <c r="AU40" s="25"/>
+      <c r="AV40" s="25"/>
+      <c r="AW40" s="25"/>
+      <c r="AX40" s="25"/>
+      <c r="AY40" s="25"/>
+      <c r="AZ40" s="25"/>
+      <c r="BA40" s="25"/>
+      <c r="BB40" s="25"/>
+      <c r="BC40" s="25"/>
+      <c r="BD40" s="25"/>
+      <c r="BE40" s="25"/>
+      <c r="BF40" s="26"/>
+    </row>
+    <row r="41" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D41" s="24"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="25"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="25"/>
+      <c r="R41" s="25"/>
+      <c r="S41" s="25"/>
+      <c r="T41" s="25"/>
+      <c r="U41" s="25"/>
+      <c r="V41" s="25"/>
+      <c r="W41" s="25"/>
+      <c r="X41" s="25"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="25"/>
+      <c r="AA41" s="25"/>
+      <c r="AB41" s="25"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="25"/>
+      <c r="AH41" s="25"/>
+      <c r="AI41" s="25"/>
+      <c r="AJ41" s="25"/>
+      <c r="AK41" s="25"/>
+      <c r="AL41" s="25"/>
+      <c r="AM41" s="25"/>
+      <c r="AN41" s="25"/>
+      <c r="AO41" s="25"/>
+      <c r="AP41" s="25"/>
+      <c r="AQ41" s="25"/>
+      <c r="AR41" s="25"/>
+      <c r="AS41" s="25"/>
+      <c r="AT41" s="25"/>
+      <c r="AU41" s="25"/>
+      <c r="AV41" s="25"/>
+      <c r="AW41" s="25"/>
+      <c r="AX41" s="25"/>
+      <c r="AY41" s="25"/>
+      <c r="AZ41" s="25"/>
+      <c r="BA41" s="25"/>
+      <c r="BB41" s="25"/>
+      <c r="BC41" s="25"/>
+      <c r="BD41" s="25"/>
+      <c r="BE41" s="25"/>
+      <c r="BF41" s="26"/>
+    </row>
+    <row r="42" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D42" s="24"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="25"/>
+      <c r="R42" s="25"/>
+      <c r="S42" s="25"/>
+      <c r="T42" s="25"/>
+      <c r="U42" s="25"/>
+      <c r="V42" s="25"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="25"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="25"/>
+      <c r="AI42" s="25"/>
+      <c r="AJ42" s="25"/>
+      <c r="AK42" s="25"/>
+      <c r="AL42" s="25"/>
+      <c r="AM42" s="25"/>
+      <c r="AN42" s="25"/>
+      <c r="AO42" s="25"/>
+      <c r="AP42" s="25"/>
+      <c r="AQ42" s="25"/>
+      <c r="AR42" s="25"/>
+      <c r="AS42" s="25"/>
+      <c r="AT42" s="25"/>
+      <c r="AU42" s="25"/>
+      <c r="AV42" s="25"/>
+      <c r="AW42" s="25"/>
+      <c r="AX42" s="25"/>
+      <c r="AY42" s="25"/>
+      <c r="AZ42" s="25"/>
+      <c r="BA42" s="25"/>
+      <c r="BB42" s="25"/>
+      <c r="BC42" s="25"/>
+      <c r="BD42" s="25"/>
+      <c r="BE42" s="25"/>
+      <c r="BF42" s="26"/>
+    </row>
+    <row r="43" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D43" s="24"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="25"/>
+      <c r="P43" s="25"/>
+      <c r="Q43" s="25"/>
+      <c r="R43" s="25"/>
+      <c r="S43" s="25"/>
+      <c r="T43" s="25"/>
+      <c r="U43" s="25"/>
+      <c r="V43" s="25"/>
+      <c r="W43" s="25"/>
+      <c r="X43" s="25"/>
+      <c r="Y43" s="25"/>
+      <c r="Z43" s="25"/>
+      <c r="AA43" s="25"/>
+      <c r="AB43" s="25"/>
+      <c r="AC43" s="25"/>
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="25"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="25"/>
+      <c r="AH43" s="25"/>
+      <c r="AI43" s="25"/>
+      <c r="AJ43" s="25"/>
+      <c r="AK43" s="25"/>
+      <c r="AL43" s="25"/>
+      <c r="AM43" s="25"/>
+      <c r="AN43" s="25"/>
+      <c r="AO43" s="25"/>
+      <c r="AP43" s="25"/>
+      <c r="AQ43" s="25"/>
+      <c r="AR43" s="25"/>
+      <c r="AS43" s="25"/>
+      <c r="AT43" s="25"/>
+      <c r="AU43" s="25"/>
+      <c r="AV43" s="25"/>
+      <c r="AW43" s="25"/>
+      <c r="AX43" s="25"/>
+      <c r="AY43" s="25"/>
+      <c r="AZ43" s="25"/>
+      <c r="BA43" s="25"/>
+      <c r="BB43" s="25"/>
+      <c r="BC43" s="25"/>
+      <c r="BD43" s="25"/>
+      <c r="BE43" s="25"/>
+      <c r="BF43" s="26"/>
+    </row>
+    <row r="44" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D44" s="24"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="25"/>
+      <c r="P44" s="25"/>
+      <c r="Q44" s="25"/>
+      <c r="R44" s="25"/>
+      <c r="S44" s="25"/>
+      <c r="T44" s="25"/>
+      <c r="U44" s="25"/>
+      <c r="V44" s="25"/>
+      <c r="W44" s="25"/>
+      <c r="X44" s="25"/>
+      <c r="Y44" s="25"/>
+      <c r="Z44" s="25"/>
+      <c r="AA44" s="25"/>
+      <c r="AB44" s="25"/>
+      <c r="AC44" s="25"/>
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="25"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="25"/>
+      <c r="AH44" s="25"/>
+      <c r="AI44" s="25"/>
+      <c r="AJ44" s="25"/>
+      <c r="AK44" s="25"/>
+      <c r="AL44" s="25"/>
+      <c r="AM44" s="25"/>
+      <c r="AN44" s="25"/>
+      <c r="AO44" s="25"/>
+      <c r="AP44" s="25"/>
+      <c r="AQ44" s="25"/>
+      <c r="AR44" s="25"/>
+      <c r="AS44" s="25"/>
+      <c r="AT44" s="25"/>
+      <c r="AU44" s="25"/>
+      <c r="AV44" s="25"/>
+      <c r="AW44" s="25"/>
+      <c r="AX44" s="25"/>
+      <c r="AY44" s="25"/>
+      <c r="AZ44" s="25"/>
+      <c r="BA44" s="25"/>
+      <c r="BB44" s="25"/>
+      <c r="BC44" s="25"/>
+      <c r="BD44" s="25"/>
+      <c r="BE44" s="25"/>
+      <c r="BF44" s="26"/>
+    </row>
+    <row r="45" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D45" s="24"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="25"/>
+      <c r="R45" s="25"/>
+      <c r="S45" s="25"/>
+      <c r="T45" s="25"/>
+      <c r="U45" s="25"/>
+      <c r="V45" s="25"/>
+      <c r="W45" s="25"/>
+      <c r="X45" s="25"/>
+      <c r="Y45" s="25"/>
+      <c r="Z45" s="25"/>
+      <c r="AA45" s="25"/>
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="25"/>
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="25"/>
+      <c r="AH45" s="25"/>
+      <c r="AI45" s="25"/>
+      <c r="AJ45" s="25"/>
+      <c r="AK45" s="25"/>
+      <c r="AL45" s="25"/>
+      <c r="AM45" s="25"/>
+      <c r="AN45" s="25"/>
+      <c r="AO45" s="25"/>
+      <c r="AP45" s="25"/>
+      <c r="AQ45" s="25"/>
+      <c r="AR45" s="25"/>
+      <c r="AS45" s="25"/>
+      <c r="AT45" s="25"/>
+      <c r="AU45" s="25"/>
+      <c r="AV45" s="25"/>
+      <c r="AW45" s="25"/>
+      <c r="AX45" s="25"/>
+      <c r="AY45" s="25"/>
+      <c r="AZ45" s="25"/>
+      <c r="BA45" s="25"/>
+      <c r="BB45" s="25"/>
+      <c r="BC45" s="25"/>
+      <c r="BD45" s="25"/>
+      <c r="BE45" s="25"/>
+      <c r="BF45" s="26"/>
+    </row>
+    <row r="46" spans="4:58" x14ac:dyDescent="0.4">
+      <c r="D46" s="27"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
+      <c r="AC46" s="28"/>
+      <c r="AD46" s="28"/>
+      <c r="AE46" s="28"/>
+      <c r="AF46" s="28"/>
+      <c r="AG46" s="28"/>
+      <c r="AH46" s="28"/>
+      <c r="AI46" s="28"/>
+      <c r="AJ46" s="28"/>
+      <c r="AK46" s="28"/>
+      <c r="AL46" s="28"/>
+      <c r="AM46" s="28"/>
+      <c r="AN46" s="28"/>
+      <c r="AO46" s="28"/>
+      <c r="AP46" s="28"/>
+      <c r="AQ46" s="28"/>
+      <c r="AR46" s="28"/>
+      <c r="AS46" s="28"/>
+      <c r="AT46" s="28"/>
+      <c r="AU46" s="28"/>
+      <c r="AV46" s="28"/>
+      <c r="AW46" s="28"/>
+      <c r="AX46" s="28"/>
+      <c r="AY46" s="28"/>
+      <c r="AZ46" s="28"/>
+      <c r="BA46" s="28"/>
+      <c r="BB46" s="28"/>
+      <c r="BC46" s="28"/>
+      <c r="BD46" s="28"/>
+      <c r="BE46" s="28"/>
+      <c r="BF46" s="29"/>
+    </row>
+    <row r="52" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C62" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="22"/>
+      <c r="O62" s="22"/>
+      <c r="P62" s="22"/>
+      <c r="Q62" s="22"/>
+      <c r="R62" s="22"/>
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
+      <c r="U62" s="22"/>
+      <c r="V62" s="22"/>
+      <c r="W62" s="22"/>
+      <c r="X62" s="22"/>
+      <c r="Y62" s="22"/>
+      <c r="Z62" s="22"/>
+      <c r="AA62" s="23"/>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C63" s="24"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="25"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="25"/>
+      <c r="N63" s="25"/>
+      <c r="O63" s="25"/>
+      <c r="P63" s="25"/>
+      <c r="Q63" s="25"/>
+      <c r="R63" s="25"/>
+      <c r="S63" s="25"/>
+      <c r="T63" s="25"/>
+      <c r="U63" s="25"/>
+      <c r="V63" s="25"/>
+      <c r="W63" s="25"/>
+      <c r="X63" s="25"/>
+      <c r="Y63" s="25"/>
+      <c r="Z63" s="25"/>
+      <c r="AA63" s="26"/>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C64" s="24"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="25"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="25"/>
+      <c r="N64" s="25"/>
+      <c r="O64" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="P64" s="25"/>
+      <c r="Q64" s="25"/>
+      <c r="R64" s="25"/>
+      <c r="S64" s="25"/>
+      <c r="T64" s="25"/>
+      <c r="U64" s="25"/>
+      <c r="V64" s="25"/>
+      <c r="W64" s="25"/>
+      <c r="X64" s="25"/>
+      <c r="Y64" s="25"/>
+      <c r="Z64" s="25"/>
+      <c r="AA64" s="26"/>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C65" s="24"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="25"/>
+      <c r="L65" s="25"/>
+      <c r="M65" s="25"/>
+      <c r="N65" s="25"/>
+      <c r="O65" s="25"/>
+      <c r="P65" s="25"/>
+      <c r="Q65" s="25"/>
+      <c r="R65" s="25"/>
+      <c r="S65" s="25"/>
+      <c r="T65" s="25"/>
+      <c r="U65" s="25"/>
+      <c r="V65" s="25"/>
+      <c r="W65" s="25"/>
+      <c r="X65" s="25"/>
+      <c r="Y65" s="25"/>
+      <c r="Z65" s="25"/>
+      <c r="AA65" s="26"/>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C66" s="24"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="25"/>
+      <c r="L66" s="25"/>
+      <c r="M66" s="25"/>
+      <c r="N66" s="25"/>
+      <c r="O66" s="25"/>
+      <c r="P66" s="25"/>
+      <c r="Q66" s="25"/>
+      <c r="R66" s="25"/>
+      <c r="S66" s="25"/>
+      <c r="T66" s="25"/>
+      <c r="U66" s="25"/>
+      <c r="V66" s="25"/>
+      <c r="W66" s="25"/>
+      <c r="X66" s="25"/>
+      <c r="Y66" s="25"/>
+      <c r="Z66" s="25"/>
+      <c r="AA66" s="26"/>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C67" s="24"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="K67" s="25"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
+      <c r="N67" s="25"/>
+      <c r="O67" s="25"/>
+      <c r="P67" s="25"/>
+      <c r="Q67" s="25"/>
+      <c r="R67" s="25"/>
+      <c r="S67" s="25"/>
+      <c r="T67" s="25"/>
+      <c r="U67" s="25"/>
+      <c r="V67" s="25"/>
+      <c r="W67" s="25"/>
+      <c r="X67" s="25"/>
+      <c r="Y67" s="25"/>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="26"/>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C68" s="24"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="25"/>
+      <c r="L68" s="25"/>
+      <c r="M68" s="25"/>
+      <c r="N68" s="25"/>
+      <c r="O68" s="25"/>
+      <c r="P68" s="25"/>
+      <c r="Q68" s="25"/>
+      <c r="R68" s="25"/>
+      <c r="S68" s="25"/>
+      <c r="T68" s="25"/>
+      <c r="U68" s="25"/>
+      <c r="V68" s="25"/>
+      <c r="W68" s="25"/>
+      <c r="X68" s="25"/>
+      <c r="Y68" s="25"/>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="26"/>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C69" s="24"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="25"/>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="25"/>
+      <c r="O69" s="25"/>
+      <c r="P69" s="25"/>
+      <c r="Q69" s="25"/>
+      <c r="R69" s="25"/>
+      <c r="S69" s="25"/>
+      <c r="T69" s="25"/>
+      <c r="U69" s="25"/>
+      <c r="V69" s="25"/>
+      <c r="W69" s="25"/>
+      <c r="X69" s="25"/>
+      <c r="Y69" s="25"/>
+      <c r="Z69" s="25"/>
+      <c r="AA69" s="26"/>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C70" s="24"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="25"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="25"/>
+      <c r="O70" s="25"/>
+      <c r="P70" s="25"/>
+      <c r="Q70" s="25"/>
+      <c r="R70" s="25"/>
+      <c r="S70" s="25"/>
+      <c r="T70" s="25"/>
+      <c r="U70" s="25"/>
+      <c r="V70" s="25"/>
+      <c r="W70" s="25"/>
+      <c r="X70" s="25"/>
+      <c r="Y70" s="25"/>
+      <c r="Z70" s="25"/>
+      <c r="AA70" s="26"/>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C71" s="24"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25"/>
+      <c r="I71" s="25"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="25"/>
+      <c r="L71" s="25"/>
+      <c r="M71" s="25"/>
+      <c r="N71" s="25"/>
+      <c r="O71" s="25"/>
+      <c r="P71" s="25"/>
+      <c r="Q71" s="25"/>
+      <c r="R71" s="25"/>
+      <c r="S71" s="25"/>
+      <c r="T71" s="25"/>
+      <c r="U71" s="25"/>
+      <c r="V71" s="25"/>
+      <c r="W71" s="25"/>
+      <c r="X71" s="25"/>
+      <c r="Y71" s="25"/>
+      <c r="Z71" s="25"/>
+      <c r="AA71" s="26"/>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C72" s="24"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="25"/>
+      <c r="L72" s="25"/>
+      <c r="M72" s="25"/>
+      <c r="N72" s="25"/>
+      <c r="O72" s="25"/>
+      <c r="P72" s="25"/>
+      <c r="Q72" s="25"/>
+      <c r="R72" s="25"/>
+      <c r="S72" s="25"/>
+      <c r="T72" s="25"/>
+      <c r="U72" s="25"/>
+      <c r="V72" s="25"/>
+      <c r="W72" s="25"/>
+      <c r="X72" s="25"/>
+      <c r="Y72" s="25"/>
+      <c r="Z72" s="25"/>
+      <c r="AA72" s="26"/>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C73" s="24"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="25"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
+      <c r="N73" s="25"/>
+      <c r="O73" s="25"/>
+      <c r="P73" s="25"/>
+      <c r="Q73" s="25"/>
+      <c r="R73" s="25"/>
+      <c r="S73" s="25"/>
+      <c r="T73" s="25"/>
+      <c r="U73" s="25"/>
+      <c r="V73" s="25"/>
+      <c r="W73" s="25"/>
+      <c r="X73" s="25"/>
+      <c r="Y73" s="25"/>
+      <c r="Z73" s="25"/>
+      <c r="AA73" s="26"/>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C74" s="24"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
+      <c r="M74" s="25"/>
+      <c r="N74" s="25"/>
+      <c r="O74" s="25"/>
+      <c r="P74" s="25"/>
+      <c r="Q74" s="25"/>
+      <c r="R74" s="25"/>
+      <c r="S74" s="25"/>
+      <c r="T74" s="25"/>
+      <c r="U74" s="25"/>
+      <c r="V74" s="25"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
+      <c r="Z74" s="25"/>
+      <c r="AA74" s="26"/>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C75" s="27"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="28"/>
+      <c r="J75" s="28"/>
+      <c r="K75" s="28"/>
+      <c r="L75" s="28"/>
+      <c r="M75" s="28"/>
+      <c r="N75" s="28"/>
+      <c r="O75" s="28"/>
+      <c r="P75" s="28"/>
+      <c r="Q75" s="28"/>
+      <c r="R75" s="28"/>
+      <c r="S75" s="28"/>
+      <c r="T75" s="28"/>
+      <c r="U75" s="28"/>
+      <c r="V75" s="28"/>
+      <c r="W75" s="28"/>
+      <c r="X75" s="28"/>
+      <c r="Y75" s="28"/>
+      <c r="Z75" s="28"/>
+      <c r="AA75" s="29"/>
+    </row>
+    <row r="79" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="3" t="s">
+        <v>219</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Docker_週報作成.xlsx
+++ b/Docker_週報作成.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ITI202302009\Documents\weeklyreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D461B16A-2FB5-4D29-A533-808187A5F671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CFC613-0F2E-4065-8C19-B700F8C14490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="7" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
+    <workbookView xWindow="-2310" yWindow="2490" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="7" xr2:uid="{949BA286-AB55-4D12-A7D1-44CDAE0F455A}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="6" r:id="rId1"/>
@@ -1740,7 +1740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1814,9 +1814,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
@@ -10045,7 +10042,7 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>登録・削除処理</a:t>
+            <a:t>登録・更新処理</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
@@ -10070,14 +10067,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>216993</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>45785</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>86031</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>145676</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>100852</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>187817</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>147572</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10092,8 +10089,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1897875" y="14030726"/>
-          <a:ext cx="1609566" cy="660185"/>
+          <a:off x="1907345" y="16667580"/>
+          <a:ext cx="2506352" cy="665238"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartInputOutput">
           <a:avLst/>
@@ -10118,15 +10115,33 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Department_cd</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Department_name</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -14240,1786 +14255,204 @@
     </row>
     <row r="16" spans="1:58" x14ac:dyDescent="0.4">
       <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="25"/>
-      <c r="AC16" s="25"/>
-      <c r="AD16" s="25"/>
-      <c r="AE16" s="25"/>
-      <c r="AF16" s="25"/>
-      <c r="AG16" s="25"/>
-      <c r="AH16" s="25"/>
-      <c r="AI16" s="25"/>
-      <c r="AJ16" s="25"/>
-      <c r="AK16" s="25"/>
-      <c r="AL16" s="25"/>
-      <c r="AM16" s="25"/>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="25"/>
-      <c r="AP16" s="25"/>
-      <c r="AQ16" s="25"/>
-      <c r="AR16" s="25"/>
-      <c r="AS16" s="25"/>
-      <c r="AT16" s="25"/>
-      <c r="AU16" s="25"/>
-      <c r="AV16" s="25"/>
-      <c r="AW16" s="25"/>
-      <c r="AX16" s="25"/>
-      <c r="AY16" s="25"/>
-      <c r="AZ16" s="25"/>
-      <c r="BA16" s="25"/>
-      <c r="BB16" s="25"/>
-      <c r="BC16" s="25"/>
-      <c r="BD16" s="25"/>
-      <c r="BE16" s="25"/>
-      <c r="BF16" s="26"/>
+      <c r="BF16" s="25"/>
     </row>
     <row r="17" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D17" s="24"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="25"/>
-      <c r="AE17" s="25"/>
-      <c r="AF17" s="25"/>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="25"/>
-      <c r="AI17" s="25"/>
-      <c r="AJ17" s="25"/>
-      <c r="AK17" s="25"/>
-      <c r="AL17" s="25"/>
-      <c r="AM17" s="25"/>
-      <c r="AN17" s="25"/>
-      <c r="AO17" s="25"/>
-      <c r="AP17" s="25"/>
-      <c r="AQ17" s="25"/>
-      <c r="AR17" s="25"/>
-      <c r="AS17" s="25"/>
-      <c r="AT17" s="25"/>
-      <c r="AU17" s="25"/>
-      <c r="AV17" s="25"/>
-      <c r="AW17" s="25"/>
-      <c r="AX17" s="25"/>
-      <c r="AY17" s="25"/>
-      <c r="AZ17" s="25"/>
-      <c r="BA17" s="25"/>
-      <c r="BB17" s="25"/>
-      <c r="BC17" s="25"/>
-      <c r="BD17" s="25"/>
-      <c r="BE17" s="25"/>
-      <c r="BF17" s="26"/>
+      <c r="BF17" s="25"/>
     </row>
     <row r="18" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D18" s="24"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25" t="s">
+      <c r="P18" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-      <c r="V18" s="25"/>
-      <c r="W18" s="25"/>
-      <c r="X18" s="25"/>
-      <c r="Y18" s="25"/>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="25"/>
-      <c r="AB18" s="25"/>
-      <c r="AC18" s="25"/>
-      <c r="AD18" s="25"/>
-      <c r="AE18" s="25"/>
-      <c r="AF18" s="25"/>
-      <c r="AG18" s="25"/>
-      <c r="AH18" s="25"/>
-      <c r="AI18" s="25"/>
-      <c r="AJ18" s="25"/>
-      <c r="AK18" s="25"/>
-      <c r="AL18" s="25"/>
-      <c r="AM18" s="25"/>
-      <c r="AN18" s="25"/>
-      <c r="AO18" s="25"/>
-      <c r="AP18" s="25"/>
-      <c r="AQ18" s="25"/>
-      <c r="AR18" s="25"/>
-      <c r="AS18" s="25"/>
-      <c r="AT18" s="25"/>
-      <c r="AU18" s="25"/>
-      <c r="AV18" s="25"/>
-      <c r="AW18" s="25"/>
-      <c r="AX18" s="25"/>
-      <c r="AY18" s="25"/>
-      <c r="AZ18" s="25"/>
-      <c r="BA18" s="25"/>
-      <c r="BB18" s="25"/>
-      <c r="BC18" s="25"/>
-      <c r="BD18" s="25"/>
-      <c r="BE18" s="25"/>
-      <c r="BF18" s="26"/>
+      <c r="BF18" s="25"/>
     </row>
     <row r="19" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="25"/>
-      <c r="W19" s="25"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="25"/>
-      <c r="AA19" s="25"/>
-      <c r="AB19" s="25"/>
-      <c r="AC19" s="25"/>
-      <c r="AD19" s="25"/>
-      <c r="AE19" s="25"/>
-      <c r="AF19" s="25"/>
-      <c r="AG19" s="25"/>
-      <c r="AH19" s="25"/>
-      <c r="AI19" s="25"/>
-      <c r="AJ19" s="25"/>
-      <c r="AK19" s="25"/>
-      <c r="AL19" s="25"/>
-      <c r="AM19" s="25"/>
-      <c r="AN19" s="25"/>
-      <c r="AO19" s="25"/>
-      <c r="AP19" s="25"/>
-      <c r="AQ19" s="25"/>
-      <c r="AR19" s="25"/>
-      <c r="AS19" s="25"/>
-      <c r="AT19" s="25"/>
-      <c r="AU19" s="25"/>
-      <c r="AV19" s="25"/>
-      <c r="AW19" s="25"/>
-      <c r="AX19" s="25"/>
-      <c r="AY19" s="25"/>
-      <c r="AZ19" s="25"/>
-      <c r="BA19" s="25"/>
-      <c r="BB19" s="25"/>
-      <c r="BC19" s="25"/>
-      <c r="BD19" s="25"/>
-      <c r="BE19" s="25"/>
-      <c r="BF19" s="26"/>
+      <c r="BF19" s="25"/>
     </row>
     <row r="20" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="25"/>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
-      <c r="V20" s="25"/>
-      <c r="W20" s="25"/>
-      <c r="X20" s="25"/>
-      <c r="Y20" s="25"/>
-      <c r="Z20" s="25"/>
-      <c r="AA20" s="25"/>
-      <c r="AB20" s="25"/>
-      <c r="AC20" s="25"/>
-      <c r="AD20" s="25"/>
-      <c r="AE20" s="25"/>
-      <c r="AF20" s="25"/>
-      <c r="AG20" s="25"/>
-      <c r="AH20" s="25"/>
-      <c r="AI20" s="25"/>
-      <c r="AJ20" s="25"/>
-      <c r="AK20" s="25"/>
-      <c r="AL20" s="25"/>
-      <c r="AM20" s="25"/>
-      <c r="AN20" s="25"/>
-      <c r="AO20" s="25"/>
-      <c r="AP20" s="25"/>
-      <c r="AQ20" s="25"/>
-      <c r="AR20" s="25"/>
-      <c r="AS20" s="25"/>
-      <c r="AT20" s="25"/>
-      <c r="AU20" s="25"/>
-      <c r="AV20" s="25"/>
-      <c r="AW20" s="25"/>
-      <c r="AX20" s="25"/>
-      <c r="AY20" s="25"/>
-      <c r="AZ20" s="25"/>
-      <c r="BA20" s="25"/>
-      <c r="BB20" s="25"/>
-      <c r="BC20" s="25"/>
-      <c r="BD20" s="25"/>
-      <c r="BE20" s="25"/>
-      <c r="BF20" s="26"/>
+      <c r="BF20" s="25"/>
     </row>
     <row r="21" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="25"/>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="25"/>
-      <c r="AC21" s="25"/>
-      <c r="AD21" s="25"/>
-      <c r="AE21" s="25"/>
-      <c r="AF21" s="25"/>
-      <c r="AG21" s="25"/>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="25"/>
-      <c r="AJ21" s="25"/>
-      <c r="AK21" s="25"/>
-      <c r="AL21" s="25"/>
-      <c r="AM21" s="25"/>
-      <c r="AN21" s="25"/>
-      <c r="AO21" s="25"/>
-      <c r="AP21" s="25"/>
-      <c r="AQ21" s="25"/>
-      <c r="AR21" s="25"/>
-      <c r="AS21" s="25"/>
-      <c r="AT21" s="25"/>
-      <c r="AU21" s="25"/>
-      <c r="AV21" s="25"/>
-      <c r="AW21" s="25"/>
-      <c r="AX21" s="25"/>
-      <c r="AY21" s="25"/>
-      <c r="AZ21" s="25"/>
-      <c r="BA21" s="25"/>
-      <c r="BB21" s="25"/>
-      <c r="BC21" s="25"/>
-      <c r="BD21" s="25"/>
-      <c r="BE21" s="25"/>
-      <c r="BF21" s="26"/>
+      <c r="BF21" s="25"/>
     </row>
     <row r="22" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D22" s="24"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="25"/>
-      <c r="AJ22" s="25"/>
-      <c r="AK22" s="25"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25"/>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
-      <c r="AQ22" s="25"/>
-      <c r="AR22" s="25"/>
-      <c r="AS22" s="25"/>
-      <c r="AT22" s="25"/>
-      <c r="AU22" s="25"/>
-      <c r="AV22" s="25"/>
-      <c r="AW22" s="25"/>
-      <c r="AX22" s="25"/>
-      <c r="AY22" s="25"/>
-      <c r="AZ22" s="25"/>
-      <c r="BA22" s="25"/>
-      <c r="BB22" s="25"/>
-      <c r="BC22" s="25"/>
-      <c r="BD22" s="25"/>
-      <c r="BE22" s="25"/>
-      <c r="BF22" s="26"/>
+      <c r="BF22" s="25"/>
     </row>
     <row r="23" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D23" s="24"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25"/>
-      <c r="AB23" s="25"/>
-      <c r="AC23" s="25"/>
-      <c r="AD23" s="25"/>
-      <c r="AE23" s="25"/>
-      <c r="AF23" s="25"/>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="25"/>
-      <c r="AJ23" s="25"/>
-      <c r="AK23" s="25"/>
-      <c r="AL23" s="25"/>
-      <c r="AM23" s="25"/>
-      <c r="AN23" s="25"/>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="25"/>
-      <c r="AT23" s="25"/>
-      <c r="AU23" s="25"/>
-      <c r="AV23" s="25"/>
-      <c r="AW23" s="25"/>
-      <c r="AX23" s="25"/>
-      <c r="AY23" s="25"/>
-      <c r="AZ23" s="25"/>
-      <c r="BA23" s="25"/>
-      <c r="BB23" s="25"/>
-      <c r="BC23" s="25"/>
-      <c r="BD23" s="25"/>
-      <c r="BE23" s="25"/>
-      <c r="BF23" s="26"/>
+      <c r="BF23" s="25"/>
     </row>
     <row r="24" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D24" s="24"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="25"/>
-      <c r="AB24" s="25"/>
-      <c r="AC24" s="25"/>
-      <c r="AD24" s="25"/>
-      <c r="AE24" s="25"/>
-      <c r="AF24" s="25"/>
-      <c r="AG24" s="25"/>
-      <c r="AH24" s="25"/>
-      <c r="AI24" s="25"/>
-      <c r="AJ24" s="25"/>
-      <c r="AK24" s="25"/>
-      <c r="AL24" s="25"/>
-      <c r="AM24" s="25"/>
-      <c r="AN24" s="25"/>
-      <c r="AO24" s="25"/>
-      <c r="AP24" s="25"/>
-      <c r="AQ24" s="25"/>
-      <c r="AR24" s="25"/>
-      <c r="AS24" s="25"/>
-      <c r="AT24" s="25"/>
-      <c r="AU24" s="25"/>
-      <c r="AV24" s="25"/>
-      <c r="AW24" s="25"/>
-      <c r="AX24" s="25"/>
-      <c r="AY24" s="25"/>
-      <c r="AZ24" s="25"/>
-      <c r="BA24" s="25"/>
-      <c r="BB24" s="25"/>
-      <c r="BC24" s="25"/>
-      <c r="BD24" s="25"/>
-      <c r="BE24" s="25"/>
-      <c r="BF24" s="26"/>
+      <c r="BF24" s="25"/>
     </row>
     <row r="25" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D25" s="24"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="25"/>
-      <c r="Y25" s="25"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="25"/>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
-      <c r="AF25" s="25"/>
-      <c r="AG25" s="25"/>
-      <c r="AH25" s="25"/>
-      <c r="AI25" s="25"/>
-      <c r="AJ25" s="25"/>
-      <c r="AK25" s="25"/>
-      <c r="AL25" s="25"/>
-      <c r="AM25" s="25"/>
-      <c r="AN25" s="25"/>
-      <c r="AO25" s="25"/>
-      <c r="AP25" s="25"/>
-      <c r="AQ25" s="25"/>
-      <c r="AR25" s="25"/>
-      <c r="AS25" s="25"/>
-      <c r="AT25" s="25"/>
-      <c r="AU25" s="25"/>
-      <c r="AV25" s="25"/>
-      <c r="AW25" s="25" t="s">
+      <c r="AW25" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AX25" s="25"/>
-      <c r="AY25" s="25"/>
-      <c r="AZ25" s="25"/>
-      <c r="BA25" s="25"/>
-      <c r="BB25" s="25"/>
-      <c r="BC25" s="25"/>
-      <c r="BD25" s="25"/>
-      <c r="BE25" s="25"/>
-      <c r="BF25" s="26"/>
+      <c r="BF25" s="25"/>
     </row>
     <row r="26" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D26" s="24"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="25"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="25"/>
-      <c r="X26" s="25"/>
-      <c r="Y26" s="25"/>
-      <c r="Z26" s="25"/>
-      <c r="AA26" s="25"/>
-      <c r="AB26" s="25"/>
-      <c r="AC26" s="25"/>
-      <c r="AD26" s="25"/>
-      <c r="AE26" s="25"/>
-      <c r="AF26" s="25"/>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="25"/>
-      <c r="AJ26" s="25"/>
-      <c r="AK26" s="25"/>
-      <c r="AL26" s="25"/>
-      <c r="AM26" s="25"/>
-      <c r="AN26" s="25"/>
-      <c r="AO26" s="25"/>
-      <c r="AP26" s="25"/>
-      <c r="AQ26" s="25"/>
-      <c r="AR26" s="25"/>
-      <c r="AS26" s="25"/>
-      <c r="AT26" s="25"/>
-      <c r="AU26" s="25"/>
-      <c r="AV26" s="25"/>
-      <c r="AW26" s="25"/>
-      <c r="AX26" s="25"/>
-      <c r="AY26" s="25"/>
-      <c r="AZ26" s="25"/>
-      <c r="BA26" s="25"/>
-      <c r="BB26" s="25"/>
-      <c r="BC26" s="25"/>
-      <c r="BD26" s="25"/>
-      <c r="BE26" s="25"/>
-      <c r="BF26" s="26"/>
+      <c r="BF26" s="25"/>
     </row>
     <row r="27" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D27" s="24"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="25"/>
-      <c r="X27" s="25"/>
-      <c r="Y27" s="25"/>
-      <c r="Z27" s="25"/>
-      <c r="AA27" s="25"/>
-      <c r="AB27" s="25"/>
-      <c r="AC27" s="25"/>
-      <c r="AD27" s="25"/>
-      <c r="AE27" s="25"/>
-      <c r="AF27" s="25"/>
-      <c r="AG27" s="25"/>
-      <c r="AH27" s="25"/>
-      <c r="AI27" s="25"/>
-      <c r="AJ27" s="25"/>
-      <c r="AK27" s="25"/>
-      <c r="AL27" s="25"/>
-      <c r="AM27" s="25"/>
-      <c r="AN27" s="25"/>
-      <c r="AO27" s="25"/>
-      <c r="AP27" s="25"/>
-      <c r="AQ27" s="25"/>
-      <c r="AR27" s="25"/>
-      <c r="AS27" s="25"/>
-      <c r="AT27" s="25"/>
-      <c r="AU27" s="25"/>
-      <c r="AV27" s="25"/>
-      <c r="AW27" s="25"/>
-      <c r="AX27" s="25"/>
-      <c r="AY27" s="25"/>
-      <c r="AZ27" s="25"/>
-      <c r="BA27" s="25"/>
-      <c r="BB27" s="25"/>
-      <c r="BC27" s="25"/>
-      <c r="BD27" s="25"/>
-      <c r="BE27" s="25"/>
-      <c r="BF27" s="26"/>
+      <c r="BF27" s="25"/>
     </row>
     <row r="28" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D28" s="24"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="25"/>
-      <c r="AB28" s="25"/>
-      <c r="AC28" s="25"/>
-      <c r="AD28" s="25"/>
-      <c r="AE28" s="25"/>
-      <c r="AF28" s="25"/>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="25"/>
-      <c r="AI28" s="25"/>
-      <c r="AJ28" s="25"/>
-      <c r="AK28" s="25"/>
-      <c r="AL28" s="25"/>
-      <c r="AM28" s="25"/>
-      <c r="AN28" s="25"/>
-      <c r="AO28" s="25"/>
-      <c r="AP28" s="25"/>
-      <c r="AQ28" s="25"/>
-      <c r="AR28" s="25"/>
-      <c r="AS28" s="25"/>
-      <c r="AT28" s="25"/>
-      <c r="AU28" s="25"/>
-      <c r="AV28" s="25"/>
-      <c r="AW28" s="25"/>
-      <c r="AX28" s="25"/>
-      <c r="AY28" s="25"/>
-      <c r="AZ28" s="25"/>
-      <c r="BA28" s="25"/>
-      <c r="BB28" s="25"/>
-      <c r="BC28" s="25"/>
-      <c r="BD28" s="25"/>
-      <c r="BE28" s="25"/>
-      <c r="BF28" s="26"/>
+      <c r="BF28" s="25"/>
     </row>
     <row r="29" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="25"/>
-      <c r="X29" s="25"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
-      <c r="AC29" s="25"/>
-      <c r="AD29" s="25"/>
-      <c r="AE29" s="25"/>
-      <c r="AF29" s="25"/>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="25"/>
-      <c r="AJ29" s="25"/>
-      <c r="AK29" s="25"/>
-      <c r="AL29" s="25"/>
-      <c r="AM29" s="25"/>
-      <c r="AN29" s="25"/>
-      <c r="AO29" s="25"/>
-      <c r="AP29" s="25"/>
-      <c r="AQ29" s="25" t="s">
+      <c r="AQ29" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AR29" s="25"/>
-      <c r="AS29" s="25"/>
-      <c r="AT29" s="25"/>
-      <c r="AU29" s="25"/>
-      <c r="AV29" s="25"/>
-      <c r="AW29" s="25"/>
-      <c r="AX29" s="25"/>
-      <c r="AY29" s="25"/>
-      <c r="AZ29" s="25"/>
-      <c r="BA29" s="25"/>
-      <c r="BB29" s="25"/>
-      <c r="BC29" s="25"/>
-      <c r="BD29" s="25"/>
-      <c r="BE29" s="25"/>
-      <c r="BF29" s="26"/>
+      <c r="BF29" s="25"/>
     </row>
     <row r="30" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="25"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="25"/>
-      <c r="X30" s="25"/>
-      <c r="Y30" s="25"/>
-      <c r="Z30" s="25"/>
-      <c r="AA30" s="25"/>
-      <c r="AB30" s="25"/>
-      <c r="AC30" s="25"/>
-      <c r="AD30" s="25"/>
-      <c r="AE30" s="25"/>
-      <c r="AF30" s="25"/>
-      <c r="AG30" s="25"/>
-      <c r="AH30" s="25"/>
-      <c r="AI30" s="25"/>
-      <c r="AJ30" s="25"/>
-      <c r="AK30" s="25"/>
-      <c r="AL30" s="25"/>
-      <c r="AM30" s="25"/>
-      <c r="AN30" s="25"/>
-      <c r="AO30" s="25"/>
-      <c r="AP30" s="25"/>
-      <c r="AQ30" s="25"/>
-      <c r="AR30" s="25"/>
-      <c r="AS30" s="25"/>
-      <c r="AT30" s="25"/>
-      <c r="AU30" s="25"/>
-      <c r="AV30" s="25"/>
-      <c r="AW30" s="25"/>
-      <c r="AX30" s="25"/>
-      <c r="AY30" s="25"/>
-      <c r="AZ30" s="25"/>
-      <c r="BA30" s="25"/>
-      <c r="BB30" s="25"/>
-      <c r="BC30" s="25"/>
-      <c r="BD30" s="25"/>
-      <c r="BE30" s="25"/>
-      <c r="BF30" s="26"/>
+      <c r="BF30" s="25"/>
     </row>
     <row r="31" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="25"/>
-      <c r="S31" s="25"/>
-      <c r="T31" s="25"/>
-      <c r="U31" s="25"/>
-      <c r="V31" s="25"/>
-      <c r="W31" s="25"/>
-      <c r="X31" s="25"/>
-      <c r="Y31" s="25"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="25"/>
-      <c r="AB31" s="25"/>
-      <c r="AC31" s="25"/>
-      <c r="AD31" s="25"/>
-      <c r="AE31" s="25"/>
-      <c r="AF31" s="25"/>
-      <c r="AG31" s="25"/>
-      <c r="AH31" s="25"/>
-      <c r="AI31" s="25"/>
-      <c r="AJ31" s="25"/>
-      <c r="AK31" s="25"/>
-      <c r="AL31" s="25"/>
-      <c r="AM31" s="25"/>
-      <c r="AN31" s="25"/>
-      <c r="AO31" s="25"/>
-      <c r="AP31" s="25"/>
-      <c r="AQ31" s="25"/>
-      <c r="AR31" s="25"/>
-      <c r="AS31" s="25"/>
-      <c r="AT31" s="25"/>
-      <c r="AU31" s="25"/>
-      <c r="AV31" s="25"/>
-      <c r="AW31" s="25"/>
-      <c r="AX31" s="25"/>
-      <c r="AY31" s="25"/>
-      <c r="AZ31" s="25"/>
-      <c r="BA31" s="25"/>
-      <c r="BB31" s="25"/>
-      <c r="BC31" s="25"/>
-      <c r="BD31" s="25"/>
-      <c r="BE31" s="25"/>
-      <c r="BF31" s="26"/>
+      <c r="BF31" s="25"/>
     </row>
     <row r="32" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="25"/>
-      <c r="Y32" s="25"/>
-      <c r="Z32" s="25"/>
-      <c r="AA32" s="25"/>
-      <c r="AB32" s="25"/>
-      <c r="AC32" s="25"/>
-      <c r="AD32" s="25"/>
-      <c r="AE32" s="25"/>
-      <c r="AF32" s="25"/>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="25"/>
-      <c r="AI32" s="25"/>
-      <c r="AJ32" s="25"/>
-      <c r="AK32" s="25"/>
-      <c r="AL32" s="25"/>
-      <c r="AM32" s="25"/>
-      <c r="AN32" s="25"/>
-      <c r="AO32" s="25"/>
-      <c r="AP32" s="25"/>
-      <c r="AQ32" s="25"/>
-      <c r="AR32" s="25"/>
-      <c r="AS32" s="25"/>
-      <c r="AT32" s="25"/>
-      <c r="AU32" s="25"/>
-      <c r="AV32" s="25"/>
-      <c r="AW32" s="25"/>
-      <c r="AX32" s="25"/>
-      <c r="AY32" s="25"/>
-      <c r="AZ32" s="25"/>
-      <c r="BA32" s="25"/>
-      <c r="BB32" s="25"/>
-      <c r="BC32" s="25"/>
-      <c r="BD32" s="25"/>
-      <c r="BE32" s="25"/>
-      <c r="BF32" s="26"/>
+      <c r="BF32" s="25"/>
     </row>
     <row r="33" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
-      <c r="O33" s="25" t="s">
+      <c r="O33" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="25"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="25"/>
-      <c r="V33" s="25"/>
-      <c r="W33" s="25"/>
-      <c r="X33" s="25"/>
-      <c r="Y33" s="25"/>
-      <c r="Z33" s="25"/>
-      <c r="AA33" s="25"/>
-      <c r="AB33" s="25"/>
-      <c r="AC33" s="25"/>
-      <c r="AD33" s="25"/>
-      <c r="AE33" s="25"/>
-      <c r="AF33" s="25"/>
-      <c r="AG33" s="25"/>
-      <c r="AH33" s="25"/>
-      <c r="AI33" s="25"/>
-      <c r="AJ33" s="25"/>
-      <c r="AK33" s="25"/>
-      <c r="AL33" s="25"/>
-      <c r="AM33" s="25"/>
-      <c r="AN33" s="25"/>
-      <c r="AO33" s="25"/>
-      <c r="AP33" s="25"/>
-      <c r="AQ33" s="25"/>
-      <c r="AR33" s="25"/>
-      <c r="AS33" s="25"/>
-      <c r="AT33" s="25"/>
-      <c r="AU33" s="25"/>
-      <c r="AV33" s="25"/>
-      <c r="AW33" s="25"/>
-      <c r="AX33" s="25"/>
-      <c r="AY33" s="25"/>
-      <c r="AZ33" s="25"/>
-      <c r="BA33" s="25"/>
-      <c r="BB33" s="25"/>
-      <c r="BC33" s="25"/>
-      <c r="BD33" s="25"/>
-      <c r="BE33" s="25"/>
-      <c r="BF33" s="26"/>
+      <c r="BF33" s="25"/>
     </row>
     <row r="34" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25" t="s">
+      <c r="Y34" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-      <c r="AF34" s="25"/>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="25"/>
-      <c r="AJ34" s="25"/>
-      <c r="AK34" s="25"/>
-      <c r="AL34" s="25"/>
-      <c r="AM34" s="25"/>
-      <c r="AN34" s="25"/>
-      <c r="AO34" s="25"/>
-      <c r="AP34" s="25"/>
-      <c r="AQ34" s="25"/>
-      <c r="AR34" s="25"/>
-      <c r="AS34" s="25"/>
-      <c r="AT34" s="25"/>
-      <c r="AU34" s="25"/>
-      <c r="AV34" s="25"/>
-      <c r="AW34" s="25"/>
-      <c r="AX34" s="25"/>
-      <c r="AY34" s="25"/>
-      <c r="AZ34" s="25"/>
-      <c r="BA34" s="25"/>
-      <c r="BB34" s="25"/>
-      <c r="BC34" s="25"/>
-      <c r="BD34" s="25"/>
-      <c r="BE34" s="25"/>
-      <c r="BF34" s="26"/>
+      <c r="BF34" s="25"/>
     </row>
     <row r="35" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D35" s="24"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25" t="s">
+      <c r="J35" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="25"/>
-      <c r="AK35" s="25"/>
-      <c r="AL35" s="25"/>
-      <c r="AM35" s="25"/>
-      <c r="AN35" s="25"/>
-      <c r="AO35" s="25"/>
-      <c r="AP35" s="25"/>
-      <c r="AQ35" s="25"/>
-      <c r="AR35" s="25"/>
-      <c r="AS35" s="25"/>
-      <c r="AT35" s="25"/>
-      <c r="AU35" s="25"/>
-      <c r="AV35" s="25"/>
-      <c r="AW35" s="25"/>
-      <c r="AX35" s="25"/>
-      <c r="AY35" s="25"/>
-      <c r="AZ35" s="25"/>
-      <c r="BA35" s="25"/>
-      <c r="BB35" s="25"/>
-      <c r="BC35" s="25"/>
-      <c r="BD35" s="25"/>
-      <c r="BE35" s="25"/>
-      <c r="BF35" s="26"/>
+      <c r="BF35" s="25"/>
     </row>
     <row r="36" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D36" s="24"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="25"/>
-      <c r="S36" s="25"/>
-      <c r="T36" s="25"/>
-      <c r="U36" s="25"/>
-      <c r="V36" s="25"/>
-      <c r="W36" s="25"/>
-      <c r="X36" s="25"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="25"/>
-      <c r="AA36" s="25"/>
-      <c r="AB36" s="25"/>
-      <c r="AC36" s="25"/>
-      <c r="AD36" s="25"/>
-      <c r="AE36" s="25"/>
-      <c r="AF36" s="25"/>
-      <c r="AG36" s="25"/>
-      <c r="AH36" s="25"/>
-      <c r="AI36" s="25"/>
-      <c r="AJ36" s="25"/>
-      <c r="AK36" s="25"/>
-      <c r="AL36" s="25"/>
-      <c r="AM36" s="25"/>
-      <c r="AN36" s="25"/>
-      <c r="AO36" s="25"/>
-      <c r="AP36" s="25"/>
-      <c r="AQ36" s="25"/>
-      <c r="AR36" s="25"/>
-      <c r="AS36" s="25"/>
-      <c r="AT36" s="25"/>
-      <c r="AU36" s="25"/>
-      <c r="AV36" s="25"/>
-      <c r="AW36" s="25"/>
-      <c r="AX36" s="25"/>
-      <c r="AY36" s="25"/>
-      <c r="AZ36" s="25"/>
-      <c r="BA36" s="25"/>
-      <c r="BB36" s="25"/>
-      <c r="BC36" s="25"/>
-      <c r="BD36" s="25"/>
-      <c r="BE36" s="25"/>
-      <c r="BF36" s="26"/>
+      <c r="BF36" s="25"/>
     </row>
     <row r="37" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D37" s="24"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="25"/>
-      <c r="S37" s="25"/>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-      <c r="V37" s="25"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="25"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="25"/>
-      <c r="AA37" s="25"/>
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="25"/>
-      <c r="AD37" s="25"/>
-      <c r="AE37" s="25"/>
-      <c r="AF37" s="25"/>
-      <c r="AG37" s="25"/>
-      <c r="AH37" s="25"/>
-      <c r="AI37" s="25"/>
-      <c r="AJ37" s="25"/>
-      <c r="AK37" s="25"/>
-      <c r="AL37" s="25"/>
-      <c r="AM37" s="25"/>
-      <c r="AN37" s="25"/>
-      <c r="AO37" s="25"/>
-      <c r="AP37" s="25"/>
-      <c r="AQ37" s="25"/>
-      <c r="AR37" s="25"/>
-      <c r="AS37" s="25"/>
-      <c r="AT37" s="25"/>
-      <c r="AU37" s="25"/>
-      <c r="AV37" s="25"/>
-      <c r="AW37" s="25"/>
-      <c r="AX37" s="25"/>
-      <c r="AY37" s="25"/>
-      <c r="AZ37" s="25"/>
-      <c r="BA37" s="25"/>
-      <c r="BB37" s="25"/>
-      <c r="BC37" s="25"/>
-      <c r="BD37" s="25"/>
-      <c r="BE37" s="25"/>
-      <c r="BF37" s="26"/>
+      <c r="BF37" s="25"/>
     </row>
     <row r="38" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D38" s="24"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="25"/>
-      <c r="N38" s="25"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="25"/>
-      <c r="S38" s="25" t="s">
+      <c r="S38" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="T38" s="25"/>
-      <c r="U38" s="25"/>
-      <c r="V38" s="25"/>
-      <c r="W38" s="25"/>
-      <c r="X38" s="25"/>
-      <c r="Y38" s="25"/>
-      <c r="Z38" s="25"/>
-      <c r="AA38" s="25"/>
-      <c r="AB38" s="25"/>
-      <c r="AC38" s="25"/>
-      <c r="AD38" s="25"/>
-      <c r="AE38" s="25"/>
-      <c r="AF38" s="25"/>
-      <c r="AG38" s="25"/>
-      <c r="AH38" s="25"/>
-      <c r="AI38" s="25"/>
-      <c r="AJ38" s="25"/>
-      <c r="AK38" s="25"/>
-      <c r="AL38" s="25"/>
-      <c r="AM38" s="25"/>
-      <c r="AN38" s="25"/>
-      <c r="AO38" s="25"/>
-      <c r="AP38" s="25"/>
-      <c r="AQ38" s="25"/>
-      <c r="AR38" s="25"/>
-      <c r="AS38" s="25"/>
-      <c r="AT38" s="25"/>
-      <c r="AU38" s="25"/>
-      <c r="AV38" s="25"/>
-      <c r="AW38" s="25"/>
-      <c r="AX38" s="25"/>
-      <c r="AY38" s="25"/>
-      <c r="AZ38" s="25"/>
-      <c r="BA38" s="25"/>
-      <c r="BB38" s="25"/>
-      <c r="BC38" s="25"/>
-      <c r="BD38" s="25"/>
-      <c r="BE38" s="25"/>
-      <c r="BF38" s="26"/>
+      <c r="BF38" s="25"/>
     </row>
     <row r="39" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25"/>
-      <c r="N39" s="25"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="25"/>
-      <c r="S39" s="25"/>
-      <c r="T39" s="25"/>
-      <c r="U39" s="25"/>
-      <c r="V39" s="25"/>
-      <c r="W39" s="25"/>
-      <c r="X39" s="25"/>
-      <c r="Y39" s="25"/>
-      <c r="Z39" s="25"/>
-      <c r="AA39" s="25"/>
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="25"/>
-      <c r="AD39" s="25"/>
-      <c r="AE39" s="25"/>
-      <c r="AF39" s="25"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="25"/>
-      <c r="AJ39" s="25"/>
-      <c r="AK39" s="25"/>
-      <c r="AL39" s="25"/>
-      <c r="AM39" s="25"/>
-      <c r="AN39" s="25"/>
-      <c r="AO39" s="25"/>
-      <c r="AP39" s="25"/>
-      <c r="AQ39" s="25"/>
-      <c r="AR39" s="25"/>
-      <c r="AS39" s="25"/>
-      <c r="AT39" s="25"/>
-      <c r="AU39" s="25"/>
-      <c r="AV39" s="25"/>
-      <c r="AW39" s="25"/>
-      <c r="AX39" s="25"/>
-      <c r="AY39" s="25"/>
-      <c r="AZ39" s="25"/>
-      <c r="BA39" s="25"/>
-      <c r="BB39" s="25"/>
-      <c r="BC39" s="25"/>
-      <c r="BD39" s="25"/>
-      <c r="BE39" s="25"/>
-      <c r="BF39" s="26"/>
+      <c r="BF39" s="25"/>
     </row>
     <row r="40" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D40" s="24"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="25"/>
-      <c r="N40" s="25"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="25"/>
-      <c r="R40" s="25"/>
-      <c r="S40" s="25"/>
-      <c r="T40" s="25"/>
-      <c r="U40" s="25"/>
-      <c r="V40" s="25"/>
-      <c r="W40" s="25"/>
-      <c r="X40" s="25"/>
-      <c r="Y40" s="25"/>
-      <c r="Z40" s="25"/>
-      <c r="AA40" s="25"/>
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="25"/>
-      <c r="AD40" s="25"/>
-      <c r="AE40" s="25"/>
-      <c r="AF40" s="25"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="25"/>
-      <c r="AJ40" s="25"/>
-      <c r="AK40" s="25"/>
-      <c r="AL40" s="25"/>
-      <c r="AM40" s="25"/>
-      <c r="AN40" s="25"/>
-      <c r="AO40" s="25"/>
-      <c r="AP40" s="25"/>
-      <c r="AQ40" s="25"/>
-      <c r="AR40" s="25"/>
-      <c r="AS40" s="25"/>
-      <c r="AT40" s="25"/>
-      <c r="AU40" s="25"/>
-      <c r="AV40" s="25"/>
-      <c r="AW40" s="25"/>
-      <c r="AX40" s="25"/>
-      <c r="AY40" s="25"/>
-      <c r="AZ40" s="25"/>
-      <c r="BA40" s="25"/>
-      <c r="BB40" s="25"/>
-      <c r="BC40" s="25"/>
-      <c r="BD40" s="25"/>
-      <c r="BE40" s="25"/>
-      <c r="BF40" s="26"/>
+      <c r="BF40" s="25"/>
     </row>
     <row r="41" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D41" s="24"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="25"/>
-      <c r="S41" s="25"/>
-      <c r="T41" s="25"/>
-      <c r="U41" s="25"/>
-      <c r="V41" s="25"/>
-      <c r="W41" s="25"/>
-      <c r="X41" s="25"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="25"/>
-      <c r="AA41" s="25"/>
-      <c r="AB41" s="25"/>
-      <c r="AC41" s="25"/>
-      <c r="AD41" s="25"/>
-      <c r="AE41" s="25"/>
-      <c r="AF41" s="25"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="25"/>
-      <c r="AJ41" s="25"/>
-      <c r="AK41" s="25"/>
-      <c r="AL41" s="25"/>
-      <c r="AM41" s="25"/>
-      <c r="AN41" s="25"/>
-      <c r="AO41" s="25"/>
-      <c r="AP41" s="25"/>
-      <c r="AQ41" s="25"/>
-      <c r="AR41" s="25"/>
-      <c r="AS41" s="25"/>
-      <c r="AT41" s="25"/>
-      <c r="AU41" s="25"/>
-      <c r="AV41" s="25"/>
-      <c r="AW41" s="25"/>
-      <c r="AX41" s="25"/>
-      <c r="AY41" s="25"/>
-      <c r="AZ41" s="25"/>
-      <c r="BA41" s="25"/>
-      <c r="BB41" s="25"/>
-      <c r="BC41" s="25"/>
-      <c r="BD41" s="25"/>
-      <c r="BE41" s="25"/>
-      <c r="BF41" s="26"/>
+      <c r="BF41" s="25"/>
     </row>
     <row r="42" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D42" s="24"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="25"/>
-      <c r="Q42" s="25"/>
-      <c r="R42" s="25"/>
-      <c r="S42" s="25"/>
-      <c r="T42" s="25"/>
-      <c r="U42" s="25"/>
-      <c r="V42" s="25"/>
-      <c r="W42" s="25"/>
-      <c r="X42" s="25"/>
-      <c r="Y42" s="25"/>
-      <c r="Z42" s="25"/>
-      <c r="AA42" s="25"/>
-      <c r="AB42" s="25"/>
-      <c r="AC42" s="25"/>
-      <c r="AD42" s="25"/>
-      <c r="AE42" s="25"/>
-      <c r="AF42" s="25"/>
-      <c r="AG42" s="25"/>
-      <c r="AH42" s="25"/>
-      <c r="AI42" s="25"/>
-      <c r="AJ42" s="25"/>
-      <c r="AK42" s="25"/>
-      <c r="AL42" s="25"/>
-      <c r="AM42" s="25"/>
-      <c r="AN42" s="25"/>
-      <c r="AO42" s="25"/>
-      <c r="AP42" s="25"/>
-      <c r="AQ42" s="25"/>
-      <c r="AR42" s="25"/>
-      <c r="AS42" s="25"/>
-      <c r="AT42" s="25"/>
-      <c r="AU42" s="25"/>
-      <c r="AV42" s="25"/>
-      <c r="AW42" s="25"/>
-      <c r="AX42" s="25"/>
-      <c r="AY42" s="25"/>
-      <c r="AZ42" s="25"/>
-      <c r="BA42" s="25"/>
-      <c r="BB42" s="25"/>
-      <c r="BC42" s="25"/>
-      <c r="BD42" s="25"/>
-      <c r="BE42" s="25"/>
-      <c r="BF42" s="26"/>
+      <c r="BF42" s="25"/>
     </row>
     <row r="43" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D43" s="24"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="25"/>
-      <c r="R43" s="25"/>
-      <c r="S43" s="25"/>
-      <c r="T43" s="25"/>
-      <c r="U43" s="25"/>
-      <c r="V43" s="25"/>
-      <c r="W43" s="25"/>
-      <c r="X43" s="25"/>
-      <c r="Y43" s="25"/>
-      <c r="Z43" s="25"/>
-      <c r="AA43" s="25"/>
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="25"/>
-      <c r="AD43" s="25"/>
-      <c r="AE43" s="25"/>
-      <c r="AF43" s="25"/>
-      <c r="AG43" s="25"/>
-      <c r="AH43" s="25"/>
-      <c r="AI43" s="25"/>
-      <c r="AJ43" s="25"/>
-      <c r="AK43" s="25"/>
-      <c r="AL43" s="25"/>
-      <c r="AM43" s="25"/>
-      <c r="AN43" s="25"/>
-      <c r="AO43" s="25"/>
-      <c r="AP43" s="25"/>
-      <c r="AQ43" s="25"/>
-      <c r="AR43" s="25"/>
-      <c r="AS43" s="25"/>
-      <c r="AT43" s="25"/>
-      <c r="AU43" s="25"/>
-      <c r="AV43" s="25"/>
-      <c r="AW43" s="25"/>
-      <c r="AX43" s="25"/>
-      <c r="AY43" s="25"/>
-      <c r="AZ43" s="25"/>
-      <c r="BA43" s="25"/>
-      <c r="BB43" s="25"/>
-      <c r="BC43" s="25"/>
-      <c r="BD43" s="25"/>
-      <c r="BE43" s="25"/>
-      <c r="BF43" s="26"/>
+      <c r="BF43" s="25"/>
     </row>
     <row r="44" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D44" s="24"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="25"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="25"/>
-      <c r="T44" s="25"/>
-      <c r="U44" s="25"/>
-      <c r="V44" s="25"/>
-      <c r="W44" s="25"/>
-      <c r="X44" s="25"/>
-      <c r="Y44" s="25"/>
-      <c r="Z44" s="25"/>
-      <c r="AA44" s="25"/>
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="25"/>
-      <c r="AD44" s="25"/>
-      <c r="AE44" s="25"/>
-      <c r="AF44" s="25"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="25"/>
-      <c r="AJ44" s="25"/>
-      <c r="AK44" s="25"/>
-      <c r="AL44" s="25"/>
-      <c r="AM44" s="25"/>
-      <c r="AN44" s="25"/>
-      <c r="AO44" s="25"/>
-      <c r="AP44" s="25"/>
-      <c r="AQ44" s="25"/>
-      <c r="AR44" s="25"/>
-      <c r="AS44" s="25"/>
-      <c r="AT44" s="25"/>
-      <c r="AU44" s="25"/>
-      <c r="AV44" s="25"/>
-      <c r="AW44" s="25"/>
-      <c r="AX44" s="25"/>
-      <c r="AY44" s="25"/>
-      <c r="AZ44" s="25"/>
-      <c r="BA44" s="25"/>
-      <c r="BB44" s="25"/>
-      <c r="BC44" s="25"/>
-      <c r="BD44" s="25"/>
-      <c r="BE44" s="25"/>
-      <c r="BF44" s="26"/>
+      <c r="BF44" s="25"/>
     </row>
     <row r="45" spans="4:58" x14ac:dyDescent="0.4">
       <c r="D45" s="24"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
-      <c r="L45" s="25"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
-      <c r="O45" s="25"/>
-      <c r="P45" s="25"/>
-      <c r="Q45" s="25"/>
-      <c r="R45" s="25"/>
-      <c r="S45" s="25"/>
-      <c r="T45" s="25"/>
-      <c r="U45" s="25"/>
-      <c r="V45" s="25"/>
-      <c r="W45" s="25"/>
-      <c r="X45" s="25"/>
-      <c r="Y45" s="25"/>
-      <c r="Z45" s="25"/>
-      <c r="AA45" s="25"/>
-      <c r="AB45" s="25"/>
-      <c r="AC45" s="25"/>
-      <c r="AD45" s="25"/>
-      <c r="AE45" s="25"/>
-      <c r="AF45" s="25"/>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="25"/>
-      <c r="AI45" s="25"/>
-      <c r="AJ45" s="25"/>
-      <c r="AK45" s="25"/>
-      <c r="AL45" s="25"/>
-      <c r="AM45" s="25"/>
-      <c r="AN45" s="25"/>
-      <c r="AO45" s="25"/>
-      <c r="AP45" s="25"/>
-      <c r="AQ45" s="25"/>
-      <c r="AR45" s="25"/>
-      <c r="AS45" s="25"/>
-      <c r="AT45" s="25"/>
-      <c r="AU45" s="25"/>
-      <c r="AV45" s="25"/>
-      <c r="AW45" s="25"/>
-      <c r="AX45" s="25"/>
-      <c r="AY45" s="25"/>
-      <c r="AZ45" s="25"/>
-      <c r="BA45" s="25"/>
-      <c r="BB45" s="25"/>
-      <c r="BC45" s="25"/>
-      <c r="BD45" s="25"/>
-      <c r="BE45" s="25"/>
-      <c r="BF45" s="26"/>
+      <c r="BF45" s="25"/>
     </row>
     <row r="46" spans="4:58" x14ac:dyDescent="0.4">
-      <c r="D46" s="27"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28"/>
-      <c r="AB46" s="28"/>
-      <c r="AC46" s="28"/>
-      <c r="AD46" s="28"/>
-      <c r="AE46" s="28"/>
-      <c r="AF46" s="28"/>
-      <c r="AG46" s="28"/>
-      <c r="AH46" s="28"/>
-      <c r="AI46" s="28"/>
-      <c r="AJ46" s="28"/>
-      <c r="AK46" s="28"/>
-      <c r="AL46" s="28"/>
-      <c r="AM46" s="28"/>
-      <c r="AN46" s="28"/>
-      <c r="AO46" s="28"/>
-      <c r="AP46" s="28"/>
-      <c r="AQ46" s="28"/>
-      <c r="AR46" s="28"/>
-      <c r="AS46" s="28"/>
-      <c r="AT46" s="28"/>
-      <c r="AU46" s="28"/>
-      <c r="AV46" s="28"/>
-      <c r="AW46" s="28"/>
-      <c r="AX46" s="28"/>
-      <c r="AY46" s="28"/>
-      <c r="AZ46" s="28"/>
-      <c r="BA46" s="28"/>
-      <c r="BB46" s="28"/>
-      <c r="BC46" s="28"/>
-      <c r="BD46" s="28"/>
-      <c r="BE46" s="28"/>
-      <c r="BF46" s="29"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="27"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="P46" s="27"/>
+      <c r="Q46" s="27"/>
+      <c r="R46" s="27"/>
+      <c r="S46" s="27"/>
+      <c r="T46" s="27"/>
+      <c r="U46" s="27"/>
+      <c r="V46" s="27"/>
+      <c r="W46" s="27"/>
+      <c r="X46" s="27"/>
+      <c r="Y46" s="27"/>
+      <c r="Z46" s="27"/>
+      <c r="AA46" s="27"/>
+      <c r="AB46" s="27"/>
+      <c r="AC46" s="27"/>
+      <c r="AD46" s="27"/>
+      <c r="AE46" s="27"/>
+      <c r="AF46" s="27"/>
+      <c r="AG46" s="27"/>
+      <c r="AH46" s="27"/>
+      <c r="AI46" s="27"/>
+      <c r="AJ46" s="27"/>
+      <c r="AK46" s="27"/>
+      <c r="AL46" s="27"/>
+      <c r="AM46" s="27"/>
+      <c r="AN46" s="27"/>
+      <c r="AO46" s="27"/>
+      <c r="AP46" s="27"/>
+      <c r="AQ46" s="27"/>
+      <c r="AR46" s="27"/>
+      <c r="AS46" s="27"/>
+      <c r="AT46" s="27"/>
+      <c r="AU46" s="27"/>
+      <c r="AV46" s="27"/>
+      <c r="AW46" s="27"/>
+      <c r="AX46" s="27"/>
+      <c r="AY46" s="27"/>
+      <c r="AZ46" s="27"/>
+      <c r="BA46" s="27"/>
+      <c r="BB46" s="27"/>
+      <c r="BC46" s="27"/>
+      <c r="BD46" s="27"/>
+      <c r="BE46" s="27"/>
+      <c r="BF46" s="28"/>
     </row>
     <row r="52" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
@@ -16057,358 +14490,84 @@
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C63" s="24"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="25"/>
-      <c r="K63" s="25"/>
-      <c r="L63" s="25"/>
-      <c r="M63" s="25"/>
-      <c r="N63" s="25"/>
-      <c r="O63" s="25"/>
-      <c r="P63" s="25"/>
-      <c r="Q63" s="25"/>
-      <c r="R63" s="25"/>
-      <c r="S63" s="25"/>
-      <c r="T63" s="25"/>
-      <c r="U63" s="25"/>
-      <c r="V63" s="25"/>
-      <c r="W63" s="25"/>
-      <c r="X63" s="25"/>
-      <c r="Y63" s="25"/>
-      <c r="Z63" s="25"/>
-      <c r="AA63" s="26"/>
+      <c r="AA63" s="25"/>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C64" s="24"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-      <c r="J64" s="25"/>
-      <c r="K64" s="25"/>
-      <c r="L64" s="25"/>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
-      <c r="O64" s="25" t="s">
+      <c r="O64" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="P64" s="25"/>
-      <c r="Q64" s="25"/>
-      <c r="R64" s="25"/>
-      <c r="S64" s="25"/>
-      <c r="T64" s="25"/>
-      <c r="U64" s="25"/>
-      <c r="V64" s="25"/>
-      <c r="W64" s="25"/>
-      <c r="X64" s="25"/>
-      <c r="Y64" s="25"/>
-      <c r="Z64" s="25"/>
-      <c r="AA64" s="26"/>
+      <c r="AA64" s="25"/>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C65" s="24"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="25"/>
-      <c r="J65" s="25"/>
-      <c r="K65" s="25"/>
-      <c r="L65" s="25"/>
-      <c r="M65" s="25"/>
-      <c r="N65" s="25"/>
-      <c r="O65" s="25"/>
-      <c r="P65" s="25"/>
-      <c r="Q65" s="25"/>
-      <c r="R65" s="25"/>
-      <c r="S65" s="25"/>
-      <c r="T65" s="25"/>
-      <c r="U65" s="25"/>
-      <c r="V65" s="25"/>
-      <c r="W65" s="25"/>
-      <c r="X65" s="25"/>
-      <c r="Y65" s="25"/>
-      <c r="Z65" s="25"/>
-      <c r="AA65" s="26"/>
+      <c r="AA65" s="25"/>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C66" s="24"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
-      <c r="K66" s="25"/>
-      <c r="L66" s="25"/>
-      <c r="M66" s="25"/>
-      <c r="N66" s="25"/>
-      <c r="O66" s="25"/>
-      <c r="P66" s="25"/>
-      <c r="Q66" s="25"/>
-      <c r="R66" s="25"/>
-      <c r="S66" s="25"/>
-      <c r="T66" s="25"/>
-      <c r="U66" s="25"/>
-      <c r="V66" s="25"/>
-      <c r="W66" s="25"/>
-      <c r="X66" s="25"/>
-      <c r="Y66" s="25"/>
-      <c r="Z66" s="25"/>
-      <c r="AA66" s="26"/>
+      <c r="AA66" s="25"/>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C67" s="24"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
-      <c r="J67" s="25" t="s">
+      <c r="J67" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K67" s="25"/>
-      <c r="L67" s="25"/>
-      <c r="M67" s="25"/>
-      <c r="N67" s="25"/>
-      <c r="O67" s="25"/>
-      <c r="P67" s="25"/>
-      <c r="Q67" s="25"/>
-      <c r="R67" s="25"/>
-      <c r="S67" s="25"/>
-      <c r="T67" s="25"/>
-      <c r="U67" s="25"/>
-      <c r="V67" s="25"/>
-      <c r="W67" s="25"/>
-      <c r="X67" s="25"/>
-      <c r="Y67" s="25"/>
-      <c r="Z67" s="25"/>
-      <c r="AA67" s="26"/>
+      <c r="AA67" s="25"/>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C68" s="24"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="25"/>
-      <c r="L68" s="25"/>
-      <c r="M68" s="25"/>
-      <c r="N68" s="25"/>
-      <c r="O68" s="25"/>
-      <c r="P68" s="25"/>
-      <c r="Q68" s="25"/>
-      <c r="R68" s="25"/>
-      <c r="S68" s="25"/>
-      <c r="T68" s="25"/>
-      <c r="U68" s="25"/>
-      <c r="V68" s="25"/>
-      <c r="W68" s="25"/>
-      <c r="X68" s="25"/>
-      <c r="Y68" s="25"/>
-      <c r="Z68" s="25"/>
-      <c r="AA68" s="26"/>
+      <c r="AA68" s="25"/>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C69" s="24"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="25"/>
-      <c r="K69" s="25"/>
-      <c r="L69" s="25"/>
-      <c r="M69" s="25"/>
-      <c r="N69" s="25"/>
-      <c r="O69" s="25"/>
-      <c r="P69" s="25"/>
-      <c r="Q69" s="25"/>
-      <c r="R69" s="25"/>
-      <c r="S69" s="25"/>
-      <c r="T69" s="25"/>
-      <c r="U69" s="25"/>
-      <c r="V69" s="25"/>
-      <c r="W69" s="25"/>
-      <c r="X69" s="25"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="25"/>
-      <c r="AA69" s="26"/>
+      <c r="AA69" s="25"/>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C70" s="24"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
-      <c r="I70" s="25"/>
-      <c r="J70" s="25"/>
-      <c r="K70" s="25"/>
-      <c r="L70" s="25"/>
-      <c r="M70" s="25"/>
-      <c r="N70" s="25"/>
-      <c r="O70" s="25"/>
-      <c r="P70" s="25"/>
-      <c r="Q70" s="25"/>
-      <c r="R70" s="25"/>
-      <c r="S70" s="25"/>
-      <c r="T70" s="25"/>
-      <c r="U70" s="25"/>
-      <c r="V70" s="25"/>
-      <c r="W70" s="25"/>
-      <c r="X70" s="25"/>
-      <c r="Y70" s="25"/>
-      <c r="Z70" s="25"/>
-      <c r="AA70" s="26"/>
+      <c r="AA70" s="25"/>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C71" s="24"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="J71" s="25"/>
-      <c r="K71" s="25"/>
-      <c r="L71" s="25"/>
-      <c r="M71" s="25"/>
-      <c r="N71" s="25"/>
-      <c r="O71" s="25"/>
-      <c r="P71" s="25"/>
-      <c r="Q71" s="25"/>
-      <c r="R71" s="25"/>
-      <c r="S71" s="25"/>
-      <c r="T71" s="25"/>
-      <c r="U71" s="25"/>
-      <c r="V71" s="25"/>
-      <c r="W71" s="25"/>
-      <c r="X71" s="25"/>
-      <c r="Y71" s="25"/>
-      <c r="Z71" s="25"/>
-      <c r="AA71" s="26"/>
+      <c r="AA71" s="25"/>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C72" s="24"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25"/>
-      <c r="I72" s="25"/>
-      <c r="J72" s="25"/>
-      <c r="K72" s="25"/>
-      <c r="L72" s="25"/>
-      <c r="M72" s="25"/>
-      <c r="N72" s="25"/>
-      <c r="O72" s="25"/>
-      <c r="P72" s="25"/>
-      <c r="Q72" s="25"/>
-      <c r="R72" s="25"/>
-      <c r="S72" s="25"/>
-      <c r="T72" s="25"/>
-      <c r="U72" s="25"/>
-      <c r="V72" s="25"/>
-      <c r="W72" s="25"/>
-      <c r="X72" s="25"/>
-      <c r="Y72" s="25"/>
-      <c r="Z72" s="25"/>
-      <c r="AA72" s="26"/>
+      <c r="AA72" s="25"/>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C73" s="24"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="25"/>
-      <c r="J73" s="25"/>
-      <c r="K73" s="25"/>
-      <c r="L73" s="25"/>
-      <c r="M73" s="25"/>
-      <c r="N73" s="25"/>
-      <c r="O73" s="25"/>
-      <c r="P73" s="25"/>
-      <c r="Q73" s="25"/>
-      <c r="R73" s="25"/>
-      <c r="S73" s="25"/>
-      <c r="T73" s="25"/>
-      <c r="U73" s="25"/>
-      <c r="V73" s="25"/>
-      <c r="W73" s="25"/>
-      <c r="X73" s="25"/>
-      <c r="Y73" s="25"/>
-      <c r="Z73" s="25"/>
-      <c r="AA73" s="26"/>
+      <c r="AA73" s="25"/>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.4">
       <c r="C74" s="24"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
-      <c r="I74" s="25"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="25"/>
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
-      <c r="N74" s="25"/>
-      <c r="O74" s="25"/>
-      <c r="P74" s="25"/>
-      <c r="Q74" s="25"/>
-      <c r="R74" s="25"/>
-      <c r="S74" s="25"/>
-      <c r="T74" s="25"/>
-      <c r="U74" s="25"/>
-      <c r="V74" s="25"/>
-      <c r="W74" s="25"/>
-      <c r="X74" s="25"/>
-      <c r="Y74" s="25"/>
-      <c r="Z74" s="25"/>
-      <c r="AA74" s="26"/>
+      <c r="AA74" s="25"/>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="C75" s="27"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="28"/>
-      <c r="J75" s="28"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="28"/>
-      <c r="M75" s="28"/>
-      <c r="N75" s="28"/>
-      <c r="O75" s="28"/>
-      <c r="P75" s="28"/>
-      <c r="Q75" s="28"/>
-      <c r="R75" s="28"/>
-      <c r="S75" s="28"/>
-      <c r="T75" s="28"/>
-      <c r="U75" s="28"/>
-      <c r="V75" s="28"/>
-      <c r="W75" s="28"/>
-      <c r="X75" s="28"/>
-      <c r="Y75" s="28"/>
-      <c r="Z75" s="28"/>
-      <c r="AA75" s="29"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
+      <c r="J75" s="27"/>
+      <c r="K75" s="27"/>
+      <c r="L75" s="27"/>
+      <c r="M75" s="27"/>
+      <c r="N75" s="27"/>
+      <c r="O75" s="27"/>
+      <c r="P75" s="27"/>
+      <c r="Q75" s="27"/>
+      <c r="R75" s="27"/>
+      <c r="S75" s="27"/>
+      <c r="T75" s="27"/>
+      <c r="U75" s="27"/>
+      <c r="V75" s="27"/>
+      <c r="W75" s="27"/>
+      <c r="X75" s="27"/>
+      <c r="Y75" s="27"/>
+      <c r="Z75" s="27"/>
+      <c r="AA75" s="28"/>
     </row>
     <row r="79" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3" t="s">
